--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -545,6 +545,53 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="150" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>«BND, CIA, Gladio e le reti stay-behind tedesche (1945-1991)»</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>confermata al Livello A (Org. Gehlen-&gt;BND 1.4.1956; Critchfield/ZIPPER/Pullach; BDJ-Technischer Dienst 1952, Zinn 8.10.1952; Felfe arresto 6.11.1961/scambio 1969; Wessel; Guillaume; Casson-Andreotti 24.10.1990; risoluzione PE 22.11.1990)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>richiama l'Aginter (Guérin-Sérac, 9.1966) = spina del corpus; i due lavori si toccano</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>l'asserzione «la CIA finanzio' l'Aginter Press» CONTRADDICE il verificato del corpus (nesso ridimensionato a possibile/leggenda): da correggere al ribasso, Livello C</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>SOLIDO e ben corredato (bibliografia di 18 rif.); pienamente utilizzabile sulla parte tedesca/gladiana; l'asserzione sull'Aginter entra col grado del corpus, non del documento</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_VERIFICA_02_BND_CIA_GLADIO.docx</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -592,6 +592,53 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="165" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>«Nazisti in fuga: Spagna e Portogallo»</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>confermata al Livello A (SOFINDUS/Bernhardt, Bayreuth 1936; Operation Safehaven 1944; Clara Stauffer ~800 salvati; Degrelle, schianto S.Sebastian 8.5.1945, cittadinanza 1954, causa Friedman 1985; Cukurs, commando Arajs, giustiziato Uruguay 1965; Skorzeny, Paladin 1970)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>RISCONTRO INCROCIATO POSITIVO col corpus: Skorzeny-Mossad (anni '60) e Paladin/DGS coincidono col gia'-verificato (Livello A) — lo rafforza, non lo contraddice</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Die Spinne/ODESSA: esistenza e portata DIBATTUTE dalla storiografia (in parte costruzioni postume) — il documento le da' per accertate: attenuare a Livello B. Stime economiche e aneddoto Eva Peron: Livello B</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>IL PIU' SOLIDO finora (bibliografia di 52 rif.); pienamente utilizzabile; Die Spinne introdotta come oggetto dibattuto, non come dato accertato</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_VERIFICA_03_NAZISTI_SPAGNA_PORTOGALLO.docx</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -639,6 +639,53 @@
         </is>
       </c>
     </row>
+    <row r="5" ht="175" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>«Reti della Criminalità Organizzata Russa»</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>snodi apicali confermati al Livello A (Vory/Obshchak; Solntsevskaya-Mikhailov, Tambovskaya-Kumarin/Petrov; Brothers' Circle OFAC 2011; Usoyan ucciso 16.1.2013; Mogilevich, Tokhtakhunov, Ivankov, Agron/Balagula; GRU 29155, Tornado Cash/Semenov, Marsalek/Wirecard; politicizzazione database MVD)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>PONTE col corpus: Agron/Balagula (Brighton Beach) legati a Genovese/Lucchese/Colombo = la fonte «Biografie famiglia Genovese» gia' in casa; da sfruttare per primo</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>OMISSIONE da correggere (Livello A): Operacion Troika (13.6.2008) presentata come smantellamento, ma nel 2018 il tribunale spagnolo ASSOLSE gli imputati. Stime d'insieme e cifre singole: Livello B. Attentati condomini 1999/Lazovsky: Livello C. Coda nomi Interpol: elenco di piste NON verificate (B/C)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>UTILE come mappatura, ben corredato; usare con 3 correzioni (esito Troika; stime al probabile; coda Interpol come piste)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_VERIFICA_04_CRIMINALITA_RUSSA.docx</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -686,6 +686,53 @@
         </is>
       </c>
     </row>
+    <row r="6" ht="175" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>«Diaspora Nazionalsocialista postbellica» (cappello, 10 teatri)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ossatura confermata al Livello A (Paperclip 1945-59, &gt;1600 scienziati; Osoaviakhim; Gehlen-&gt;BND; ratlines iberiche/Skorzeny/Perón; Stille Hilfe 1951/Burwitz; Sudafrica NP 1948; Nasser/ex-nazisti; Paraguay Villarrica 1927/1929; Australia SIU 841 casi/3 processi)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>COERENTE col corpus: conferma Gehlen (n.2) e Skorzeny/Iberia/Nasser (n.3), non contraddice; e ridimensiona ODESSA da se' (metodo)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>QUARANTENA Livello C: Skorzeny addestra Arafat (leggenda); riciclaggio Perón '&gt;1 miliardo' (gonfiato); marina tedesca addestra milizie indonesiane PETA (anacronistico, PETA 1943 giapponese). Die Spinne e arruolamento ex-SS nella Stasi: Livello B</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>BUON cappello, ben corredato e coerente col gia'-verificato; usare espungendo i 3 claim C; apre i sotto-teatri USA/URSS/Sud America da verificare incrociati</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_VERIFICA_05_DIASPORA_NAZISTA.docx</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -733,6 +733,53 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="175" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>«Nazisti in USA: l'Operazione Paperclip»</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>figure apicali confermate una per una al Livello A (Overcast/Paperclip lug.1945, JIOA, &gt;1600; von Braun NSDAP 1937/SS/Dora; Rudolph NSDAP 1931/SS, rinuncia cittadinanza 1984; Debus SS; Dornberger; Rickhey unico processato-Dora, assolto; Strughold/Dachau; Schreiber/Ravensbrück-&gt;Argentina; Barbie informatore CIC)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>COERENTE col cappello (nota n.5): cifre/date/organismi coincidono. Barbie si salda alla filiera vie di fuga (nota n.3)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>correzioni di grado A: Overcast e' del 19 (non 20) luglio; onore Strughold revocato in due tempi (biblioteca 1995, Hall of Fame 2006). Stima brevetti '~10 mld' al Livello B; coda anagrafica NARA = inventario da riscontrare (B)</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>ACCURATO e ben ancorato agli archivi; pienamente utilizzabile con 2 minime correzioni di data</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_VERIFICA_06_NAZISTI_USA_PAPERCLIP.docx</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -780,6 +780,51 @@
         </is>
       </c>
     </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>«Nazisti in URSS: l’Operazione Osoaviakhim» (sotto-teatro sovietico)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>ossatura confermata al Livello A: Osoaviakhim (notte 21-22 ott. 1946; &gt;2.200 specialisti, &gt;6.000 con le famiglie); regia Berija; Istituto A (Sinop/Suchumi, von Ardenne) e Istituto G (Agudzery, Hertz); Riehl (uranio metallico); Gröttrup a Gorodomlja; direzione sovietica sotto Korolev.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>COERENTE col corpus: dà il riscontro di dettaglio alla formula del cappello (n.5) sulla «deportazione speculare»; contraltare esatto della n.6 (Paperclip): deportazione coatta vs reclutamento negoziato.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Livello B (non C): ripartizioni numeriche fini fra dicasteri (di provenienza secondaria); dicotomia netta «contratto volontario» (Ovest) vs «coercizione» (Est), da usare come chiave interpretativa. Nessuna quarantena C.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Documento accurato, ben ancorato e coerente col cappello e con la nota gemella su Paperclip; pienamente utilizzabile, tenendo al grado del probabile le ripartizioni numeriche fini e la dicotomia volontà-coercizione.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_VERIFICA_07_NAZISTI_URSS.docx</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -825,6 +825,51 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>«Nazisti in Sud America: le Ratlines e i santuari» (sotto-teatro sudamericano)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>spina confermata al Livello A: Ratlines (non ODESSA); Hudal e Draganović a Roma; lasciapassare Croce Rossa; op. Ratline del controspionaggio USA (1947); Barbie (recluta apr. 1947, «Altmann» in Bolivia, golpe García Meza 1980, arresto 1983, ergastolo in Francia); Argentina/Perón/Fuldner/CAPRI/Eichmann/Priebke; Brasile/Stangl/Wagner/Mengele (DNA 1992); Cile/Rauff/Colonia Dignidad; Paraguay/Stroessner/Archivos del Terror; Perù/Schwend/op. Bernhard; Uruguay/Cukurs/Mossad; Stille Hilfe (revoca 1999).</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>COERENTE col corpus: conferma vie di fuga e Barbie (n.3, n.6) e Stille Hilfe (n.5); chiude l'incrocio dei tre sotto-teatri della diaspora (n.6 USA, n.7 URSS, n.8 Sud America). Argentina 1.850 file declassificati sotto Milei (2025) confermato.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>QUARANTENA Livello C: tesoro «Max Heiliger» -&gt; Skorzeny -&gt; Eva Perón (catena al condizionale); sommergibile di Göring carico di bottino (leggenda dei sottomarini del tesoro); milione di franchi Perón-&gt;Draganović (stima non documentata) - in continuità con la quarantena del «miliardo di Perón» della n.5.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Documento ricco, accurato e coerente col gia'-verificato; usare espungendo le tre catene finanziarie leggendarie, tenendo al grado del probabile le stime d'insieme (1.500-5.000 Arg.; ~2.000 Bra.; ~1.000 Cile) e il tariffario di Draganović, e correggendo la data di morte di Cukurs (23 non 24 feb. 1965).</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_VERIFICA_08_NAZISTI_SUD_AMERICA.docx</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -870,6 +870,51 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>«Biografie dei primi membri della famiglia Genovese» (repertorio prosopografico, anni '30-'50)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>fonti/ (estrazione)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>spina storica confermata al Livello A: guerra castellammarese (1930-31, Masseria ucciso apr. 1931; le cinque famiglie); genealogia Luciano-&gt;Genovese, reggenza Costello; divieto narcotici del 1948; udienze Kefauver (1951); conclave di Apalachin (14 nov. 1957, ~100 convenuti, 58 fermati); deposizione Valachi (1963). Date interne collimanti con la storiografia.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>PONTE col corpus (n.4): e' l'ancoraggio italo-americano del nesso Brighton Beach (Agron/Balagula)-Cosa Nostra. MA il repertorio si ferma agli anni '50 e NON contiene quel nesso, che e' di epoca posteriore e sta nella fonte sulle reti russe: qui solo l'anello italo-americano di partenza; l'incrocio va compiuto altrove.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Livello B/C (non verificato voce per voce): la coda di centinaia di schede individuali poggia su fonti disomogenee (Valachi, rapporto FBN 1950, NARA/censimenti, alberi genealogici 1963/75/83/89, libri divulgativi), col compilatore onestamente incerto (date di morte alternative, «non si sa altro»). Livello C per aneddoti di fonte libraria singola: Bernava nell'omicidio Tresca (attribuzione corrente ad altri esecutori); paternita' del cantante.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Repertorio prezioso come materiale di lavoro, esatto sulla spina storica; privo di apparato di fonti unitario, per il resto inventario anagrafico di affidabilita' disuguale. Usare la spina al grado pieno; trattare le schede come elenco di piste, non attribuzioni chiuse. Il ponte italo-russo (n.4) va cercato nelle fonti di epoca posteriore, non qui.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_VERIFICA_09_FAMIGLIA_GENOVESE.docx</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -915,6 +915,51 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="165" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>«Arsenale della Magliana e strage di Peteano» (depositi d'armi / eversione)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>cronaca confermata al Livello A: arsenale Magliana nello scantinato del Ministero della Sanità in via Liszt (scoperto 25 nov. 1981; canone ~1 mln lire; armi modificate, silenziatori artigianali); Peteano (31 mag. 1972, utilitaria esplosa, 3 CC uccisi - Poveromo/Dongiovanni/Ferraro; 6 innocenti di Gorizia poi assolti); confessione spontanea di Vinciguerra (Ordine Nuovo, 1984). Lettura strategia della tensione coerente col corpus.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>PONTE col corpus (n.1 stato profondo, n.2 Gladio/stay-behind): Peteano e la manovalanza nera come tesi sostenuta dalle sentenze su cui poggia il corpus.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>QUARANTENA Livello C + RETTIFICA grado A: l'affermazione che il legame esplosivo-Gladio (nasco di Aurisina, tesi Casson) sarebbe stato «smentito» e confermato civile da Salvini ROVESCIA il dato giudiziario: Casson accerto' esplosivo militare come nei depositi Gladio, e il perito Marco Morin (ex Ordine Nuovo) fu CONDANNATO (&gt;3 anni) per falsa perizia/depistaggio proprio per aver detto il contrario. Fonte citata dal doc di parte (stay-behind.it, «Salvini scagiona Gladio»). Il nesso di Casson resta in piedi.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Utile sui fatti di cronaca (arsenale e dinamica di Peteano esatti), da usare con due integrazioni di grado A sull'arsenale (cogestione NAR; provenienza della pistola dell'omicidio Pecorelli, 1979) e con la quarantena/rovesciamento della minimizzazione del nesso gladiano.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_VERIFICA_10_MAGLIANA_PETEANO.docx</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -31,7 +31,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,11 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -61,7 +66,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -70,6 +75,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -437,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -960,6 +968,51 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="165" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>«Network finanziario Sud Africa» (compilazione di organigrammi societari)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>fonti/ (estrazione)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>spina storica salvabile al Livello A: casa madre Naspers (Nasionale Pers, 1915, di ambienti nazionalisti afrikaner; Die Burger diretto da D.F. Malan, poi PM dell'apartheid nel 1948); metamorfosi in Prosus/Tencent sotto Koos Bekker (partecipazione Tencent 2001; scorporo Prosus 2019); ceto Investec/Ninety One/De Beers/JSE. Continuita' capitale-apartheid -&gt; finanza globale: nodo autentico.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>AGGANCIO all'asse apartheid del corpus (monografie Sudafrica): ma il documento NON costruisce l'argomento, lo presuppone soltanto; la mappa promessa dal titolo non e' disegnata. Tesi implicita tutta da documentare altrove.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Livello C (non verificato): la massa di centinaia di nominativi (CDA attuali di decine di multinazionali, da Naspers/Tencent a LATAM, banca indonesiana, piattaforme di consegna, studi legali) e' priva di qualunque fonte, di tono redazionale/comunicazione istituzionale, datata al presente e al futuro (nomine e previsioni 2025-2027). Ha il tono del riempitivo generato piu' che del dato riscontrato. Non entra nell'opera come fatto.</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Documento largamente inutilizzabile come fonte: dump di organigrammi senza racconto, tesi o fonti, in parte redazionale e proiettato al futuro. Salvare SOLO la spina storica (Naspers/apartheid/Bekker/Prosus/Tencent + ceto finanziario SA), da documentare per proprio conto; il resto in quarantena come inventario non verificato. Primo caso in cui il difetto e' l'assenza stessa di un testo verificabile.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_VERIFICA_11_NETWORK_SUD_AFRICA.docx</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1013,6 +1013,51 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="165" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>«Operazioni antimafia: compendio A-Z» (inventario di operazioni giudiziarie)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>fonti/ (estrazione)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>spina confermata al Livello A: Crimine-Infinito (2010, 'ndrangheta unitaria, &gt;300 arresti); Rinascita-Scott (Gratteri, dic. 2019, &gt;330 arresti, cosca Mancuso); Tramonto (stragi 1992 Capaci/Via D'Amelio); Aemilia (Grande Aracri); Spartacus (Casalesi); ciclo Gotha (Barcellona P.G.); Cupola (2018, ricostituzione Commissione dopo Riina). Inventario di operazioni reali e nominate: molto piu' affidabile della coda genovese.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>DUE PONTI col corpus: New Bridge (2014, DDA RC + FBI, cosca Ursino &lt;-&gt; famiglia Gambino NY) salda al repertorio Genovese/Gambino (n.9); il «mondo di mezzo» chiama in causa Massimo Carminati, ex NAR, la stessa figura del terrorismo nero incrociata attorno all'arsenale della Magliana (n.10).</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>RETTIFICA grado A + Livello C: il doc definisce «Mafia Capitale» un'organizzazione mafiosa, ma la Cassazione (22 ott. 2019) ESCLUSE il 416-bis, derubricando ad associazione per delinquere + reati contro la PA (condanne definitive 2022). La corruzione/appalti/accoglienza restano Livello A, ma la patente di «mafia» e' stata negata in via definitiva. Cautela Livello B sulla premessa «tutto in giudicato»: falso per le inchieste recenti; es. 'ndrangheta stragista (Graviano/Filippone) sub iudice - Cassazione annullo' i reati di sangue (dic. 2024), appello bis riconfermo' gli ergastoli il 10 lug. 2026.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Inventario solido e prezioso come mappa; spina al grado pieno; due ponti verso il corpus. Usare con due rettifiche: non chiamare «mafia» il «mondo di mezzo» (in via definitiva non lo e'); non dare per definitive le inchieste piu' recenti (a partire dalla 'ndrangheta stragista, ancora sub iudice). Accreditata al compilatore l'onesta' d'aver segnalato la voce anarchica (Scripta Manent) come non mafiosa.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_VERIFICA_12_OPERAZIONI_ANTIMAFIA.docx</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1058,6 +1058,51 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="180" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>«Nazi Havens in South America» (aish.com) - approfondimento delle fonti nominate</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>fonti/ (estrazione)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>spina fattuale COINCIDE con la n.8 e riconfermata al Livello A (Ratlines/non-ODESSA, Hudal, Peron, biografie Mengele/Rauff/Roschmann/G.Wagner/Barbie). Valore aggiunto = le FONTI nominate, gradate una per una: Uki Goñi «The Real Odessa» (2002), 20 anni d'archivi, ora fondo USHMM «Uki Goñi collection» (acq. 2010) = Livello A; Gerald Steinacher «Nazis on the Run» (2011): ICRC ~25.000 documenti, ~800 SS in Argentina con carte Croce Rossa false, antisemitismo di Burckhardt = Livello A; memorandum ambasciata USA 1947 sul Vaticano = Livello A.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>APPROFONDIMENTI col corpus: (a) NODO NUOVO non presente in n.8 - Horst Wagner (capo Inland II, collegamento MAE-SS, imputato per deportazione/omicidio di 356.000 ebrei; «Kloster Line»; libro Heidenreich 2012) = Livello A su ruolo/crimini/fuga; (b) fissata la PROVENIENZA della cifra del «miliardo di Peron» gia' quarantenata in n.5: e' la stima della giornalista Gaby Weber (2005, Mercedes-Benz, Eichmann possibile cassiere).</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Livello C (quarantena, ora con provenienza nota): il «miliardo» di riciclaggio = stima della sola Weber, non corroborata dall'accademia, Eichmann-cassiere al condizionale (l'impiego di Eichmann alla Mercedes-Benz e' pero' Livello A); Evita/Skorzeny (il doc stesso usa «si sospetta»); coda su Horst Wagner a Bariloche fra canti nazisti = probabile conflazione con Priebke, da verificare. CORREZIONE grado A: partito nazista brasiliano NON 40.000 iscritti ma ~2.822 affiliati ufficiali (cfr. n.8) + simpatizzanti; il «9.000» totale = stima dei magistrati tedeschi, Livello B.</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Non un doppione ma il compagno documentariamente piu' ricco della n.8: riconferma la spina, esplicita e ancora le fonti a due archivi solidi (fondo Goñi/USHMM; Steinacher sulla Croce Rossa), aggiunge il nodo Horst Wagner e fissa la provenienza del «miliardo» (Weber). Chiude documentariamente il teatro sudamericano.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_VERIFICA_13_NAZI_HAVENS_FONTI.docx</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1103,6 +1103,51 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="165" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>APPROFONDIMENTO di nodo - «Operazione New Bridge» (ponte 'ndrangheta-Gambino)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica (nodo, non documento)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>fatti dell'operazione al Livello A: New Bridge (feb. 2014), prima operazione congiunta polizie italiana e USA sui legami 'ndrangheta-mafie americane; coord. DDA Reggio Calabria + FBI (+ EDNY), &gt;150 uomini; org. transnazionale eroina/cocaina Calabria-America; cosca Ursino di Gioiosa Ionica &lt;-&gt; famiglia Gambino di NY; accuse: narcotraffico internazionale, traffico d'armi, riciclaggio. Fermi in Italia (RC, Napoli, Caserta, Torino, Benevento, Catanzaro) e a New York.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>figure-cerniera (Livello A): Franco Lupoi (vicino alla crew della 18a Avenue dei Gambino, contatto diretto con gli Ursino); affiliato Bonanno riciclatore + funzionario di banca NY (ponte anche di denaro); Francesco Ursino (capo cosca Gioiosa Ionica); Giovanni Morabito (nipote di Giuseppe «u tiradrittu» di Africo -&gt; cuore ionico, stessa fascia San Luca-Aspromonte di Eureka/Pollino, n.12). Ribaltamento della «Pizza Connection»: la 'ndrangheta come socio maggiore/fornitore.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>riserva di definitivita' sui singoli giudizi (Livello A sui fatti dell'operazione): fermi e capi d'imputazione documentati; il processo ha prodotto condanne in primo grado per diversi imputati, ma il singolo esito irrevocabile va verificato caso per caso (cfr. cautela generale n.12).</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Nodo pienamente utilizzabile come prova documentata del ponte contemporaneo 'ndrangheta-Gambino. Si salda alla n.9 (Gambino tra le cinque famiglie, proiezione odierna a NY) e alla n.12 (operazione gia' annoverata, qui approfondita). DISTINTO dalla pista della n.4 (Brighton Beach, mafia russa/Agron-Balagula): due assi diversi, calabro-USA vs russo-USA, da non confondere. Prima voce dedicata a un nodo, non a un documento.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_VERIFICA_14_NEW_BRIDGE.docx</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1148,6 +1148,46 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="195" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>GENERAZIONE NODI + SINAPTOGENESI - integrazione di 5 censimenti (destra/giustizia, province FI-PDL, criminalita' composita, P2/Governali, nodi per dominio)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>generati 39 nodi nuovi e 19 archi (sinapsi) conformi allo statuto del registro-madre: candidato entra a Livello C, sale per triangolazione; stato probatorio distingue definitivo/non definitivo/indagine/esito negativo (assolti-prescritti NON fanno nodo-reato).</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONI col corpus verificato: Montalto 1969 (radice mafia-eversione) -&gt; n.12; Carminati NAR/Magliana + Mafia Capitale (Alemanno genero di Rauti, Gramazio) -&gt; note 10 e 12 (416-bis escluso); Bologna 1980 mandanti P2 (Gelli/Ortolani/D'Amato/Tedeschi) -&gt; P2/Governali; Peteano/Vinciguerra CONFERMA il nesso gladiano che la n.10 aveva difeso; Gotha (Scopelliti/Sarra/Romeo), Pittelli-&gt;Rinascita-Scott, Rosso-&gt;Bonavota/Carmagnola, Creazzo-&gt;Alvaro/Eyphemos -&gt; n.12; Cinque Famiglie (Genovese/Gambino/Lucchese-Bronx/Bonanno/Colombo) -&gt; note 9, 14, 4.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>LACUNE dichiarate: molte schede provinciali sub iudice; archivio Governali segnala atti distrutti (processo Leggio, scarto 2007: persi i legami Cosa Nostra-Banco Ambrosiano-P2) o inaccessibili; il censimento composito eccede questo primo vaglio. Sinaptogenesi completa in attesa delle istruzioni dell'autore.</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_SINAPTOGENESI_INTEGRAZIONE_5_CENSIMENTI.docx + repertorio/ITALIA_NERA_NODI_INTEGRAZIONE_E_ARCHI.xlsx</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1188,6 +1188,46 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="195" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SINAPTOGENESI ESTESA - il nodo cardinale P2 come hub cross-dominio (mappa archivi + sinapsi)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>costruito il primo HUB della struttura neuronale a partire dal censimento fonti P2/Governali. Nodi-archivio (Livello A come esistenza/collocazione): processo romano 59/94 (AS Roma); fallimento Banco Ambrosiano (AS Milano); Commissione P2/Relazione Anselmi; Fondo Gelli (AS Pistoia, don. 2006); archivio uruguayano (Montevideo 1981); Archivio Flamigni (fondi Flamigni/Amendola/Nunziata); Castiglion Fibocchi (962 affiliati); conto Protezione; De Magni (massoneria-Cosa Nostra); Italicus (AS Bologna).</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>SINAPSI del hub (dalle relazioni dei consulenti della Commissione): D2 (caso Moro, Piano di Rinascita, conto Protezione/Craxi); D3 (SID parallelo, Pazienza); D6 (Sindona, Calvi, Ambrosiano, Eni-Petromin); D5 (IOR/Marcinkus); D7 (Italicus, Bologna, golpe Borghese); D8 (Pecorelli, Corriere della Sera); D10 (magistratura); D1 (armi/droga, De Magni). La P2 tocca tutti e dieci i domini = definizione di hub.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>INCROCI col corpus: Bologna, mandanti P2 (Gelli/Ortolani/D'Amato/Tedeschi) -&gt; sinaptogenesi prec.; OP. PECORELLI (relazione consulente) -&gt; NOTA 10 (l'arma dell'omicidio Pecorelli veniva dall'arsenale della Magliana di via Liszt): P2+Magliana+Pecorelli convergono. LACUNA dichiarata: atti Leggio distrutti nel 2007 (scarto Trib. Milano) = prova del legame Cosa Nostra-Banco Ambrosiano-P2 sottratta. Esito conto Protezione riportato con esattezza (Gelli annullato in appello; def. solo Larini).</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_P2_HUB_SINAPTOGENESI.docx + repertorio/ITALIA_NERA_P2_HUB_ARCHIVI_E_SINAPSI.xlsx</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1228,6 +1228,46 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="210" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>ESTRAZIONE NODI D1 - dal Censimento globale della criminalita organizzata (struttura composita)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>estratti 55 nodi del Dominio Primo (Italia 24, USA/internazionale 19, trasversali 12), ordinati per libro/area con la numerazione di scheda dell opera (201-590). Distinti: gia nel registro-madre (verde) / nuovo candidato Livello C (arancio) / storica estinta (grigio). Statuto rispettato: nodo schedato mantiene il grado, candidato nuovo entra a C e sale per triangolazione.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>CUORE ITALIANO: Cosa Nostra siciliana (Cupola, mandamenti Corleone/Brancaccio/Ciaculli/Porta Nuova); ndrangheta (Camera di Controllo, La Santa = ponte con massoneria deviata, San Luca/Rosarno/RC/Locride, Mancuso); Camorra (Casalesi, Secondigliano); SCU/Foggiana/baresi; Banda della Magliana (nodo doppio D1/D7). INTERNAZIONALE: Five Families + regionali USA + Rizzuto; cartelli messicani (fazioni Sinaloa/CJNG/Golfo/Zetas); triadi, yakuza, Bratva/Vory, mafie caucasiche; diaspora (albanese/nigeriana/Mocro).</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>INCROCI: Corleonesi/Graviano/Mancuso/Casalesi/San Luca/baresi/Grande Aracri -&gt; nota 12; Magliana -&gt; nota 10 + hub P2; Locride-Morabito -&gt; nota 14 (New Bridge); Five Families/Genovese/Gambino/Lucchese(Bronx) -&gt; note 9, 14; Bratva/caucasiche -&gt; corpus russo (memoria operativa). CATEGORIE NUOVE (candidati C): ibride paramilitari (RSF, M23, UWSA, Taleban-oppio), reti finanziarie Hezbollah/Hamas, cyber-scam compounds, cyber di Stato (Lazarus/APT41/Sandworm), RaaS. LACUNE: vaglio capillare sotto-articolazioni e numeri di scheda alla fase successiva.</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_ESTRAZIONE_NODI_D1_CRIMINALITA.docx + repertorio/ITALIA_NERA_NODI_D1_CRIMINALITA_ORGANIZZATA.xlsx</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1268,6 +1268,46 @@
         </is>
       </c>
     </row>
+    <row r="19" ht="195" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>NODO European Union Bank - banca off-shore digitale/virtuale/cyber (nodizzazione delle evidenze)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>nodizzate le evidenze su EUB: 7 nodi collegati, 8 documenti d evidenza, 7 archi. Dominio primario D6 (economia/finanza) con archi verso D1 (riciclaggio), D3 (KGB) e D2 (Eltsin/Khodorkovsky). Statuto tenuto fermo.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>FATTO al Livello A (fonti ufficiali FinCEN adv. 11, FDIC special alert, DoJ 1997, Washington Post, rapporto ONU): EUB registrata ad Antigua ~1994, PRIMA banca al mondo interamente su Internet (anonimato, segreto bancario, no domande); crollata ago. 1997 con sparizione di operatori e depositi (furto attivi non reato sotto legge antiguana). Livello B: affiliazione a MENATEP, partnership con Khodorkovsky, nesso con lo scandalo Bank of New York (nessuna banca incriminata). Livello C: narrazione Konanykhin (persecuzione KGB) da fonte di parte.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>LIGNAGGIO (arco ancestrale): EUB (1994, banca-Internet off-shore) = archetipo storico della criminalita finanziaria digitale -&gt; reti di riciclaggio transnazionale (cat. P 466-475 del censimento) -&gt; cripto-mixer sanzionati (Tornado Cash/Roman Semenov, NOTA 4) -&gt; cyber-scam compounds e RaaS (estrazione D1, cat. M e P). Da iscrivere fra gli hub off-shore accanto a Caraibi/Cipro/studi di comodo del registro.</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_NODO_EUROPEAN_UNION_BANK.docx + repertorio/ITALIA_NERA_NODO_EUROPEAN_UNION_BANK.xlsx</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1308,6 +1308,46 @@
         </is>
       </c>
     </row>
+    <row r="20" ht="195" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>APPROFONDIMENTO nodo EUB -&gt; sotto-hub del riciclaggio russo (MENATEP - Bank of New York - Mogilevich)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>trasformato il nodo isolato EUB in sotto-hub connesso del corpus russo: 11 nodi, 8 archi. La catena: EUB (banca-Internet Antigua) -&gt; MENATEP/Khodorkovsky -&gt; schema Bank of New York (Edwards/Berlin/Benex) &lt;- Inkombank &lt;- galassia Mogilevich (SMO) -&gt; Solntsevskaya -&gt; NOTA 4.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: scandalo BoNY (Edwards e Berlin guilty pleas; oltre 7 mld $ dal 1995 al 1999; BoNY non incriminata ma 38 mln $ di sanzioni); frode YBM Magnex (raid FBI 13 mag. 1998, PA; investitori -150 mln $); incriminazione Mogilevich (45 capi, distretto orientale PA, 2003; FBI Ten Most Wanted 2009). Livello B: partecipazione di MENATEP e Inkombank allo schema BoNY fino al 1998; SMO come ramo europeo della Solntsevskaya. Livello C: Mogilevich protetto/agente dei servizi; narrazione KGB di Konanykhin.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>DISTINZIONE tenuta ferma: Mogilevich e INCRIMINATO E LATITANTE, mai processato negli USA - non un condannato. INCROCI: nota 4 (Solntsevskaya/Michajlov, Mogilevich), nodo EUB (sessione), estrazione D1 (Bratva; cat. P riciclaggio; cat. M cyber). Domini: D6 (asse), D1 (Mogilevich/Solntsevskaya), D2 (Khodorkovsky), D3 (tesi da vagliare), D10 (incriminazioni).</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_SOTTOHUB_RICICLAGGIO_RUSSO_BONY.docx + repertorio/ITALIA_NERA_SOTTOHUB_RICICLAGGIO_RUSSO_BONY.xlsx</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1348,6 +1348,46 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="195" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>ESTENSIONE sotto-hub russo -&gt; dal boss all arma del gas (Mogilevich - RosUkrEnergo/Firtash - Gazprom - off-shore)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>completato il ramo energia-geopolitica del sotto-hub: 10 nodi, 8 archi. La catena: Mogilevich (controllo ALLEGATO nei cablo USA) -&gt; RosUkrEnergo (50% Gazprom / 50% Firtash-Fursin) -&gt; dispute del gas Russia-Ucraina -&gt; politica filo-russa (Yanukovych) -&gt; incriminazione USA di Firtash (titanio/Boeing) -&gt; saga estradizione di Vienna (bloccata).</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: assetto e ruolo di RUE (registrata in Svizzera; 50/50); dispute del gas 2005-2006; esistenza dei cablo diplomatici USA e dell ammissione di Firtash (legami con Mogilevich, accordo di Putin); incriminazione Firtash (Chicago 2013, ~18,5 mln $ tangenti titanio) e saga estradizione di Vienna (2014-, bloccata). Livello B: il CONTROLLO di RUE da parte di Mogilevich e ALLEGAZIONE dei cablo, non provata; finanziamento politico riferito.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>CAUTELA DECISIVA: distinguere allegazione da sentenza. Firtash INCRIMINATO, mai condannato (estradizione bloccata); Mogilevich latitante. Off-shore: RUE in Svizzera, holding viennese; hub Cipro (Bratva) dal registro. INCROCI: nota 4 (Mogilevich/Solntsevskaya), nodo EUB + sotto-hub BoNY (sessione), registro (Cipro; Gazprom-Media/Kovalchuk candidati D8). Domini: D6 (asse), D1, D2 (Ucraina/Yanukovych/Putin), D3 (cablo), D10.</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_SOTTOHUB_GAS_ROSUKRENERGO_FIRTASH.docx + repertorio/ITALIA_NERA_SOTTOHUB_GAS_ROSUKRENERGO_FIRTASH.xlsx</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1388,6 +1388,46 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="195" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ESTENSIONE sotto-hub russo -&gt; dal gas ai media (Gazprom - Bank Rossiya/Kovalchuk - National Media Group)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>aperto il fronte D8 (media/guerra cognitiva): 8 nodi, 8 archi. La catena: Gazprom (leva energetica) -&gt; cessione a prezzo di favore -&gt; Bank Rossiya / Jurij Kovalchuk (banchiere di Putin) -&gt; National Media Group -&gt; Channel One/REN TV/Channel Five/Izvestia -&gt; controllo dell informazione di massa russa.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: designazione del Tesoro USA (Kovalchuk banchiere personale/cassiere di Putin, 2014); controllo di Bank Rossiya (dal 2004); cessione da Gazprom a Bank Rossiya di asset mediatici, Sogaz e altri attivi a prezzo di favore; NMG (2008) e le reti controllate; cooperativa di dacie Ozero (nucleo della cerchia ristretta); sanzioni USA+UE. La cornice guerra cognitiva e interpretazione dell opera; il controllo mediatico e fatto documentato.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>PROMOZIONE dei candidati D8 del registro-madre (Gazprom-Media, National Media Group, Kovalchuk, Sogaz, VGTRK) da presenza testuale a nodo documentato, via triangolazione. Kovalchuk = cerniera finanza (Bank Rossiya/Sogaz) - media (NMG/Gazprom-Media) - cerchia Putin (Ozero). Perno condiviso col ramo gas: Gazprom. INCROCI: ramo gas/RosUkrEnergo (sessione); corpus Media e guerra cognitiva (memoria operativa). Domini: D6, D8 (aperto), D2.</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_SOTTOHUB_MEDIA_KOVALCHUK.docx + repertorio/ITALIA_NERA_SOTTOHUB_MEDIA_KOVALCHUK.xlsx</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1428,6 +1428,46 @@
         </is>
       </c>
     </row>
+    <row r="23" ht="210" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>FRONTE D8 - la guerra cognitiva russa in tre generazioni (IRA -&gt; Doppelganger -&gt; Tenet/Pravda)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>popolato il fronte esterno del dominio media (guerra cognitiva): 13 nodi, 8 archi, per generazioni. Gen 1 (2016): Internet Research Agency, finanziata da Prigozhin (Concord); incriminazione Mueller (2018, 13 persone); caso Concord ritirato (2020). Gen 2 (2022-): Doppelganger, siti-clone; regia Amministrazione presidenziale (Kiriyenko) via SDA (Gambashidze), Structura (Tupikin), ANO Dialog (IA/deepfake); sanzioni OFAC + sequestro 32 domini (2024). Gen 3 (2024-): Tenet Media (RT compra influencer USA, ~9,7 mln $, incriminazione SDNY); rete Pravda / LLM grooming.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: incriminazioni (Mueller 2018; SDNY 2024), sanzioni OFAC, sequestri di domini, affidavit DoJ che nomina Kiriyenko. Livello B: esistenza/volume della rete Pravda (DFRLab/EU DisinfoLab). Livello C: il MECCANISMO del LLM grooming (manipolazione dei modelli) e CONTESTATO - Harvard Misinfo Review lo legge come data voids.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>CAUTELE: caso Concord RITIRATO (nessun processo USA); influencer di Tenet INCONSAPEVOLI e non incriminati; incriminato non e condannato. INCROCI: nodo Kovalchuk/NMG (fronte interno, sessione) = contraltare interno; PROMOZIONE dei candidati D8 del registro (IRA, SDA, Gambashidze, Structura, Tupikin, ANO Dialog, Doppelganger, Tenet, RT, Pravda, Kiriyenko) via triangolazione; Prigozhin doppio nodo con Wagner (D9). Domini: D8 (asse), D2 (Kiriyenko), D3 (deepfake), D10, D9.</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_FRONTE_D8_GUERRA_COGNITIVA.docx + repertorio/ITALIA_NERA_FRONTE_D8_GUERRA_COGNITIVA.xlsx</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1468,6 +1468,46 @@
         </is>
       </c>
     </row>
+    <row r="24" ht="210" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>MINACCIA IBRIDA RUSSA IN ITALIA - la guerra cognitiva a casa (disinformazione + influenza politica)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>porta il fronte della guerra cognitiva in Italia: 9 nodi, 8 archi, su due fronti convergenti. 1) DISINFORMAZIONE: Doppelganger clona ANSA e testate occidentali (dal 2022); Italia bersaglio diretto nei cluster Pravda/Doppelganger/Meta (Commissione UE); narrative anti-Ucraina (Bucha negata) e allarmismo anti-sanzioni. 2) INFLUENZA POLITICA: affare Metropol (18 ott. 2018) - Savoini (uomo di Salvini, Associazione Lombardia-Russia) negozia uno schema petrolifero per finanziare la Lega alle europee 2019; audio pubblicato da BuzzFeed/Bellingcat/The Insider; indagine procura di Milano dal feb. 2019.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: siti-clone Doppelganger e bersagliamento dell Italia (EU DisinfoLab, Commissione UE); esistenza e contenuto dell audio del Metropol; presenza di Savoini; accordo Associazione Lombardia-Russia / Russia Unita (2017); indagine di Milano. Contenuti narrativi documentati.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>CAUTELA DECISIVA (persone viventi/indagate): l affare Metropol NON risulta consumato (nessun denaro provato trasferito); Savoini e INDAGATO, non condannato; Salvini non imputato e ha negato. Negoziazione documentata != reato accertato. INCROCI: fronte D8 esterno (sessione) qui atterra in Italia; registro-madre (candidati scansione: Savoini, Metropol Mosca, Salvini Premier, Gladio Rossa) PROMOSSI. Capitolo contemporaneo dell interferenza straniera, in continuita con la stagione storica degli apparati. Domini: D8, D2 (Lega/Savoini), D6 (petrolio), D3, D10.</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_MINACCIA_IBRIDA_RUSSA_IN_ITALIA.docx + repertorio/ITALIA_NERA_MINACCIA_IBRIDA_RUSSA_IN_ITALIA.xlsx</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1508,6 +1508,46 @@
         </is>
       </c>
     </row>
+    <row r="25" ht="210" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>NODO Khodorkovsky / Yukos - il pivot MENATEP che chiude l arco russo della sessione</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>nodizzato l intero arco: 12 nodi, 9 archi. Ascesa (MENATEP -&gt; Yukos, 61%, via privatizzazioni prestiti-per-azioni 1994-95) -&gt; caduta (Lebedev arrestato lug. 2003; arresto FSB di Khodorkovsky 25 ott. 2003; condanne 2005 e 2010; grazia di Putin 20 dic. 2013) -&gt; espropriazione (Yukos smembrata -&gt; Rosneft/Sechin, da Yuganskneftegaz) -&gt; lodo dell Aja (~50 mld $ agli ex azionisti GML; 2014, annullato 2016, ripristinato 2020, appello russo respinto) -&gt; esilio a Londra (Dossier Center, Comitato Anti-Guerra).</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>IL PIVOT: MENATEP e l anello comune ai tre nodi russi della sessione - affiliata della European Union Bank, partecipe dello schema Bank of New York, madre di Yukos. Chiude il cerchio. SALDATURA ENERGETICA: Yukos -&gt; Rosneft = la renazionalizzazione che fa dell energia leva di Stato (stesso Gazprom del ramo gas). SPECCHIO: il Dossier Center in esilio e il controcampo della guerra cognitiva del Cremlino.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: arresti, processi, condanne, grazia, espropriazione a Rosneft, lodo dell Aja e sua motivazione (rimozione di Khodorkovsky dall arena politica). EQUILIBRIO (non agiografia): la persecuzione fu selettiva/politica (accertato da tribunali internazionali/CEDU) MA la fortuna originaria nacque dalle privatizzazioni contestate degli anni 90 - entrambe le cose vanno dette. CAUTELA: il caso FSB per presa violenta del potere/terrorismo e accusa della parte persecutrice (Livello C nel merito). Domini: D6 (asse), D2, D10, D3, D8, D9.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_NODO_KHODORKOVSKY_YUKOS.docx + repertorio/ITALIA_NERA_NODO_KHODORKOVSKY_YUKOS.xlsx</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1548,6 +1548,51 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SINAPTOGENESI AGINTER PRESS + ASSI DELL'APARTHEID - nodizzazione delle monografie di ricerca profonda (circa trenta schede)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera (32 .md) + corpus/diagnostica + repertorio</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>genera 57 nodi, 24 archi, 14 reperti negativi su 6 domini. HUB: Aginter Press (Lisbona 1966; ruolo dottrinale A, operativo B) e Guerin-Serac. SERVIZI: liaison PIDE-CIA (A) distinta dalla leggenda CIA-Aginter (assenza). Le Cercle finanziato da Pretoria (A); unico ponte Aginter-Cercle = contatto Guerin-Serac/Damman 1969 (B). APARTHEID: asse nucleare RFT/URENCO-Rossing, U-Boot HDW/IKL, ISSA Israele-SA (A), obice Bull/G5, broker petroliferi (Chiavelli/Deuss/Rich). SECONDA FILIERA: Thiriart/Jeune Europe -&gt; Mutti/QUEX -&gt; Murelli/Orion -&gt; Dugin -&gt; Savoini/Metropol (through-line al presente).</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: esistenza e natura di Aginter, Ordre et Tradition, doc 'Notre action politique'; liaison PIDE/DGS-CIA; finanziamento sudafricano a Le Cercle (Khan Committee 1991); ISSA 1975; U-Boot-Affare (Bundestag); ALCORA; contro-campo comunista. Filiere atlantista e antiatlantista tenute distinte.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Livello C e reperti negativi (dichiarati): offerta nucleare Jericho (transazione non avvenuta); Aginter-CIA diretta = leggenda a fonte unica (SDCI-&gt;Laurent-&gt;Christie-&gt;Ganser); Aginter-Sudafrica NON documentato nei 5 paesi; Aginter-Asia/mondo arabo/Kissinger = assenza; FM 30-31B = falso; Delle Chiaie 'membro fondatore' = distorsione (assoluzioni giudiziarie); nesso Aginter-JFK cronologicamente impossibile; 'Shaganovitch' = fabbricazione (vero: Gusev). INCROCI: registro-madre D7 (Aginter, Guerin-Serac, ON, AN, Delle Chiaie, Giannettini gia' registrati); nota su strategia della tensione; nota Minaccia ibrida (Dugin-&gt;Savoini). Vincolo fonti rispettato (no Grokipedia, no 'il manifesto').</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>NODIZZAZIONE CERTIFICATA. Domini: D7, D3, D9, D6, D2, D10.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_SINAPTOGENESI_AGINTER_APARTHEID.docx + repertorio/ITALIA_NERA_NODI_AGINTER_APARTHEID_INTEGRAZIONE.xlsx</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1593,6 +1593,51 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SINAPTOGENESI AGINTER (APPROFONDIMENTO) - servizi dell'elenco SDCI, Terza Posizione, assi apartheid del Cono Sud</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera (33 .md) + corpus/diagnostica + repertorio</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>aggiunge 22 nodi, 14 archi, 8 reperti negativi alla voce 25. SERVIZI (elenco SDCI voce per voce): la voce GRECA (KYP/Plevris) e' la meglio fondata, da fonte primaria (lettera Guerin-Serac 3 dic 1973, atti Brescia); SDECE = matrice/provenienza non committenza; canale tedesco = Taubert/Kampfbund, non BND; Strauss != BND; DGS spagnola = Paladin/Skorzeny (post-1974). USA: liaison CIA-PIDE certa, 'CIA creo' Aginter' = eccesso di Ganser; rete Digilio/US Navy = ipotesi istruttoria. TERZA POSIZIONE (Fiore/Adinolfi/Dimitri 1978): nessun nesso organico con Aginter. ASSI: Paraguay-Vorster 1975, Rheinmetall-Durban; Cile skunk status/Cardoen; Argentina CAL 1980/P2 (Massera, Suarez Mason); Brasile Decreto 1985/MNU/Abdias.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: visite di Stato Stroessner-Vorster; P2 in Argentina (Massera, Suarez Mason); matrice SDECE/OAS del personale. Livello B: lettera KYP 1973; viaggio Grecia 1968; Taubert/Kampfbund; Rheinmetall-Paraguay-Durban; CAL 1980; Cardoen 'Made in Chile'; golpe Garcia Meza (Delle Chiaie+Barbie); mandanti Bologna (sentenza Bellini 2022, Cavallini def. 2025).</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Reperti negativi dichiarati: Piazza Fontana = assoluzioni definitive (Cassazione 2005 n.21998; Digilio 'inattendibile'); Aginter-Terza Posizione = nessun nesso organico (cronologia; TP assente dagli atti Salvini); 'CIA creo' Aginter' = eccesso tesistico; von Leers cofondatore Paladin = impossibile (morto 1965); Strauss=BND non dimostrato; presenza SA a WACL Asuncion 1979 / Archivio del Terrore = assente; Cile in 'Pia Vesta' = assente (solo Peru' e Panama); Condor-Sudafrica = sistemi paralleli. INCROCI: voce 25 (prima tornata); note su strategia della tensione; registro-madre D4 (P2) e D7.</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>NODIZZAZIONE CERTIFICATA. Domini: D7, D3, D2, D9, D6, D4.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_SINAPTOGENESI_AGINTER_APARTHEID_2.docx + repertorio/ITALIA_NERA_NODI_AGINTER_APARTHEID_APPROFONDIMENTO.xlsx</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1638,6 +1638,51 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE DEI NODI ATTORNO A VLADIMIR PUTIN - convergenza dell'arco russo, della filiera eurasiatista e (in negativo) della galassia Aginter</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio (nodi dell'intera sessione)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>fa convergere sul nodo-hub Putin 24 nodi, 15 archi, 8 reperti negativi. FASCIO 1 (solido): catena finanza/energia - Ozero/Kovalchuk/Bank Rossiya; espropriazione Yukos e lodo Aja (~50 mld); pivot MENATEP/Khodorkovsky; Gazprom renazionalizzata; tagli gas 2006/2009; RosUkrEnergo/Firtash/Mogilevich. FASCIO 2 (solido): guerra cognitiva - IRA/Prigozhin -&gt; Doppelganger -&gt; Tenet/Pravda; proiezione in Italia via Lombardia-Russia/Savoini e affare Metropol (Dugin in trattativa). FASCIO 3 (genealogia, non comando): filiera eurasiatista Thiriart -&gt; Murelli/Orion -&gt; Dugin -&gt; Malofeev/Komov.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: espropriazione Yukos/lodo Aja; sanzioni a Bank Rossiya (2014); renazionalizzazione Gazprom; tagli del gas; IRA/Doppelganger; invasione Ucraina (2022); esistenza dell'audio Metropol e di Lombardia-Russia; repressione (Navalny, Dossier Center).</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Livello B/C e reperti negativi: la galassia AGINTER/APARTHEID NON converge su Putin (assenza di riscontro: Aginter atlantista, sciolta 1974, antipodo della filiera filorussa); Thiriart-&gt;Dugin-&gt;Putin = genealogia di idee, non catena di comando; Dugin 'cervello di Putin' = semplificazione; Metropol = negoziazione documentata != reato (archiviazione 2023; Savoini indagato non condannato; Salvini non imputato); 'portafoglio di Putin'/Roldugin = allegazione; Khodorkovsky = persecuzione accertata ma origine fortuna contestata; unico ponte legittimo Aginter-Putin = ECO DI METODO (strategia della tensione = falsa bandiera), non linea di comando. INCROCI: voci 5-24 della sessione (arco russo) + voci 25-26 (Aginter/apartheid). Vincolo fonti rispettato.</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE CERTIFICATA. Domini: D2, D3, D6, D7, D8, D9, D10.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_TRIANGOLAZIONE_PUTIN.docx + repertorio/ITALIA_NERA_TRIANGOLAZIONE_PUTIN.xlsx</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1683,6 +1683,51 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>VERIFICA BIOGRAFICA DI VLADIMIR PUTIN DALLA GIOVENTU' - documentazione e certificazione su fonti online</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio (verifica online)</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>certifica la spina biografica del nodo-hub Putin in 17 tappe datate, riscontrate su fonti indipendenti reperite in rete e incrociate. Nascita a Leningrado (7 ott 1952; kommunalka vicolo Baskov; padre reduce ferito, due fratelli morti); infanzia di cortile, sambo/judo (First Person); Giurisprudenza a Leningrado (1970-75, docente Sobchak); KGB dal 1975 (scuola di Okhta); Dresda 1985-90; ritiro col grado di tenente colonnello; staff di Sobchak; Comitato Relazioni Esterne 1991; primo vicesindaco 1994; Mosca 1996; direttore FSB 1998; premier ago 1999; presidente ad interim 31 dic 1999; eletto 26 mar 2000.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: tutti i fatti biografici e di carriera (nascita, scuola, laurea, KGB, Dresda, staff Sobchak, ascesa a Mosca, FSB, premier, presidenza), riscontrati su Wikipedia, Britannica, kremlin.ru (bilanciata), GlobalSecurity, Russia Beyond, Wilson Center, RFE/RL, TBIJ, Havighurst Center (Miami), IAI.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Livello B e precisazioni (fragilita'): l'autonarrazione della gioventu' rissosa ('First Person') e' segnalata come tale; la TESSERA STASI di Dresda e' agevolazione d'accesso documentata, NON appartenenza alla Stasi (precisazione Wilson Center contro la 'sensazione stampa'); la COMMISSIONE SALYE (1992) contesto' a Putin un DIFETTO DI CONTROLLO, non una corruzione personale, e non produsse alcun procedimento (allegazione != sentenza). INCROCIO: radice biografica del nodo-hub gia' triangolato (voce 27). Verifica online, non collazione; fonte ufficiale usata ma bilanciata. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>VERIFICA CERTIFICATA. Domini: D2, D3.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_VERIFICA_BIOGRAFICA_PUTIN.docx + repertorio/ITALIA_NERA_VERIFICA_BIOGRAFICA_PUTIN.xlsx</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1728,6 +1728,51 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>PUTIN 1970-1994 IN DIECI BLOCCHI - approfondimento biografico titanico, fattualmente documentato su fonti online</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio (verifica online)</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>dieci blocchi mirati: 1) Giurisprudenza a Leningrado 1970-75 (docente Sobchak); 2) reclutamento e KGB, scuola 401 di Okhta, Secondo/Primo Direttorato; 3) Istituto Bandiera Rossa 'Andropov' 1984-85, nome in codice 'Platov'; 4) Dresda 1985-90, residentura di Angelikastrasse 4, cooperazione Stasi (Boehm), medaglia 1988, fascicolo declassificato 2019 ('solida B'); 5) crollo di Dresda dic. 1989 ('Mosca tace', documenti bruciati); 6) rientro 1990, prorettore, 'riserva attiva' (vicerettore Molchanov); 7) staff di Sobchak, dimissioni dal KGB 20 ago 1991 (golpe); 8) Comitato Relazioni Esterne 1991-94 (investimenti, casino', banca Rossiya); 9) scandalo materie prime-contro-cibo, commissione Salye 1992; 10) primo vicesindaco 1994 e allegazioni criminalita' organizzata (Tambov, SPAG).</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: tutti i fatti biografici e di carriera (Giurisprudenza; KGB e scuola 401; Istituto Andropov e 'Platov'; Dresda/Angelikastrasse/Boehm/medaglia 1988; folla e documenti bruciati; riserva attiva/Molchanov; capo KVS giu 1991; dimissioni 20 ago 1991; primo vicesindaco 1994; esportazioni &gt;100 mln per cibo). Fonti: Britannica, Wikipedia, Moscow Times, Russia Beyond, Wilson Center, Bloomberg, RFE/RL, TBIJ, Havighurst Center, Dawisha, Applebaum.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Livello B/C e cautele: fascicolo KGB 'solida B' (autovalutazione del servizio); tessera Stasi = agevolazione d'accesso, NON appartenenza; pistola a Dresda = solo documentario 2009 (C); commissione Salye 1992 = difetto di controllo, non corruzione personale, nessun procedimento (B, fragilita'); casino'/Neva Chance, capitalizzazione di Bank Rossiya via casino', banda di Tambov, Ozero, SPAG (indagine BND) = ricostruzioni giornalistiche/storiografiche al grado dell'INDAGINE (C), mai condanna di Putin. INCROCI: radice biografica del nodo triangolato (voce 27) e della verifica (voce 28). Approccio fattualmente documentato; fonte ufficiale bilanciata; vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>APPROFONDIMENTO CERTIFICATO. Domini: D2, D3, D6.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_PUTIN_1970_1994_DIECI_BLOCCHI.docx + repertorio/ITALIA_NERA_PUTIN_1970_1994_DIECI_BLOCCHI.xlsx</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1773,6 +1773,51 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>PUTIN - VENTI BLOCCHI ULTERIORI dai soli URL del corpus e dagli Archivi online in lista</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio (URL_CENSITI + ARCHIVI_OPERATIVO)</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>vincolo di metodo: solo domini gia' in URL_CENSITI (oltre mille) e archivi elencati in ARCHIVI_OPERATIVO. PARTE A (rilettura archivistica): A1 fascicolo KGB (archivio di Stato SPb); A2 fondi Stasi del Bundesarchiv (corrispondenza 1984-90, squadra di 10-15); A3 tessera Stasi 1986 (nessuna prova di appartenenza); A4 episodio marzo 1989 (telefono all'informatore); A5 medaglia NVA feb 1988; A6 'guerra segreta per la Germania' (NSArchive); A7 recensione CIA di Belton 'Putin's People'; A8 'Mosca tace' nell'Office of the Historian; A9 Trattato Due-piu'-Quattro (12 set 1990, NSArchive/Wilson); A10 vertice di Malta (Wilson); A11 documenti Salye (Havighurst/Miami); A12 licenze/Gaidar/100 mln (TBIJ, RFE/RL, openDemocracy). PARTE B (estensione via corpus): B13 Bank Rossiya/SPAG; B14 Ozero/Tambov; B15 caduta Sobchak e Mosca 1996 (kremlin.ru); B16 Direzione controllo 1997; B17 direttore FSB 1998; B18 premier/ad interim 1999-2000; B19 pivot Yukos; B20 gas + guerra cognitiva fino all'Italia.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: fondi Stasi (Bundesarchiv); Trattato Due-piu'-Quattro e vertice di Malta (NSArchive/Wilson); cronologia crollo URSS (Office of the Historian); medaglia 1988; episodio marzo 1989; licenze/100 mln; caduta Sobchak, Direzione controllo, FSB, premier/presidenza (kremlin.ru/Britannica); nodo Yukos e gas (repertorio). Archivi in lista usati: Bundesarchiv-Stasi, NSArchive, CIA readingroom, history.state.gov, Wilson Center.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Livello B/C: fascicolo KGB 'solida B'; 'guerra segreta' CIA e recensione CSI = contesto/storiografia (non nessi diretti); tessera Stasi = lasciapassare, non appartenenza (precisazione autorita' d'archivio); Salye = difetto di controllo, non corruzione personale (fragilita'); Bank Rossiya/SPAG, Ozero/Tambov = INDAGINE (arancio), nessuna condanna di Putin. VINCOLO FONTI: solo corpus; Grokipedia e 'il manifesto', pur presenti in URL_CENSITI, NON usati. INCROCI: voci 27-29 (triangolazione, verifica, dieci blocchi).</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>APPROFONDIMENTO ARCHIVISTICO CERTIFICATO. Domini: D2, D3, D6.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_PUTIN_VENTI_BLOCCHI_ARCHIVI.docx + repertorio/ITALIA_NERA_PUTIN_VENTI_BLOCCHI_ARCHIVI.xlsx</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1818,6 +1818,51 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE INTEGRALE - Vladimir Putin contro tutto il corpus, per dominio</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio (intero corpus della sessione)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>rieffettua la triangolazione del nodo-hub sull'intero corpus, disponendo 28 nodi per i dieci Domini di Potere + la radice biografica, con 13 archi maestri e 10 reperti negativi. RADICE: spina 1952-2000 (voci 28-30). CUORE DURO (D6): EUB-&gt;BoNY-&gt;MENATEP/Yukos/lodo Aja; Ozero/Bank Rossiya; Gazprom/RosUkrEnergo/tagli gas. D8+D2: IRA/Doppelganger/Tenet + Lombardia-Russia/Metropol/accordo Lega + invasione Ucraina. D1: Tambov/Kumarin e Mogilevich (cerniera). D7/D10: filiera eurasiatista Thiriart-&gt;Murelli-&gt;Dugin-&gt;Malofeev (genealogia). D9: repressione (Navalny, Dossier Center).</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: radice biografica; catena finanza EUB-BoNY-MENATEP/Yukos; Bank Rossiya (sanzioni 2014); Gazprom/tagli gas; IRA/Doppelganger; Metropol (esistenza) e accordo Lega-Russia Unita; invasione Ucraina; persecuzione oppositori. Cornice D3: KGB/FSB, siloviki, Ozero.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Reperti negativi maestri: GALASSIA AGINTER/APARTHEID non converge (antipodo atlantista; solo eco di metodo); TERZA POSIZIONE distinta; LOGGIA P2 non converge (rete italo-argentina di altra epoca; analogia di forma, non nesso); Thiriart-&gt;Dugin = genealogia non comando; Metropol negoziazione non reato; Salye difetto di controllo non corruzione; Bank Rossiya via casino'/SPAG/Tambov/Ozero = indagine; 'portafoglio'/Roldugin = allegazione; Khodorkovsky persecuzione accertata ma fortuna contestata. INCROCI: voci 25-30 (Aginter, arco russo, biografia). Vincolo fonti rispettato.</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE INTEGRALE CERTIFICATA. Domini: D1, D2, D3, D4, D6, D7, D8, D9, D10 + radice biografica.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_TRIANGOLAZIONE_INTEGRALE_PUTIN.docx + repertorio/ITALIA_NERA_TRIANGOLAZIONE_INTEGRALE_PUTIN.xlsx</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1863,6 +1863,51 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>PRIMA TRIANGOLAZIONE Putin e la GALASSIA NERA (Aginter, Sudafrica, Brighton Beach, Sud America, estrema destra, nazi-fascismo)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio (schede e documentazioni caricate e generate)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>triangola Putin con i temi neri del corpus. UN SOLO PONTE REALE E DOCUMENTATO, non ideologico ma criminale-finanziario-energetico: Brighton Beach -&gt; Ivankov (Solntsevskaya) -&gt; Mogilevich (FBI most wanted; pago' un giudice per Ivankov nel 1991) -&gt; riciclaggio Bank of New York (YBM Magnex/Benex, 1998-99, miliardi) -&gt; RosUkrEnergo/Firtash (cablogramma 2010: 'partito con l'aiuto di Mogilevich') -&gt; Gazprom. Secondo ponte: estrema destra come GENEALOGIA (Thiriart-&gt;Murelli/Orion-&gt;Dugin-&gt;Malofeev/Komov/Lombardia-Russia). Terzo filo: ECO DI METODO (strategia della tensione di Aginter -&gt; guerra cognitiva).</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: schema di riciclaggio Bank of New York (miliardi; condanne 2000). Livello B: Brighton Beach/Ivankov/Mogilevich (atti giudiziari/FBI); RosUkrEnergo/Firtash-Mogilevich (cablogramma 2010); convergenza sistemica crimine-finanza-gas con lo Stato-cerchia; genealogia eurasiatista; eco di metodo; strumentalizzazione odierna del nazi-fascismo (Movimento Imperiale Russo, terrorista USA 2020).</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>GRANDE CAMPO NEGATIVO (assenza di riscontro): Aginter Press (atlantista, sciolta 1974); Sudafrica apartheid (assi occidentali; il solo filo sovietico e' il CONTROCAMPO che armava l'ANC, epoca pre-Putin, lato opposto); Sud America neofascista (Condor, Delle Chiaie, Garcia Meza, CAL, Stroessner = Guerra Fredda); diaspora nazista storica (Skorzeny, Paladin, von Leers, ratlines = Guerra Fredda occidentale). CAUTELA: il ponte di Brighton Beach e' CONVERGENZA SISTEMICA, NON comando personale provato di Putin su Mogilevich; Thiriart-&gt;Dugin = genealogia non comando; nazi-fascismo odierno = inversione, non continuita'. INCROCI: voci 25-31. Vincolo fonti rispettato.</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE FOCALIZZATA CERTIFICATA. Domini: D1, D6, D7, D8, D10.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_TRIANGOLAZIONE_PUTIN_GALASSIA_NERA.docx + repertorio/ITALIA_NERA_TRIANGOLAZIONE_PUTIN_GALASSIA_NERA.xlsx</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1908,6 +1908,51 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE 5 FAMIGLIE (Censimento Criminalita') - mafia russa di Brighton Beach - Putin</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio (nodi D1 dal Censimento + arco eurasiatico)</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>triangola le Cinque Famiglie di Cosa Nostra USA (Genovese, Gambino, Lucchese, Bonanno, Colombo; dal Censimento globale della criminalita') con l'arco che arriva a Putin. NESSO DOCUMENTATO: lo schema della benzina degli anni Ottanta - Agron (Leningrado) e Balagula (associato di Lucchese e Colombo) con le 'burn companies' (~150 mln di carburante/mese); le Cinque Famiglie imposero il 'Family tax' di 2 centesimi/gallone (maggiore introito dopo la droga); Colombo (Franzese/Sciortino), Lucchese (mediazione Furnari), Genovese (ramo Galizia). CERNIERA RUSSA: da Balagula la regia passa a Ivankov (Solntsevskaya) e Mogilevich -&gt; riciclaggio Bank of New York -&gt; RosUkrEnergo/Firtash -&gt; Gazprom -&gt; orbita statale.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: schema della benzina e 'Family tax' (RICO, testimonianze Franzese); Balagula associato di Lucchese/Colombo; riciclaggio Bank of New York. Livello B: subentro Ivankov/Mogilevich; RosUkrEnergo/Firtash-Mogilevich (cablogramma 2010); convergenza sistemica gas-Stato.</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>REPERTO NEGATIVO CENTRALE: le Cinque Famiglie NON convergono direttamente su Putin - ne sono separate da DUE CERNIERE (1. mafia russa di Brighton Beach; 2. complesso crimine-finanza-gas su Mogilevich); e neppure la catena russa risale a un comando personale di Putin (convergenza di milieu, non ordine). Cosa Nostra italiana e mafia russa = 'alleanza scomoda' (tributo/coordinamento, non fusione); il 'Family tax' e' crimine di strada anni Ottanta, precedente all'era Putin. ASSE LATERALE distinto: Gambino-'ndrangheta (Ursino, New Bridge), italo-italiano, estraneo alla catena russa. Mafie del Censimento tenute distinte. INCROCI: nodi D1 (Censimento); note 9 e 14; voce 32. Vincolo fonti rispettato.</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE CERTIFICATA. Domini: D1, D6, D2.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_TRIANGOLAZIONE_5FAMIGLIE_PUTIN.docx + repertorio/ITALIA_NERA_TRIANGOLAZIONE_5FAMIGLIE_PUTIN.xlsx</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1953,6 +1953,51 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE El Caribe / Cohen / Fred Christ Trump / Donald J Trump con Cinque Famiglie e Brighton Beach</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio (registro principale + nodi D1 Censimento)</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>34 blocchi mirati sulle 4 keyword, incrociati con le triangolazioni precedenti. EL CARIBE: club di Mill Basin dello zio di Cohen (Morton Levine; Levine mai incriminato), ritrovo di Agron/Balagula/Nayfeld = cerniera fisica col milieu di Brighton Beach. COHEN: suocero Fima Shusterman (colpevole 1993, frode fiscale taxi); condanna 2018 (finanziamento elettorale, fisco, false dichiarazioni; Trump Tower Moscow con Sater). FRED TRUMP: causa DOJ 1973 (discriminazione razziale; avvocato Roy Cohn); inchiesta NYT 2018 (295 flussi; All County Building Supply). DONALD TRUMP: cerniera Roy Cohn (avvocato di Trump E di Salerno/Genovese e Castellano/Gambino; cemento S&amp;A Concrete della Trump Tower); cerniera Felix Sater (frode titoli 1998 con mafia russa; Bayrock/Trump SoHo); FinCEN Taj Mahal.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: causa DOJ 1973; Shusterman 1993; condanna Cohen 2018; Roy Cohn avvocato di Trump e dei boss Genovese/Gambino; S&amp;A Concrete/Trump Tower; Sater frode 1998 e ruolo Bayrock; FinCEN Taj Mahal; inchiesta NYT 2018 (All County); LOI Trump Tower Moscow. Fonti: DOJ/Clearinghouse, NYT, FinCEN, rapporto Mueller, SDNY, Rolling Stone, City&amp;State, Forward, Seth Hettena.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>REPERTI NEGATIVI: il rapporto Mueller NON stabili' cospirazione/coordinamento penale campagna Trump-Stato russo; i reati di Cohen NON sono condanna 'per la Russia'; Morton Levine mai incriminato; schemi fiscali di Fred Trump documentati (NYT) ma non giudicati penalmente (prescrizione); 'Trump agente di Putin' = tesi giornalistica (Unger), non accertamento; Bayrock-riciclaggio = allegazione civile. DUE CERNIERE DOCUMENTATE: Roy Cohn (lato italiano, verso le Cinque Famiglie) e Felix Sater (lato russo, verso la finanza mafiosa e Mosca); milieu di Brooklyn (El Caribe) sovrapposto a Brighton Beach - ma NESSUNA catena penale accertata fino a Putin. Statuto massimo su persone viventi. INCROCI: registro principale; nodi D1 (Censimento); voci 32-33. Vincolo fonti rispettato.</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE CERTIFICATA (persone viventi - massimo rigore). Domini: D1, D6, D2.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>ITALIA_NERA_TRIANGOLAZIONE_ELCARIBE_COHEN_TRUMP.docx + repertorio/ITALIA_NERA_TRIANGOLAZIONE_ELCARIBE_COHEN_TRUMP.xlsx</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1998,6 +1998,51 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>ARMI E BOSSOLI DEL CASO MORO (via Fani 16.3.1978 + omicidio 9.5.1978) - 20 blocchi di ricerca mirati, Excel di servizio</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>repertorio (foglio di servizio balistico)</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>VIA FANI: 91 bossoli cal. 9 Parabellum repertati (93 colpi sparati per la Scientifica, di cui 2 di Iozzino; 87 bossoli in esami successivi - discrepanza dichiarata). Ripartizione perizia 1978 (Ugolini-Jadevito-Lopez): 49 (FNAB-43 o Sten) + 22 (seconda FNAB-43) + 5 (TZ-45) + 3 (Beretta M12) + 8 (pistola S&amp;W cal.9) + 4 (Beretta mod.51) = 91. Fucilieri (memoriali): Morucci e Bonisoli (FNAB-43), Fiore (M12, inceppata), Gallinari (TZ-45); piu' inceppamenti; unica reazione: Iozzino, 2 colpi. Munizioni G.F.L. 9M38 (Fiocchi); 30 bossoli su 87 SENZA anno di fabbricazione. 9 MAGGIO: Walther PPK 9 corto con silenziatore (inceppata) + Skorpion vz.61 7,65 (raffica di 11 colpi, varianti 9/12); esecutore Moretti; Renault 4 rossa targa Roma N57686.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: ripartizione della perizia 1978; 91 bossoli; esiti Salza-Benedetti (il 'super-killer' dei 49 colpi NON confermato; solo 6 a segno); marchio GFL 9M38 e cartucce senza data; armi del 9 maggio; sequestro della Skorpion in via Dogali (15.6.1988) e catena balistica Tarantelli-Conti-Ruffilli.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Fragilita' e ipotesi dichiarate: discrepanza 87/91/93; arma NON identificata (Comm. Moro 2: nessun proiettile 9 Para dalle armi sequestrate); interpretazione delle cartucce senza data (forniture non convenzionali/export) = ipotesi peritale, replicata da Fiocchi; identita' Skorpion via Dogali = arma di Moro (B) e nesso Acca Larentia (B); provenienza Skorpion: Jimmy Fontana, Sanremo feb. 1971, ceduta 1977, passaggio alle BR MAI chiarito (C); numero esatto bossoli 7,65/9 corto di via Caetani: da atti (C); provenienza armi lunghe BR non accertata. INCROCI: registro-madre D7; note sulla strategia della tensione. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>RICOGNIZIONE BALISTICA CERTIFICATA (con discrepanze dichiarate). Domini: D7, D3.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>repertorio/ITALIA_NERA_MORO_ARMI_E_BOSSOLI.xlsx (Excel di servizio, 6 fogli)</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2043,51 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>ARMI E BOSSOLI USATI DIRETTAMENTE SU ALDO MORO NELL'ESECUZIONE (9 maggio 1978) - perimetro ristretto: SOLO il covo/garage, ESCLUSO il rapimento di via Fani</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>repertorio (foglio di servizio balistico - esecuzione)</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>DUE ARMI sul corpo: (uno) Walther PPK cal. 9 corto (9x17 / .380 ACP), con silenziatore, esploso il primo colpo e subito INCEPPATA (uno-due colpi), MAI ritrovata; (due) mitra cecoslovacco Skorpion vz.61 cal. 7,65 Browning (.32 ACP), con silenziatore, raffica di undici colpi (varianti in perizia dieci/dodici). Esecutore materiale indicato: Mario Moretti. ESITO SUL CORPO: undici fori d'ingresso al torace (perizia necroscopica; perizie successive parlano di piu' colpi); otto proiettili ritenuti nel corpo, solo tre fuoriusciti. Corpo nel bagagliaio di una Renault 4 rossa targata Roma N57686, via Michelangelo Caetani. Il garage/box: via Camillo Montalcini. RIS Parma 2017: Moro colpito di fronte e in posizione eretta o semi-eretta, non rannicchiato nel bagagliaio come da versione BR.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: le due armi (Walther PPK 9 corto inceppata + Skorpion 7,65); il silenziatore; la Renault 4 e la targa; via Caetani e via Montalcini; il sequestro della Skorpion in via Dogali (15.6.1988) con la catena balistica che la lega ai colpi su Moro; la rilettura RIS 2017. Livello B: numero dei colpi Skorpion (undici, con varianti dieci/dodici a seconda della perizia); attribuzione a Moretti come esecutore.</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Fragilita' e ipotesi dichiarate: NUMERO ESATTO DEI BOSSOLI per calibro (7,65 Browning e 9 corto) raccolti nel covo/garage = DA VERIFICARE sugli atti processuali (C) - la Walther si inceppa dopo il primo colpo, quindi i bossoli 9 corto sono pochissimi; discrepanza undici/dodici colpi tra perizia necroscopica e perizie successive; la Walther PPK non fu MAI ritrovata (arma non periziabile fisicamente); provenienza e passaggio della Skorpion alle BR non pienamente chiariti (C). PERIMETRO DICHIARATO: questa voce isola i colpi/bossoli dell'ESECUZIONE (garage, sul corpo) ed ESCLUDE i novantuno bossoli cal. 9 Parabellum di via Fani (rapimento, gia' alla voce trentacinque). INCROCI: voce trentacinque (quadro completo Moro); registro-madre D7. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>RICOGNIZIONE BALISTICA DELL'ESECUZIONE CERTIFICATA (perimetro ristretto, con discrepanze dichiarate). Domini: D7, D3.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>repertorio/ITALIA_NERA_MORO_ESECUZIONE_ARMI_E_BOSSOLI.xlsx (Excel di servizio, 6 fogli)</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -31,7 +31,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +53,11 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -66,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -78,6 +83,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -445,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2088,6 +2096,51 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>RICOGNIZIONE: omicidi in Italia FINO AL 1977 con Walther PPK calibro 9 corto (escluso il caso Moro) - dieci blocchi di ricerca, esito negativo dichiarato</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>repertorio (foglio di servizio balistico - ricognizione)</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>ESITO CENTRALE (REPERTO NEGATIVO): nessun omicidio in Italia fino al 1977 risulta attribuito, nelle fonti aperte consultate, a una Walther PPK cal. 9 corto. Casi esaminati con arma accertata: Calabresi 1972 (S&amp;W .38), Mantakas 1975 (.38 fatale / 7,65 rinvenuta), Alcamo Marina 1976 (cal. 9 'militare' matricola abrasa), Occorsio 1976 (mitraglietta 9 Para), Casalegno 1977 (Nagant 7,62, lo stesso di Croce), Walter Rossi 1977 (Beretta M34 cal. 9 CORTO matricola abrasa CON ATTACCO SILENZIATORE, mai ritrovata). Pedenovi 1976 e Ciotta 1977: calibro non specificato nelle fonti aperte. Contesto: in Italia il 9 corto e' il calibro della Beretta M34 d'ordinanza (PS/CC/GdF), non della PPK.</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: armi accertate dei singoli casi (Calabresi, Casalegno/Croce, Occorsio, Alcamo Marina); il quadro del 9 corto italiano (M34 d'ordinanza, soglia civile). Livello B: Beretta M34 9 corto con attacco silenziatore per Walter Rossi (inchiesta e atti di parte, procedimento archiviato).</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Fragilita' dichiarate: reperto negativo, NON prova d'inesistenza (perizie d'epoca non integralmente digitalizzate; calibri di Pedenovi e Ciotta non reperiti in rete = giallo); la PPK di Moro MAI ritrovata, quindi nessuna comparazione balistica con delitti precedenti fu mai possibile (limite strutturale della prova, arancio). NON-INFERENZA dichiarata: il parallelo tipologico col caso Walter Rossi (9 corto + silenziatore + arma sparita, Roma, otto mesi prima di via Montalcini) registra una convergenza di tipologia, NON un'identita' d'arma ne' un ponte tra i due fatti. Direzione d'archivio: perizie balistiche originali e casellario balistico storico PS/CC (C). INCROCI: voci 35-36 (balistica Moro). Vincolo fonti rispettato (no Grokipedia, no il manifesto). Ricerca a finalita' difensiva/storiografica.</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>RICOGNIZIONE CON ESITO NEGATIVO DICHIARATO (assenza di riscontro registrata come risultato). Domini: D7, D3.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>repertorio/ITALIA_NERA_WALTHER_PPK_PRE1978_RICOGNIZIONE.xlsx (Excel di servizio, 5 fogli)</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2141,6 +2141,51 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>RICOGNIZIONE: omicidi in Italia FINO AL 1977 con Beretta M34 calibro 9 corto (escluso il caso Moro) - undici blocchi di ricerca, esito parziale - gemella della voce 37 (Walther PPK)</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>repertorio (foglio di servizio balistico - ricognizione)</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>ESITO PARZIALE: UN caso positivo probabile - omicidio di WALTER ROSSI (Roma, 30.9.1977): Beretta M34 cal. 9 corto, matricola abrasa, ATTACCO PER SILENZIATORE, mai ritrovata (Alibrandi/Fioravanti, FdG/futuri NAR; procedimento archiviato). TRE candidati 'd'ordinanza' con modello non accertato: Lorusso 1977 (Beretta cal. 9 del carabiniere Tramontani, proiettile mai comparabile), Alcamo Marina 1976 (cal. 9 'militare' matricola abrasa, caso Gulotta), Mantini 1975 (colpo ravvicinato d'ordinanza, Tuzzolino). NEGATIVI con arma accertata diversa: Calabresi (S&amp;W .38), Spampinato (S&amp;W), Campanile (due 7,65), Occorsio (9 Para), Masi (.22 blindato), Casalegno/Croce (Nagant 7,62), Reggio Emilia 1960 (mitra e moschetti). Non modellizzati in rete: Cavallero 1967, Di Rosa 1976, Dalmine 1977.</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: quadro d'ordinanza della M34 (Regio Esercito/EI/CC; PS fino ai primi anni Sessanta; GdF fino agli anni Novanta); armi accertate dei casi negativi. Livello B: M34 di Walter Rossi (fonte d'inchiesta e atti di parte - l'arma non fu mai sequestrata ne' periziata, quindi il grado NON sale ad A). Nota extra-perimetro: Gandhi 1948 (l'omicidio piu' celebre con M34, fuori Italia).</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Fragilita' dichiarate: fascia 'd'ordinanza' (Mantini/Alcamo/Lorusso) con modello non negli atti pubblici e comparazione balistica mancata in tutti e tre i casi - stessa fragilita' strutturale della PPK di Moro (voce 37); calibri non modellizzati in rete per Cavallero, Pedenovi, Ciotta, Di Rosa, Dalmine (chiudibili solo in archivio, C). PONTE dichiarato con la voce 37: Walter Rossi e' insieme il positivo della M34 e l'unica adiacenza tipologica della PPK di via Montalcini (9 corto + silenziatore + arma sparita, stessa citta', otto mesi prima) - convergenza di tipologia, NON identita' d'arma. INCROCI: voci 35-37. Vincolo fonti rispettato (no Grokipedia, no il manifesto). Ricerca a finalita' difensiva/storiografica.</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>RICOGNIZIONE CON ESITO PARZIALE (un positivo probabile, tre candidati, resto negativo). Domini: D7, D3.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>repertorio/ITALIA_NERA_BERETTA_M34_PRE1978_RICOGNIZIONE.xlsx (Excel di servizio, 5 fogli)</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2186,6 +2186,51 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>RICOGNIZIONE: omicidi in Italia DAL 1978 IN POI con Walther PPK calibro 9 corto - nove blocchi di ricerca - terza ricognizione della serie balistica (chiude il trittico con le voci 37-38)</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>repertorio (foglio di servizio balistico - ricognizione)</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>ESITO: l'UNICO omicidio italiano dal 1978 in poi attribuito a una Walther PPK cal. 9 corto resta l'esecuzione di ALDO MORO (9.5.1978, caso ancora, gia' voci 35-36). Oltre Moro: NESSUN altro caso nelle fonti aperte. CANDIDATO D'IDENTITA' (C): nel covo BR di via Silvani fu sequestrata una PPK/S nata 7,65 e RICALIBRATA 9 corto, matricola abrasa riemersa con acidi che danneggiarono la rigatura (reperto 47/18) - candidata come arma di via Montalcini secondo la ricostruzione Cucchiarelli, MAI verificata balisticamente ('mai riconosciuta' anziche' 'mai ritrovata'). NEGATIVI accertati: Acca Larentia (7,65/Skorpion), Fausto e Iaio (Beretta 34 ricalibrata 7,65 CON SILENZIATORE, proiettili spariti, indagini riaperte), Pecorelli (7,65 Gevelot), Mattarella (.38 Special/Colt Cobra), Amato (revolver), Gucci 1995 (7,65 con silenziatore artigianale). Tobagi: calibro non modellizzato (giallo).</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Livello A: armi accertate dei casi negativi; il caso ancora Moro. Livello B: quadro Fausto e Iaio (perizia citata da fonti aperte; proiettili spariti). CONCLUSIONE DEL TRITTICO (voci 37-38-39): il 9 corto italiano e' territorio della Beretta M34; la Walther PPK non ha scia ne' prima ne' dopo Moro - l'arma dell'esecuzione e' un UNICUM balistico nella storia italiana, il che rende provenienza e sparizione ancora piu' significative.</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Fragilita' dichiarate: candidato via Silvani = ricostruzione di parte su atti, mai verificata (C); calibro Tobagi non reperito in rete (giallo); indagini Fausto e Iaio riaperte (2025) con ricerca di collegamenti balistici col caso Pecorelli - quadro in evoluzione. Non-inferenza: le adiacenze del silenziatore (Fausto e Iaio, Gucci) restano convergenze di tipologia, nessun ponte balistico accertato con la PPK di Moro. INCROCI: voci 35-38. Vincolo fonti rispettato (no Grokipedia, no il manifesto). Ricerca a finalita' difensiva/storiografica.</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>RICOGNIZIONE CON ESITO NEGATIVO OLTRE L'ANCORA (unico caso: Moro). Domini: D7, D3.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>repertorio/ITALIA_NERA_WALTHER_PPK_POST1978_RICOGNIZIONE.xlsx (Excel di servizio, 5 fogli)</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2231,6 +2231,51 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>ARSENALE SARDO delle Brigate Rosse (Lula, Monte Albo-Monte Pitzinnu, febbraio 1982) - ricognizione delle armi e TRIANGOLAZIONE con il corpus (canale OLP, lodo Moro, Hyperion, Barbagia Rossa)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>repertorio (foglio di servizio - ricognizione e triangolazione)</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>FATTO (A): 23-27.2.1982, campagne di Lula (NU) tra Monte Albo e Monte Pitzinnu: deposito BR scoperto su indicazione del pentito Savasta; custodia di Barbagia Rossa; possibile destinazione l'assalto a Badu 'e Carros (B). INVENTARIO di fonte sarda: cinque razzi per bazooka USA, UN missile anticarro sovietico, due missili ARIA-TERRA francesi, trenta chili di plastico, otto bombe a mano USA, sei mitra Sterling inglesi, un centinaio di cartucce. Discrepanze del paragrafo circolante in inglese dichiarate (plurali amplificati, 'aria-aria', 'centinaia'). FILIERA (A): viaggio del Papago (Moretti, agosto 1979, Numana-Cipro-Libano) e consegne OLP su spiagge venete (settembre 1979: Sterling, lanciarazzi, esplosivi); incriminati da Mastelloni Abu Ayad e Abu Jihad; retroterra del lodo Moro (B).</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE: (1) doppio canale degli armamenti BR - Skorpion di Moro dal mercato interno (Sanremo 1971, voce 35), arsenale di Lula dal canale OLP: due filiere parallele che si confermano; (2) fronte carcerario: colonna sarda nata per Asinara/Badu 'e Carros; (3) lodo Moro = quadro mediterraneo gia' censito nel corpus; (4) Hyperion/Superclan come snodo ambiguo alla maniera di Aginter (paragone METODOLOGICO); (5) il catalogo 'internazionalista' delle armi dimostra il bazar OLP, NON una regia sovietica.</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Fragilita' dichiarate: filone Hyperion chiuso con PROSCIOGLIMENTO GENERALE 1990 (imputati anche i generali Lugaresi, Notarnicola, Grassini) - incriminato NON e' condannato, resta allegazione istruttoria (C); tesi della catena di comando Mosca-BR = tesi pubblicistica alla Claire Sterling, mai accertata (C); identita' pezzo-per-pezzo carico Papago-arsenale Lula non cristallizzata in sentenza (B); pista sarda-bolognese del 'passaporto di Aritzo' = C; eco di metodo coi depositi Nasco/Gladio senza equivalenza. Convergenza di milieu diverso da catena di comando. INCROCI: voci 35-36-39 (balistica Moro), registri D7 e mediorientali. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>RICOGNIZIONE E TRIANGOLAZIONE CERTIFICATE (con proscioglimenti e tesi di parte dichiarati). Domini: D7, D3.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>repertorio/ITALIA_NERA_ARSENALE_SARDO_TRIANGOLAZIONE.xlsx (Excel di servizio, 6 fogli)</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2276,6 +2276,51 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE NASCO di Gladio + catena della Skorpion (due testi ricevuti) con il corpus - verifica preliminare dei testi e doppio aggancio (voci 35-36, 39-40, strategia della tensione)</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica + repertorio (verifica di testi ricevuti e triangolazione)</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>NASCO (impianto CONFERMATO): 139 depositi e 622 gladiatori (dati Andreotti 1990); protocollo SIFAR-CIA 26.11.1956 (De Lorenzo); CAG di Capo Marrargiu; scoperta casuale di Aurisina (24.2.1972) e recupero 1972-73 di 127 NASCO su 139 - DODICI mai recuperati; Peteano a pochi km tre mesi dopo, sospetto Casson su esplosivo/detonatore (istruttorio, mai in sentenza); Serravalle imputato di falso su Aurisina. SKORPION (testo CORRETTO in tre punti): DUE armi distinte, non una - la Skorpion di Morucci (Roma 1979) indicata dalle perizie come arma di Moro, e la ex Jimmy Fontana (Sanremo 1971) sequestrata in VIA DOGALI (Milano, 15-18.6.1988, non 'via Griffini/ottobre') e legata ad Acca Larentia 1978, Tarantelli 1985, Conti 1986, Ruffilli 1988; 'matricola 5075' NON riscontrata; Palma, Tartaglione e Hunt promossi indebitamente a Skorpion (arma non modellizzata: C).</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE: (1) specularita' dei depositi - NASCO di Gladio vs arsenale BR di Lula (voce 40): stessa tecnica, finalita' opposte, Sardegna su entrambi i fronti (Capo Marrargiu / Lula); eco di metodo formalizzato; (2) doppio canale armamenti BR confermato: nessuna delle due Skorpion proviene dai NASCO - il sospetto 'armi NATO alle BR' resta senza riscontro in questa catena; (3) Peteano come cerniera giudiziaria: dal processo Casson alla rivelazione di Gladio (1990); (4) la Skorpion di via Dogali attraversa i fronti opposti (Acca Larentia MSI - omicidi BR-PCC): il singolo reperto che meglio dimostra la circolarita' del mercato nero delle armi; (5) ipotesi FARL su Hunt = quadro mediterraneo del lodo Moro (C).</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Fragilita' e correzioni dichiarate: la voce 35 registrava in B l'identita' 'Skorpion via Dogali = arma di Moro' - questa triangolazione la DECLASSA a favore della ricostruzione a due armi (perizie d'archivio unica via di chiusura); tesi 'esplosivi NASCO nelle stragi' = C senza promozione (i dodici NASCO mancanti sono dato aperto, non prova); Rocca: morte archiviata come suicidio, tesi omicidio = C; attribuzioni Marras/de Lellis/Polgar e dettagli (radio 'Angora', prede belliche, sommergibili) = C non riscontrati; errori materiali dei testi corretti (via Montalcini, via Dogali, date recupero NASCO). Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE CERTIFICATA CON VERIFICA PRELIMINARE DEI TESTI (correzioni e declassamenti dichiarati). Domini: D7, D3, D4.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>repertorio/ITALIA_NERA_NASCO_SKORPION_TRIANGOLAZIONE.xlsx (Excel di servizio, 7 fogli)</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2321,6 +2321,51 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>CENSIMENTO CAPILLARE: i 139 NASCO di Gladio (mappa regionale e dotazioni), nove arsenali/covi BR con inventari, 'arsenali del Superclan' (esito: assenza dichiarata)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>repertorio (censimento dei tre sistemi di arsenali clandestini)</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>NASCO (A): mappa regionale completa - FVG cento, Lombardia undici, Veneto sette, Piemonte sette, Trentino cinque, Liguria quattro, Emilia-Romagna due, Puglia due, Campania uno = 139; interrati dal 1963; recupero post-Aurisina chiuso nel 1973: 127 recuperati, DODICI mai recuperati, di cui due localizzati in rete (cappella del cimitero di Mariano del Friuli: 2 contenitori metallici + 3 plastica; Santa Petronilla di San Vito al Tagliamento: 2+2); dotazione tipo da atti (armi portatili, munizioni, esplosivi, bombe a mano, fucili di precisione, radio). ARSENALI BR (nove siti censiti con inventario): Robbiano di Mediglia 1974, Cascina Spiotta 1975, via Gradoli 1978 (Sten, Reck, Beretta 6,35/1941, cal.22 950, fucile a pompa USA, 17 candelotti dinamite, 75 detonatori), via Monte Nevoso 1978 (cinque armi corte, 770 g polvere da mina, due bombe a mano + doppio fondo 1990 con fucile e 40 detonatori), viale Giulio Cesare 1979 (arsenale Morucci con la Skorpion di Moro), via Fracchia 1980 (cinque pistole, DUE STERLING, fucile Franchi, 2000 cartucce, DUE ENERGA, due mine anticarro, plastico), via Silvani 1980 (PPK/S 47/18), Lula 1982 (voce 40), via Dogali 1988 (Skorpion ex Fontana).</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>SUPERCLAN: NESSUN arsenale fisico mai sequestrato o censito - solo presunta INTERMEDIAZIONE di armi OLP (Galati, Savasta; incriminazioni Mastelloni 1982) con proscioglimento 1990: il Superclan non aggiunge siti alla mappa, aggiunge (in ipotesi mai giudicata) una regia sul flusso. INCROCIO CENTRALE: Sterling ed Energa compaiono sia in via Fracchia sia a Lula = la tipologia del canale OLP si distribuisce su colonne del nord e deposito sardo. NASCO e BR: nessun travaso accertato tra le due filiere.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Limiti dichiarati: elenco integrale dei 139 NASCO con distinte di carico negli atti (Commissione stragi/doc. Andreotti), non in rete - qui mappa regionale e due dei dodici irrisolti; inventari di Robbiano e Cascina Spiotta non modellizzati in rete (giallo); censimento BR = covi-arsenale maggiori documentati, non le basi minori; tracciabilita' pezzo-per-pezzo del canale OLP solo dagli atti (C). INCROCI: voci 39-41. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>CENSIMENTO CERTIFICATO CON LACUNE D'ARCHIVIO DICHIARATE. Domini: D7, D3, D4.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>repertorio/ITALIA_NERA_CENSIMENTO_NASCO_ARSENALI_BR_SUPERCLAN.xlsx (Excel di servizio, 7 fogli)</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2366,6 +2366,51 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>CENSIMENTO ARSENALI del fronte nero-criminale romano: NAR, Avanguardia Nazionale, Banda della Magliana (gemello della voce 42)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>repertorio (censimento arsenali - fronte nero-criminale)</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>MAGLIANA (A): arsenale-madre nei sotterranei del MINISTERO DELLA SANITA' (via Franz Liszt 34, EUR), scoperto il 27.11.1981: custode l'usciere Biagio Alesse (un milione di lire al mese, intermediario la guardia giurata Alvaro Pompili); inventario: diciannove pistole/revolver, Beretta M12, MAB 38, Sten, altri mitra, cartucce, bombe a mano, esplosivi, materiale per travisamento. REPERTO-CHIAVE: quattro proiettili GEVELOT dello stesso raro tipo di quelli che uccisero Pecorelli (ponte materiale con la voce 39; assoluzioni definitive di Perugia dichiarate). Arsenale CONDIVISO coi NAR (armi di entrambi). NAR (A): via Alessandria (dic. 1979: undici pistole, granate, esplosivi, divise da carabiniere) - crocevia di servizi e neofascisti legato agli omicidi Amato e Straullu, con ipotesi di depistaggio fino a Bologna (C); Acilia (granate da via Alessandria); via Decio Mure (Vale, giallo). AN: NESSUN arsenale unitario - flusso di armi/esplosivi/timer Roma-Reggio Calabria sotto supervisione Delle Chiaie, istruttore ex OAS in via Michele Amari (aggancio Aginter/OAS del corpus), arsenale-provocazione di Camerino (Fachini-SID, C), archivio segreto Delle Chiaie (2021, cartaceo).</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE: (1) lo Stato come deposito - rovescio speculare dei NASCO (voce 42): la' lo Stato interrava armi nel territorio, qui il crimine interrava armi dentro un ministero; (2) la cerniera nera-criminale (NAR-Magliana) = logistica comune, matrice del Mondo di mezzo; (3) ponte Gevelot-Pecorelli documentato come reperto, non come responsabilita'; (4) l'istruttore OAS = eco diretto delle monografie Aginter del corpus; (5) morfologia comparata: BR arsenali propri, fronte nero arsenali condivisi e flussi senza siti.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Fragilita' dichiarate: assoluzioni definitive nel processo Pecorelli (il reperto resta reperto); Camerino come provocazione = ricostruzione istruttoria (C); nesso via Alessandria-Bologna = C senza promozione; inventari dei depositi minori (Magliana, via Decio Mure) non modellizzati in rete - direzione d'archivio. INCROCI: voci 39, 41, 42; monografie Aginter; registro strategia della tensione. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>CENSIMENTO CERTIFICATO (fronte nero-criminale; assoluzioni e ipotesi dichiarate). Domini: D7, D4, D6.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>repertorio/ITALIA_NERA_ARSENALI_NAR_AN_MAGLIANA.xlsx (Excel di servizio, 7 fogli)</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2411,6 +2411,51 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE TERMINALE A CENTO BLOCCHI: NASCO contro/accanto a tutti gli arsenali censiti (BR, NAR, AN, Magliana, Superclan) + due sistemi nuovi (Rosa dei Venti/NDS, MAR di Fumagalli) + il sistema-radice delle armi partigiane occultate</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>repertorio (matrice di confronto a cento blocchi)</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Mandato ('fare di tutto perche' emerga natura speculare o affine') eseguito come OBBLIGO DI PROFONDITA', non di esito. VERDETTO: (1) SPECULARITA' DI METODO PROVATA (A) - interramento, compartimentazione, custodi fiduciari remunerati, travisamento, patti internazionali segreti (SIFAR-CIA 1956 / BR-OLP 1979), organi ristretti con le mappe; (2) AFFINITA' DI MATERIALE PROVATA (A) - stesso bacino di residuati della guerra civile 1943-45 (Sten, MAB, TZ-45, FNAB-43: quest'ultima da via Fani all'Algeria), stessi standard NATO (Sterling, Energa, 9 Para), stessi plastici e detonatori; (3) AFFINITA' DI RADICE PROVATA (A/B) - tutte le reti discendono dalla guerra civile e dalle sue armi occultate (caso Val di Susa); (4) SPECULARITA' GEOGRAFICA PROVATA (A) - Sardegna (Capo Marrargiu/Lula), Nord-Est (100 NASCO/spiagge OLP), Alpi (Trentino/Valtellina MAR), Roma armeria diffusa, Parigi doppia centrale (CPC/Hyperion); (5) SPECULARITA' DELLE CODE PROVATA (A) - 12 NASCO, PPK di Moro, pistola di Pecorelli, reperti spariti, matricole abrase.</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>NUOVI SISTEMI CENSITI IN CAMPAGNA: Rosa dei Venti/Nuclei per la Difesa dello Stato (dispositivo parallelo dal 1964, atti Tamburino, inchiesta avocata dalla Cassazione 1978) e MAR di Fumagalli (ex partigiani bianchi, Valtellina, esplosivi sequestrati marzo 1974, referenti indicati Sogno/Taviani) = la 'matrioska' delle reti parallele, provata come PLURALITA' (B), non come catena unica. TRAVASO eversione-crimine PROVATO (arsenale condiviso NAR-Magliana). Il chiasmo di sintesi: lo Stato-seminatore (NASCO nel territorio) contro lo Stato-contenitore (la Magliana nel ministero).</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>NON PROVATO E DICHIARATO: travaso fisico Stato-eversione (unico ponte ipotizzato Peteano, istruttorio, C); regia unica dei due fronti (tesi sovietica alla Sterling e tesi dello Stato-stragista integrale: entrambe C). La specularita' e' un fatto morfologico certificato; l'identita' operativa sarebbe una tesi e resta tale. Metodo: cento blocchi alimentati dalle voci 35-43 + campagna nuova (Rosa dei Venti, MAR, residuati, FNAB-43). INCROCI: voci 35-43, monografie Aginter (istruttori OAS), registro strategia della tensione. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE TERMINALE CERTIFICATA (specularita' e affinita' emerse ai gradi dichiarati; identita' non promossa). Domini: D7, D4, D3.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>repertorio/ITALIA_NERA_TRIANGOLAZIONE_CENTO_BLOCCHI_ARSENALI.xlsx (Excel di servizio, 4 fogli, 100 blocchi)</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2456,6 +2456,51 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE della matrice a cento blocchi (voce 44) con i VENTICINQUE CASI PRINCIPALI del corpus - 250 blocchi mirati - Excel + DOCX</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica (DOCX di prosa) + repertorio (Excel a 250 blocchi)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Struttura: 250 blocchi = 25 casi x 10 assi (metodo/logistica, materiale bellico, radice storica, geografia, uomini/custodi/formatori, regia/patti, code irrisolte, esito giudiziario, travaso/cerniera, verdetto del caso). CASI: esecuzione Moro, via Fani, trittico PPK/M34, Arsenale Sardo, NASCO, catena Skorpion, arsenali BR, Superclan/Hyperion, NAR, Avanguardia Nazionale, Magliana, Rosa dei Venti/NDS, MAR Fumagalli, matrice cento blocchi, piazza Fontana, Bologna, piazza della Loggia, Peteano, Aginter/Guerin-Serac, Delle Chiaie/Condor, apartheid Sudafrica-Namibia, Brighton Beach/Bratva, Cinque Famiglie, cluster Trump, Putin. Campagna di ricerca nuova su: esplosivo di Bologna (TNT+T4 da residuato bellico), gelignite di piazza Fontana (timer Junghans-Diehl, candelotti di Trieste-Gorizia), Aginter (60% personale ex OAS), dimensione armiera della Bratva (elicotteri Armata Rossa, Fainberg).</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>VERDETTO TRASVERSALE ai 250 blocchi: la natura SPECULARE e AFFINE dei sistemi e' EMERSA E CERTIFICATA (A) su cinque dimensioni - metodo dell'occultamento, materiale/standard (residuati 1943-45 + NATO), radice nella guerra civile, geografia (Sardegna, Nord-Est, Alpi, Roma, Parigi), simmetria delle code irrisolte (armi mai ritrovate, reperti spariti). Travaso eversione-crimine PROVATO (arsenale condiviso NAR-Magliana). Il vertice Putin: la galassia Aginter/apartheid NON converge sul Cremlino (antipode atlantista); l'unico ponte reale e' la spina euroasiatica del crimine organizzato = convergenza sistemica, non catena di comando personale.</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>NON PROVATO E DICHIARATO: travaso fisico Stato-eversione (unico appiglio Peteano, istruttorio, C); regia unica dei due fronti (tesi sovietica alla Sterling e Stato-stragista integrale: C); Putin-regista (C). La specularita' e' un fatto morfologico certificato; l'identita' operativa resta tesi. Ogni blocco col proprio grado Savona. INCROCI: voci 35-44 e i registri analitici del corpus (Aginter, guerra fredda, Sudafrica-Sudamerica, censimento criminalita', Putin). Vincolo fonti rispettato (no Grokipedia, no il manifesto ne' il manifesto in rete).</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE TERTMINALE CERTIFICATA (250 blocchi; specularita'/affinita' emerse ai gradi dichiarati; identita' e regia unica non promosse). Domini: D7, D4, D3, D1, D2.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica/ITALIA_NERA_TRIANGOLAZIONE_250_BLOCCHI_CORPUS.docx + repertorio/ITALIA_NERA_TRIANGOLAZIONE_250_BLOCCHI_CORPUS.xlsx</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2501,6 +2501,51 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE dei PRIMI VENTICINQUE PERSONAGGI del corpus PER NUMERO DI NODI con l'intero corpus - 250 blocchi mirati - Excel + DOCX</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica (DOCX di prosa) + repertorio (Excel a 250 blocchi)</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>CLASSIFICA (proxy = frequenza di menzione su 95 file, &gt;4 milioni di caratteri; cautela dichiarata su omonimie/locuzioni): 1 Guerin-Serac (615), 2 Delle Chiaie (362), 3 Putin (176), 4 P.W. Botha (115), 5 Skorzeny (114), 6 Kissinger (107), 7 Gelli (101), 8 Aldo Moro (91, gonfiato da 'lodo/commissione Moro'), 9 Dugin (79), 10 Pinochet (75), 11 Vinciguerra (71), 12 Giannettini (68), 13 Klaus Barbie (59), 14 Thiriart (59), 15 Mogilevich (50), 16 Borghese (46), 17 Robert Leroy (38), 18 Vorster (35), 19 Michael Cohen (35), 20 Carminati (33), 21 Andreotti (29), 22 Williamson (29), 23 Khodorkovsky (27), 24 Firtash (25), 25 Kovalchuk (23). STRUTTURA: 250 blocchi = 25 personaggi x 10 assi (dominio, rete, geografia, funzione, cerniera con altri nodi, rapporto Stato/servizi, esito giudiziario, aggancio Putin/euroasia, code irrisolte, verdetto del nodo).</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>VERDETTO TRASVERSALE: il corpus e' BICEFALO. Blocco EGEMONE nero-atlantista (Guerin-Serac, Delle Chiaie, Botha, Skorzeny, Kissinger, Gelli, Pinochet, Vorster, Barbie, Williamson, Leroy, Borghese, Vinciguerra, Giannettini, Carminati, Andreotti) che NON converge su Putin ma ne e' l'ANTIPODE di guerra fredda. Blocco EUROASIATICO (Putin, Dugin, Thiriart, Mogilevich, Firtash, Kovalchuk, Khodorkovsky, Cohen). I due mondi si toccano SOLO in due punti: (a) ponte DOTTRINALE Thiriart-&gt;Dugin; (b) SPINA crimine-energia Mogilevich-Firtash-Kovalchuk. Kovalchuk = aggancio piu' diretto (cerchia Ozero); Khodorkovsky converge IN NEGATIVO (oligarca espulso).</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Fragilita' dichiarate: la classifica e' ordinamento di centralita' (frequenza-proxy), NON conteggio notarile dei nodi - omonimie e locuzioni ('lodo Moro', 'Cohen') dichiarate caso per caso; su viventi (Putin, Cohen, Khodorkovsky, Firtash, Kovalchuk) massimo rigore; tesi 'Putin-regista', influenza Dugin sul Cremlino, caso Palme/Williamson = C. Convergenza sistemica e di milieu certificata; catena di comando unica NON provata. INCROCI: voci 35-45 e i registri analitici dei nodi (Aginter, apartheid, D1 criminalita', sotto-hub russi). Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE DEI NODI-PERSONA CERTIFICATA (250 blocchi; struttura bicefala; convergenza certificata, catena unica non promossa). Domini: D7, D3, D2, D6, D1, D8.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica/ITALIA_NERA_TRIANGOLAZIONE_250_BLOCCHI_PERSONAGGI.docx + repertorio/ITALIA_NERA_TRIANGOLAZIONE_250_BLOCCHI_PERSONAGGI.xlsx</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2546,6 +2546,51 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>REGISTRO ANALITICO DEI NODI - versione INTEGRALE e RINNOVATA: consolidamento di tutti i registri-nodi + i nodi nuovi delle voci 35-46 - Excel + DOCX</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera (DOCX) + repertorio (Excel del registro integrale)</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>260 NODI consolidati per estrazione automatica dai registri-fonte (Aginter/apartheid integrazione+approfondimento, censimento criminalita' D1, integrazione e archi, sotto-hub euroasiatici gas/media/riciclaggio/EUB/Khodorkovsky, hub P2), deduplicazione per nome con unione dei domini, e aggiunta di 30 nodi nuovi dalle voci 35-46 (PPK e Skorpion di Moro, Jimmy Fontana, Walter Rossi, via Silvani; arsenale di Lula, Barbagia Rossa, Papago, lodo Moro; NASCO, Aurisina, Capo Marrargiu; arsenale del Ministero della Sanita', Alesse, via Alessandria; Rosa dei Venti/NDS, Spiazzi, MAR, Fumagalli, FNAB-43; quattro stragi; Brighton Beach, Ivankov, Fainberg, cluster Trump/Cohn/Sater). Distribuzione: D1=67, D7=48, D2=43, D6=34, D3=27, D4=16, D9=12, D10=9, D8=4.</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>STRUTTURA a 5 fogli: quadro; registro integrale (260 nodi con dominio primario, tutti i domini, descrizione, registro di provenienza); indice per dominio con conteggi; dieci grandi hub per centralita' (Guerin-Serac, Delle Chiaie, Putin, Gelli, Botha/Vorster, Mogilevich, Carminati, Moro, Thiriart-&gt;Dugin, Kovalchuk/Firtash); sinapsi principali con grado (compreso l'arco NEGATIVO galassia Aginter/apartheid -&gt; Putin = nessuna convergenza, antipode). Il registro integrale e' la vista d'insieme che sussume i registri parziali (che restano fonti di dettaglio).</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: registro DESCRITTIVO dei nodi e degli archi; la gradazione probatoria dei singoli fatti resta nei registri analitici di dominio e nel registro delle verifiche (voci 35-46). Massimo rigore sui viventi (Putin, Cohen, Firtash, Kovalchuk, Khodorkovsky); nessuna convergenza sistemica promossa a catena di comando personale. Correzione tecnica: i nodi del censimento D1 (col localita') riclassificati correttamente sotto D1 (zero nodi non classificati). INCROCI: tutti i registri-nodi del corpus e le voci 35-46. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>REGISTRO INTEGRALE DEI NODI GENERATO E CERTIFICATO (260 nodi, 9 domini, 10 hub, sinapsi principali). Domini: tutti (D1-D10).</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera/ITALIA_NERA_REGISTRO_ANALITICO_NODI_INTEGRALE.docx + repertorio/ITALIA_NERA_REGISTRO_ANALITICO_NODI_INTEGRALE.xlsx</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2591,6 +2591,51 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>MONOGRAFIA dei GRANDI HUB (parte prima): i dieci nodi a piu' alta centralita' del corpus spiegati per filo e per segno - nodi, sinapsi, ponti, casi ed evidenze - DOCX pubblicato</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera (DOCX monografico dell'opera)</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Primo DOCX della serie sui personaggi/entita' con piu' nodi certificati (criterio: voci 46-47). Tratta i DIECI GRANDI HUB: (1) Yves Guerin-Serac/Aginter Press (nodo-madre; OAS 60%; raid 1974; assassinii Mondlane 1969, Cabral 1973); (2) Stefano Delle Chiaie (AN, Aginter, Condor, golpe Bolivia 1980; assolto piazza Fontana); (3) Vladimir Putin (vertice euroasiatico; siloviki/Ozero; tre sinapsi Kovalchuk/Firtash-Mogilevich/Dugin; massimo rigore); (4) Licio Gelli/P2 (hub eversione-Stato-finanza; mandante Bologna nelle sentenze; liste Castiglion Fibocchi); (5) Stato dell'apartheid Botha/Vorster (entita'; BOSS/NIS; Williamson; omicidi First 1982, September 1988, Lubowski 1989; amnistie TRC); (6) Semyon Mogilevich (architetto crimine euroasiatico; Ivankov/Brighton Beach 1992; RosUkrEnergo; BoNY); (7) Massimo Carminati (cerniera NAR-Magliana; arsenale ministero 27.11.1981; Gevelot-Pecorelli; assoluzioni); (8) Aldo Moro (vittima baricentrica; via Fani 91 bossoli e FNAB-43; esecuzione PPK+Skorpion; PPK mai ritrovata); (9) ponte dottrinale Thiriart-&gt;Dugin (Jeune Europe 1962-69; eurasiatismo); (10) coppia finanziaria Kovalchuk-Firtash (Bank Rossiya/Ozero 1996; sanzioni 2014; RUE/Gazprom).</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>STRUTTURA BICEFALA esplicitata: 7 hub nel blocco nero-atlantista (antipode di Putin), 3 nel blocco euroasiatico, 1 ponte dottrinale di cerniera. Tre nature di legame distinte e dichiarate: (a) sinapsi operative accertate (Serac-Leroy in Aginter; NAR-Magliana nell'arsenale = travaso PROVATO); (b) ponti di metodo/idee (eco Aginter nelle stragi; Thiriart-&gt;Dugin = convergenza, non committenza); (c) l'ARCO NEGATIVO: la galassia Aginter/apartheid NON converge su Putin (antipode). Specularita'/affinita' = fatto morfologico certificato; identita' operativa = tesi non promossa.</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: documento narrativo-monografico che rende in prosa le evidenze gia' gradate nei registri (voci 35-47); massimo rigore sui viventi (Putin, Kovalchuk, Firtash); assoluzioni dichiarate (Delle Chiaie piazza Fontana; Carminati/Pecorelli); mandato Bologna di Gelli come accertamento raggiunto. 'Parte prima' = seguiranno monografie sugli hub successivi in graduatoria. INCROCI: voci 35-47; registro analitico integrale dei nodi. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>MONOGRAFIA DEI GRANDI HUB (PARTE PRIMA) PUBBLICATA. Domini: D7, D3, D2, D6, D4, D1.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera/ITALIA_NERA_MONOGRAFIA_GRANDI_HUB_PARTE_PRIMA.docx</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2636,6 +2636,51 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>OPERA MONUMENTALE in 5 Fasi / 50 Capitoli / 250 nodi-ponti - FASE I: 'La centrale e la radice: Aginter Press e la galassia nera internazionale' - DOCX (stile accademico, cifre arabe)</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera (DOCX della Fase I dell'opera monumentale)</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Prima delle cinque Fasi dell'opera che riordina l'intero corpus. FASE I, 10 capitoli, 50 nodi/ponti certificati (numerati I.1-I.50): Aginter Press e Guerin-Serac (nodo-madre), Robert Leroy, raid 1974; dottrina (Notre action politique 1968-69, guerre revolutionnaire, Ordre et Tradition, OACI); matrice OAS/algerina (11e Choc, istruttore di via Michele Amari); Delle Chiaie e Avanguardia Nazionale; Ordine Nuovo (Rauti, Zorzi, Maggi); servizi (PIDE/DGS, liaison CIA-PIDE 1957, rapporto SDCI, BND/Gehlen); internazionale reazionaria (Le Cercle, Crozier, Damman, Thiriart-&gt;Dugin); dottrina religiosa (Cite Catholique, Giannettini, convegno Pollio 1965); operazioni africane (Mondlane 1969, Cabral 1973, ponte verso apartheid/Williamson); 3 triangolazioni finali + arco negativo galassia-Putin + appendice analitica sulle evidenze.</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Requisiti dell'autore rispettati: stile accademico (Crusca/Treccani); NUMERI IN CIFRE ARABE (deroga esplicita al guardiano anti-cifre, generatore dedicato gen_docx_cifre.py che mantiene A4/Times New Roman 12/giustificato); triangolazioni incrociate tra nodi e ponti diversi; struttura 5 Fasi/50 Capitoli/250 nodi-ponti (questa e' la Fase I). Statuto Savona applicato in prosa (certo/probabile/candidato/negativo); tesi bicefala del corpus e ponte negativo galassia nera&lt;-&gt;Putin come architrave.</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>NOTA DI LUNGHEZZA DICHIARATA: la Fase I e' completa nella struttura (10 capitoli, 50 nodi/ponti, appendice) ma consta di circa 8.750 parole, contro il bersaglio di +/-20.000 parole per Fase indicato dall'autore. La lunghezza piena e' raggiungibile con ulteriore espansione capitolo per capitolo (piu' contesto storico-biografico ed evidenziale); in attesa di disposizione dell'autore, che ha chiesto di fermarsi dopo ogni Fase. Vincolo fonti rispettato (no Grokipedia, no il manifesto). Si procede una Fase per volta.</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>FASE I DELL'OPERA MONUMENTALE GENERATA (struttura completa; lunghezza da confermare/espandere). Domini: D7, D3, D10, D2.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera/ITALIA_NERA_OPERA_MONUMENTALE_FASE_I.docx</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2681,6 +2681,51 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>ATTO DI RICEZIONE: ingresso nel corpus di 21 documenti d'autore nuovi - la linea 'ALDO MORO - Il Registro dei Cinquantacinque Giorni' (Fase Settima), la Tavola Unica, la Tutta la Verita' e materiali di ricerca</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera (ingesti con nome pulito, senza prefisso UUID)</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Ricevuti e collocati in corpus/opera 21 file (deduplicati per contenuto; saltati 20 gia' presenti e 7 doppioni identici). NUCLEO PRINCIPALE - serie 'ALDO MORO - IL REGISTRO DEI CINQUANTACINQUE GIORNI' (autore Luigi De Michele, agosto 2026): dieci Appendici alla FASE SETTIMA (seconda, terza, quarta, quinta, sesta, ottava, nona, decima, undicesima, dodicesima) - documenti di verifica genealogica delle fonti, sull'apparato dell'Indice generale atti della X legislatura (Commissione Moro 2, 102 sedute), che NON modificano i 70 Capitoli dell'opera Moro ma ne raffinano l'apparato probatorio. Inoltre: ITALIA_NERA_PRIMA_SESSIONE_ESECUTIVA_TAVOLA_UNICA (Sezione Metafisica, Religiosa ed Esoterica; verbale in 20 blocchi; chiusura L38, avanzamento L36-L37, voci L39-L43); Opera_Aldo_Moro_Tutta_la_Verita_Triangolazione (consolidamento della matrice probatoria: genealogia delle fonti, fonte derivata, indipendenza, lacuna, causalita', ponte documentale, autore materiale).</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Materiali di ricerca annessi: Diaspora_Nazista_PostBellica_Ricerca_Approfondita_2 (3 MB); Come_i_simzia_1 (simpatizzanti nazisti a Citta' del Capo, Robey Leibbrandt - materiale asse Sudafrica/diaspora nazista, Fase II); Clandestine_Arms_Caches_and_Subversive_Networks (fonte diretta sull'arsenale della Magliana in via Liszt - riscontro della voce 43); cinque registri analitici di sessione in versione senza suffisso (Aginter/Sudafrica-Sudamerica, Guerra Fredda, sessione 2 agosto, Aginter-Sunniti, PayPal-Apartheid, Asse Asiatico-Pacifico).</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: ATTO DI RICEZIONE, non verifica: i documenti entrano come fonti/opere d'autore, conservate cumulativamente (nulla si cancella). MANCANTI dalla serie Moro: appendice PRIMA e appendice SETTIMA (non presenti nel lotto caricato) - da richiedere all'autore per completare la Fase Settima. La linea 'Registro dei Cinquantacinque Giorni' (70 Capitoli + Fase Settima) e' opera parallela dell'autore, di cui il corpus ITALIA NERA accoglie qui l'apparato. Nessuna interrogazione in rete effettuata. Vincolo fonti rispettato.</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>RICEZIONE E COLLOCAZIONE CERTIFICATA (21 documenti d'autore integrati in corpus/opera). Domini: D7 (Moro), D2/D3 (diaspora nazista, Sudafrica), D4 (P2/apparati).</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera/ (21 file; nucleo: ALDO_MORO_APPENDICE_*_FASE_SETTIMA, PRIMA_SESSIONE_ESECUTIVA_TAVOLA_UNICA, Opera_Aldo_Moro_Tutta_la_Verita_Triangolazione)</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2726,6 +2726,51 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>RACCORDO fra la FASE SETTIMA del 'Registro dei Cinquantacinque Giorni' (audit genealogico delle fonti del caso Moro) e ITALIA NERA - DOCX + Excel di crosswalk</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica (DOCX di raccordo) + repertorio (Excel di crosswalk)</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>IDENTITA' DI METODO accertata: i tre atti della Fase Settima (PRODUZIONE genera catena; ACQUISIZIONE = detenere non attestare; ESPOSIZIONE non accresce il computo) sono la formulazione piu' rigorosa dello statuto Savona; il COLLASSO GENEALOGICO (tre fonti di natura diversa NON sono tre catene indipendenti se risalgono al medesimo atto) e' la 'convergenza di milieu diverso da catena di comando' applicata alle FONTI. Regole letteralmente coincidenti: il non reperito non e' il distrutto/occultato (= reperto negativo voci 37,39); il rifiuto a comparire = constatazione negativa netta.</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>CROSSWALK delle 10 appendici possedute (seconda-dodicesima, manca prima e settima) con i nodi del corpus: app. ottava (canale orientale, quarta persona, Stato Zero di 4 apparati, XIII leg. doc. XXIII n.37) &lt;-&gt; lodo Moro/canale OLP (voce 40) e Hyperion; app. undicesima (falsificatore su 3 fascicoli: Moro, Ustica, struttura clandestina) &lt;-&gt; tre grandi nodi del corpus (balistica Moro voci 35-39/48; Gladio voci 41-42,44; Ustica); app. nona (100 record di un servizio estero, sala di lettura elettronica) &lt;-&gt; archivio cia.gov/readingroom in lista, distinzione indirizzo/atto. PROVA GENEALOGICA sulle conclusioni balistiche: confermate 'due armi' e 'PPK mai ritrovata'; il test spiega il declassamento gia' operato di 'Skorpion Dogali=arma di Moro' (voce 41, le molte esposizioni collassano su poche perizie); restano C il candidato di via Silvani (47/18) e il numero bossoli (indirizzo noto, atto non posseduto).</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: RACCORDO, non rifacimento; la Fase Settima non modifica i 70 Capitoli dell'opera Moro. Le due linee si scambiano profondita' (caso singolo) e ampiezza (trama). PENDENZE: mancano appendice PRIMA e SETTIMA (non caricate) - raccordo completo sulle 10 possedute, sospeso sulle 2 assenti; quarta persona non identificata e audizione 21.1.2000 non posseduta; 19 unita' non individuate (app. quarta) aperte = omologo archivistico della PPK mai ritrovata. Nessuna interrogazione in rete (ritorno al solo corpus, come prescrive la Tavola Unica). Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>RACCORDO CERTIFICATO (identita' di metodo fra le due linee; prova genealogica sulla balistica). Domini: D7, D2, D3, D4.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica/ITALIA_NERA_RACCORDO_FASE_SETTIMA_MORO.docx + repertorio/ITALIA_NERA_RACCORDO_FASE_SETTIMA_MORO.xlsx</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2771,6 +2771,51 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>INGRESSO dell'APPENDICE SETTIMA (Fase Settima Moro) e AGGIORNAMENTO del raccordo con ITALIA NERA - resta fuori la sola appendice prima</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera (appendice settima) + corpus/diagnostica + repertorio (raccordo aggiornato)</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Ricevuta e collocata in corpus/opera l'APPENDICE SETTIMA alla Fase Settima ('L'organismo successore e la dichiarazione del proprio standard'): opera sulle due relazioni semestrali della XII legislatura (doc. XXIII n.1 e n.3, 26.1 e 20.7.1995). CONTENUTO CARDINE: la Commissione DICHIARA il proprio standard - i suoi compiti non coincidono con quelli della magistratura, e puo' andare 'oltre la prova processuale', potenzialmente 'insufficiente o deformante' per fenomeni complessi. Da qui l'UNDICESIMA REGOLA DELLA RISALITA: quando un organo dichiara il proprio standard, il grado delle sue ricostruzioni si fissa su quella dichiarazione e non sull'autorevolezza della sede ('la sede conferisce pubblicita', non grado').</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>EFFETTO SUL CORPUS: la regola FONDA la gradazione gia' adottata (atti delle Commissioni = A per le acquisizioni documentali, B per ricostruzioni/valutazioni) sulla dichiarazione della FONTE medesima, non piu' sulla sola prudenza dell'autore - mutamento di natura, non di esito. Conferma la cautela della voce 40 (documenti parlamentari del filone Hyperion registrati ma proscioglimento -&gt; grado C). Il raccordo (DOCX + Excel di crosswalk) e' stato aggiornato: crosswalk esteso alla settima; nuovo paragrafo nel DOCX; pendenze corrette.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: RACCORDO ora completo su UNDICI appendici su dodici; resta fuori la sola APPENDICE PRIMA (non caricata). La settima non modifica i 70 Capitoli (i settanta restano settanta). Restano non possedute la 'quarta persona' e l'audizione 21.1.2000; aperte le 19 unita' non individuate (app. quarta). Nessuna interrogazione in rete. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>INGRESSO E RACCORDO AGGIORNATI (11/12 appendici; undicesima regola della risalita fonda la gradazione del corpus). Domini: D7, D3, D4.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera/ALDO_MORO_APPENDICE_SETTIMA_FASE_SETTIMA.docx + raccordo aggiornato (DOCX + xlsx voce 51)</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2816,6 +2816,51 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>INGRESSO di 3 nuove appendici della Fase Settima Moro (PRIMA/base, QUATTORDICESIMA, QUINDICESIMA) e AGGIORNAMENTO del raccordo - resta fuori la sola tredicesima</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera (3 appendici) + corpus/diagnostica + repertorio (raccordo aggiornato)</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Ricevute e collocate (deduplicate; scartati numerosi doppioni di appendici gia' presenti): (1) APPENDICE PRIMA / base ('Appendice alla Fase Settima - Tavola accresciuta delle acquisizioni necessarie'): accresce il Capitolo 69 dell'opera Moro, iscrive le 19 voci con condizione di chiusura e di smentita, e formula la REGOLA DI FERRO ('dove la fonte documenta, l'opera certifica; dove la fonte tace, l'opera indaga e non afferma') = lo statuto Savona nella sua forma piu' nuda; (2) APPENDICE QUATTORDICESIMA ('La classe di comparazione che non c'e'): opera sulle schede informative delle STRAGI 1969-1984 (XI leg., 36 pagine), respingendo 'un errore che dispensa dal cercare'; (3) APPENDICE QUINDICESIMA ('La relazione che non fu discussa': terza relazione semestrale XII leg., doc. XXIII n.7, 21.2.1996): una proposta depositata e non discussa non acquista grado dal deposito.</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>AGGANCI AL CORPUS: la REGOLA DI FERRO (app. prima) e' identica allo statuto Savona (fondazione comune delle due linee); le STRAGI 1969-1984 (app. quattordicesima) sono i nodi-stragi gia' triangolati alla voce 45 (piazza Fontana, Bologna, piazza della Loggia, Peteano), e il rifiuto dell''errore che dispensa dal cercare' e' la non-inferenza del corpus; la quindicesima e' corollario dell'undicesima regola (la sede conferisce pubblicita', non grado). Raccordo (DOCX + Excel di crosswalk) aggiornato: crosswalk esteso a prima/quattordicesima/quindicesima; due nuovi paragrafi nel DOCX; pendenze corrette.</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: la serie Fase Settima si estende alla QUINDICESIMA; il corpus ne possiede ora QUATTORDICI (prima [base], seconda-dodicesima, quattordicesima, quindicesima). Resta fuori la sola appendice TREDICESIMA (non caricata): raccordo completo su 14, sospeso su 1. Le appendici non modificano i 70 Capitoli. Nessuna interrogazione in rete. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>INGRESSO E RACCORDO AGGIORNATI (14/15 appendici; Regola di Ferro = statuto Savona; stragi 1969-1984 agganciate alla voce 45). Domini: D7, D3, D4.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera/ALDO_MORO_APPENDICE_{PRIMA,QUATTORDICESIMA,QUINDICESIMA}_FASE_SETTIMA.docx + raccordo aggiornato (DOCX + xlsx)</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2861,6 +2861,51 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>INGRESSO dell'APPENDICE TREDICESIMA (Fase Settima Moro) e CHIUSURA della serie e del raccordo - il corpus possiede ora tutte le 15 appendici</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera (appendice tredicesima) + corpus/diagnostica + repertorio (raccordo chiuso)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Ricevuta e collocata l'APPENDICE TREDICESIMA ('Una sola testimonianza formale', Esecuzione della Voce quarantaseiesima): ricava dal prospetto analitico delle sedute l'oggetto delle 27 sedute i cui verbali non sono posseduti e individua fra gli auditi in sede formale le deposizioni che riguardano il caso. CASO METODOLOGICO LIMPIDO: DICHIARA un difetto della fonte (il riconoscimento ottico deforma gli indicatori ordinali - la prima seduta appare 18a, la seconda 24a, ecc.) e lo RISOLVE per inferenza posizionale, VERIFICATA su 5 ancoraggi indipendenti (processi verbali posseduti, es. 4a voce = 23.11.1988), dichiarando che 'la risoluzione e' un'inferenza dell'opera e non un dato del documento, ed e' falsificabile'; corregge l'appendice dodicesima in un punto che essa non sapeva spiegare.</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>AGGANCIO AL CORPUS: la vicenda e' un modello da laboratorio della disciplina comune - difetto della fonte dichiarato anziche' taciuto, errore plausibile riconosciuto come la specie peggiore, inferenza tenuta distinta dal dato, verifica su ancoraggi indipendenti, falsificabilita' offerta al lettore = la stessa operazione del corpus (registrare l'indirizzo e non il contenuto di un atto non posseduto; dichiarare falsificabile ogni ricostruzione). 'Una sola testimonianza formale' = conferma empirica del COLLASSO GENEALOGICO (poche deposizioni realmente sul caso fra i molti auditi). Raccordo (DOCX + Excel di crosswalk) aggiornato: crosswalk esteso alla tredicesima; due nuovi paragrafi nel DOCX; pendenze chiuse.</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: SERIE COMPLETA - il corpus possiede tutte le QUINDICI appendici della Fase Settima (prima/base, seconda-quindicesima); il raccordo e' CHIUSO, nessuna appendice manca. Restano aperte come pendenze INTERNE alle appendici (non del raccordo): la 'quarta persona' (app. ottava), l'audizione 21.1.2000 non posseduta, le 19 unita' non individuate (app. quarta) - code documentali dichiarate. Le appendici non modificano i 70 Capitoli. Nessuna interrogazione in rete. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>SERIE FASE SETTIMA COMPLETA (15/15) E RACCORDO CHIUSO. Domini: D7, D3, D4.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera/ALDO_MORO_APPENDICE_TREDICESIMA_FASE_SETTIMA.docx + raccordo chiuso (DOCX + xlsx)</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2906,6 +2906,51 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>ATTO DI RICEZIONE: 12 documenti d'autore nuovi - la linea 'Registro Analitico del caso Moro' (V1/V3/V4/V5/V6 + Speculare), tre Registri Dominiali (D03/D04/D08), Sacro-Guevara-Moro, Seconda Sequenza Giornaliera, e il generatore 'titanico' dei 50 blocchi</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera (ingesti con nome pulito)</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Ricevuti e collocati in corpus/opera 12 file nuovi (saltati per contenuto identico i 2 ri-caricamenti del mio raccordo Fase Settima e la Tutta la Verita' v2). LINEA REGISTRO ANALITICO DEL CASO MORO ('Registro autonomo delle reti informali del sequestro e dell'omicidio di Aldo Moro'), versioni progressive: V1 Integrale, V3 con secondo anello, V4 'salto della quaglia', V5 'rinnovamento cartesiano', V6 'apporto kuhniano' (manca V2, non caricata), piu' REGISTRO SPECULARE 'Anelli Profondi' V1 (dal secondo al quarto anello di prossimita'). TRE REGISTRI DOMINIALI 'delle Reti Informali Transnazionali': D03 Intelligence, D04 Massoneria, D08 Media (2 ago 2026). ITALIA_NERA_REGISTRO_DI_TRIANGOLAZIONE_SACRO_GUEVARA_MORO (23 ago; 'Il Sacro, il Dossier Guevara e i Dossier Moro'). ITALIA_NERA_OPERA_SECONDA_SEQUENZA_GIORNALIERA_PARTE_PRIMA ('Tutta la Verita' - prosecuzione titanica').</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>GENERATORE: OPERA_ALDO_MORO_TUTTA_LA_VERITA_TITANICO_50_BLOCCHI_generatore.js - script Node/docx d'autore (De Michele) che genera 'Approfondimento titanico della triangolazione in cinquanta blocchi mirati' (10 parti, 50 blocchi), condotto sui tre reperti (Opera del 22 ago; Dossier V74 del 19 ago, 17a tavola; Trattato Topografico), con impronte SHA-256 dichiarate e la REGOLA DI FERRO in ogni blocco. E' la sorgente di un documento dell'opera: conservato con la linea Moro.</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: ATTO DI RICEZIONE, non verifica; conservazione cumulativa (nulla si cancella). Le versioni progressive del Registro Analitico si conservano tutte (manca V2). I tre Registri Dominiali (D03/D04/D08) arricchiscono i domini del corpus e potranno alimentare un aggiornamento del registro analitico integrale dei nodi (voce 47). Nessuna interrogazione in rete. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>RICEZIONE E COLLOCAZIONE CERTIFICATA (12 documenti d'autore + 1 generatore in corpus/opera). Domini: D7 (Moro), D3 (Intelligence), D4 (Massoneria), D8 (Media).</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera/ (REGISTRO_ANALITICO_CASO_MORO_V1..V6 + SPECULARE; REGISTRO_DOMINIALE_D03/D04/D08; SACRO_GUEVARA_MORO; SECONDA_SEQUENZA_GIORNALIERA; titanico generatore)</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2951,6 +2951,51 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>ATTO DI RICEZIONE MAGGIORE: 556 schede-nodo per dominio (DOCUMENTO-NODO del Registro Integrale V63) + il REGISTRO SINAPTICO GENERALE ('il connettoma dell'opera')</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera/nodi/&lt;dominio&gt; (schede) + corpus/opera (registro sinaptico generale)</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Ricevuti e collocati 556 dossier per-nodo (ciascuno 'DOCUMENTO-NODO' del Registro Integrale V63, con dominio primario e grado Savona conservato dalla sede d'origine), estratti da 10 archivi ZIP e ordinati in corpus/opera/nodi/&lt;dominio&gt;: D02 (attori geopolitici e regimi) 305 schede; D03 (intelligence e servizi) 58 + D03 SINAPTICO 58; D09 (assi militari) 44; D06 (reti bancarie/finanza) 23; D10 (magistratura/giustizia) 22; D05 (religione/matrici) 16; D04 (massoneria) 10 + D04 SINAPTICO 10; D08 (media) 7; D01 (criminalita' organizzata: Riina) 1 + SINAPTICO 1; D02 SINAPTICO (Andreotti) 1. Deduplicato un ZIP D08 identico (stesso md5). Aggiunte le schede singole Riina (D01) e Andreotti (D02) con le loro varianti sinaptiche.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>REGISTRO SINAPTICO GENERALE (78.231 parole): 'il connettoma dell'opera' - elenco integrale delle sinapsi per co-occorrenza rilevate dalla cascata sui tredici registri della Conoscenza di Progetto, con la matrice delle coppie di dominio e la gerarchia dei nodi per grado sinaptico. E' la versione d'autore, granulare e completa, del concetto di nodo/sinapsi che il corpus aveva consolidato nel registro analitico integrale (voce 47, 260 nodi): questa collezione lo espande a oltre 550 schede monografiche piu' il connettoma generale.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: ATTO DI RICEZIONE, non verifica; conservazione cumulativa. I gradi Savona delle schede sono attribuiti nella sede d'origine (Registro Integrale V63) e qui conservati senza eccezioni. FOLLOW-UP possibile: federare queste schede e il connettoma con il registro analitico integrale dei nodi (voce 47), aggiornandolo dalla base granulare V63. Nessuna interrogazione in rete. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>RICEZIONE MAGGIORE CERTIFICATA (556 schede-nodo + connettoma generale in corpus/opera). Domini: tutti (D01-D10).</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera/nodi/ (556 DOCUMENTO-NODO in 13 cartelle di dominio) + corpus/opera/ITALIA_NERA_REGISTRO_SINAPTICO_GENERALE_2AGO2026.docx</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2996,6 +2996,51 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>ATTO DI RICEZIONE: 15 documenti d'autore (l'opera-madre 'Aldo Moro - Tutta la verita' / Una guerra senza fine' da 374.593 parole; Registro Analitico Caso Moro V11 e Speculare V4; registri di metodo; triangolazioni; 'Il Sacro e l'Eversione'; 'Canale Petrolifero'; due PDF V63)</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera (ingesti con nome pulito; PDF inclusi)</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Ricevuti e collocati 15 file nuovi (deduplicato un doppione interno: REGISTRO_TRIANGOLAZIONE_CORPUS 1=2). OPERA-MADRE: 'Aldo_Moro_Tutta_la_verita - Una guerra senza fine' (374.593 parole) - il grande testo integrale del caso Moro. LINEA REGISTRO ANALITICO CASO MORO: V11 'Applicazione definitiva' (38.467 parole, ultima versione) e Speculare V4 'Applicazione definitiva' (Anelli Profondi, edizione seconda). REGISTRI DI METODO: Registro Analitico Rete; Registro di Vaglio (Fascia Prima); Registro dei Pattern Avanzati; Registro dei Neuroni Neonati. TRIANGOLAZIONI: Tre Famiglie in cinquanta blocchi; Registro di Triangolazione del Corpus ('Spine, ambienti e Stati Zero'); Opera Aldo Moro - Registro Esteso di Triangolazione. TEMATICI: 'Il Sacro e l'Eversione' (esoterismo/religione/metafisica nella storia nera, D10); 'Dossier Maestri Cosmici - Aetherius Society, dieci testimonianze'; 'Canale Petrolifero in dieci capitoli' (nodo Chiavelli, contratto Lucina, intermediari privati - area ENI/energia, D6).</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>DUE PDF: 'ITALIA_NERA_Registro_Verifica_Triangolazione_V63' (512 KB) e 'ITALIA_NERA_REGISTRO_TRIANGOLAZIONE_CONFERIMENTO_23AGO2026' (130 KB) - registri di verifica/conferimento della base V63, collocati in corpus/opera accanto alle schede-nodo V63 (voce 56). Tutti i documenti si ancorano al 'Registro Integrale V63' e alla Regola di Ferro.</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: ATTO DI RICEZIONE, non verifica; conservazione cumulativa (nulla si cancella; le versioni Moro V1-V6 e V11 coesistono). FOLLOW-UP: 'Il Sacro e l'Eversione' e 'Maestri Cosmici' arricchiscono il dominio D10 (matrici dottrinali/esoteriche); 'Canale Petrolifero' (Chiavelli/Lucina) e' un nodo D6 (energia/finanza) triangolabile con la dorsale gas-energia (voci 44-46). Nessuna interrogazione in rete. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>RICEZIONE CERTIFICATA (13 DOCX + 2 PDF in corpus/opera; opera-madre Moro inclusa). Domini: D7 (Moro), D10 (sacro/esoterismo), D6 (petrolifero), D1-D3 (triangolazioni).</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera/ (Aldo_Moro_Tutta_la_verita_Una_guerra_senza_fine; REGISTRO_ANALITICO_CASO_MORO_V11; REGISTRO_SPECULARE_V4; registri di metodo e triangolazione; IL_SACRO_E_L_EVERSIONE; CANALE_PETROLIFERO; 2 PDF V63)</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3041,6 +3041,51 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE TOTALE: il connettoma d'autore V63 (grado sinaptico) e le triangolazioni del corpus (frequenza, voce 46) a confronto - DOCX + Excel</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica (DOCX) + repertorio (Excel a 6 fogli)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>DUE METODI INDIPENDENTI a confronto: (a) la mia classifica per FREQUENZA di menzione (voce 46), (b) il CONNETTOMA V63 per GRADO SINAPTICO (numero di neuroni distinti connessi sui 13 registri). Gerarchia V63: CIA (159), Gelli (152), Moro (151), Andreotti (146), Lucky Luciano (143), Trump (129), Delle Chiaie (122), Falcone (118), Sindona (113), Banco Ambrosiano (113), SISMI (111), Ordine Nuovo (109), SID (105), Salvo Lima (103), Di Bernardo, Maletti, Riina, Gioia, Magliana, Pinochet. CONVERGENZA CERTIFICATA: entrambi i metodi collocano ai vertici Gelli, Moro, Delle Chiaie, Andreotti, Pinochet, Ordine Nuovo (nucleo di hub dello Stato profondo italiano). DIVERGENZA SPIEGATA: la mia frequenza illumina il lobo INTERNAZIONALE (Aginter/apartheid/euroasia), il connettoma il lobo ISTITUZIONALE ITALIANO (Stato-mafia-P2-Vaticano). Struttura BICEFALA confermata da due metodi.</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>SINAPSI INTER-DOMINIO MAESTRE = i ponti del corpus, misurati: SID-Ordine Nuovo (141) = porosita' Stato-eversione (cerniera Giannettini, voci 45,48); quadrilatero Gelli-Sindona-IOR-Banco Ambrosiano (101-135) = cluster P2-Vaticano-finanza (in parte da triangolare); Andreotti-Falcone (119) = politica-magistratura; SCU-Corona (176) = mafia-massoneria. Trump 6o nel connettoma = aggancio alla dorsale euroasiatica (voci 45-46). INNESTI TEMATICI NUOVI: 'Il Sacro e l'Eversione' e 'Maestri Cosmici' (esoterismo, aggancio alla matrice religiosa di Aginter, Fase I); 'Canale Petrolifero' (Chiavelli/Lucina, energia D6, triangolabile con dorsale gas ed con Sindona/Ambrosiano).</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>RICONCILIAZIONE TASSONOMICA: la base V63 e' autoritativa; coincide col registro voce 47 tranne il DOMINIO D10, che in V63 e' MAGISTRATURA (Falcone, Caponnetto, Terranova) e non 'matrici dottrinali' - il registro voce 47 va riallineato. STATUTO SAVONA ANCHE SUL CONNETTOMA: la sinapsi piu' intensa (PCC-PCC, 193) e' un REPERTO DI OMONIMIA (sigla, non nesso), non un ponte storico - nessuna misura dispensa dal giudizio. VERDETTO-CARDINE INVARIATO: convergenza di milieu/sistema certificata (ora da 2 metodi); catena di comando unica NON provata; arco negativo galassia nera&lt;-&gt;Putin permane (solo ponte euroasiatico). Nessuna interrogazione in rete. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE TOTALE CERTIFICATA (2 metodi indipendenti convergenti; struttura bicefala; riconciliazione domini). Domini: tutti (D1-D10).</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica/ITALIA_NERA_TRIANGOLAZIONE_TOTALE_V63.docx + repertorio/ITALIA_NERA_TRIANGOLAZIONE_TOTALE_V63.xlsx</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3086,6 +3086,51 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>ATTO DI RICEZIONE: i documenti FONDATIVI della base V63 - il REGISTRO INTEGRALE V63 (registro-madre, 1.417.722 parole), il V67 Tomo 1 Titanico, la Nota Metodologica, e tre triangolazioni V63</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera (ingesti con nome pulito)</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Ricevuti e collocati 6 file fondativi (deduplicato un doppione: Seconda Serie Ricognizioni caricata due volte). PEZZO CARDINE: ITALIA_NERA_REGISTRO_INTEGRALE_V63 (1.417.722 parole, 3,6 MB) - il registro-madre dei nodi da cui derivano le 556 schede della voce 56 e il connettoma della voce 56; e' la SORGENTE AUTORITATIVA dell'intera base V63. ITALIA_NERA_V67_TOMO_1_TITANICO_V63 (193.384 parole, 'Edizione Integrale Federata', Tomo 1). ITALIA_NERA_V63_NOTA_METODOLOGICA_E_SEZIONI (19.440 parole: premessa epistemologica, il problema della conoscenza nel caso Moro, e la partizione in sezioni). ITALIA_NERA_V63_SCHEDA_DIAGNOSTICA_PMI (scheda diagnostica complessiva). TRIANGOLAZIONE SECONDA SERIE - Ricognizioni ('le diciotto ricognizioni'). TRIANGOLAZIONE SCHEDE-DOSSIER V63 ('la sesta tavola').</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>COMPLETAMENTO DELLA BASE V63: con questi documenti il corpus possiede ora l'intera architettura V63 - il registro-madre (voce 59), le 556 schede-nodo e il connettoma (voce 56), i registri di metodo e verifica (voci 57-59), le triangolazioni d'autore. La Nota Metodologica fornisce la premessa epistemologica esplicita che fonda tutto l'impianto. Questi documenti ABILITANO DEFINITIVAMENTE il riallineamento del registro analitico integrale dei nodi (voce 47) alla tassonomia autoritativa V63 (compreso il D10 = Magistratura, gia' rilevato alla voce 58).</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: ATTO DI RICEZIONE, non verifica; conservazione cumulativa. Il REGISTRO INTEGRALE V63 e' la sorgente autoritativa: ogni futura verifica o federazione dei nodi attinge ad esso. Nessuna interrogazione in rete. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>RICEZIONE CERTIFICATA (6 documenti fondativi V63, compreso il registro-madre da 1,4 milioni di parole). Domini: tutti (D1-D10).</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera/ (REGISTRO_INTEGRALE_V63; V67_TOMO_1_TITANICO_V63; V63_NOTA_METODOLOGICA_E_SEZIONI; V63_SCHEDA_DIAGNOSTICA_PMI; TRIANGOLAZIONE_SECONDA_SERIE_RICOGNIZIONI_V63; TRIANGOLAZIONE_SCHEDE_DOSSIER_V63)</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3131,6 +3131,51 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>REGISTRO UNICO DEI NODI: federazione della base V63 (486 schede + connettoma) e della sintesi del corpus (voce 47) in un solo registro autoritativo - DOCX + Excel</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica (DOCX) + repertorio (Excel del registro unico)</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>753 NODI federati in un unico registro, ordinati per dominio e per grado sinaptico. FONTI dichiarate per ciascun nodo: 486 schede-nodo di base del Registro Integrale V63 (voci 56,59), i nodi della sintesi del corpus (registro voce 47) non gia' coperti, e i 40 nodi di grado sinaptico massimo annotati dal connettoma. Distribuzione (tassonomia V63): D1=70, D2=351, D3=85, D4=27, D5=16, D6=56, D7=49, D8=11, D9=56, D10=32. RICONCILIAZIONE DEFINITIVA: la base V63 e' autoritativa; il D10 e' MAGISTRATURA E GIUSTIZIA (Falcone, Borsellino, Caponnetto, Terranova, Saetta, Caccia), non 'matrici dottrinali'; la religione e' D5 (con lo IOR); le matrici dottrinali restano materia tematica.</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>LACUNA DICHIARATA: le schede del dominio D7 (eversione nera) NON sono state caricate nella base V63; i suoi 49 nodi provengono qui dalla sintesi voce 47 e dal connettoma (Delle Chiaie, Ordine Nuovo, BR, AN, Vinciguerra - tutti alti per grado sinaptico) - da completare con le schede V63 del D7 quando disponibili. Il registro unico rende visibile la struttura bicefala: i 40 hub di grado massimo sono in larga parte l'intreccio istituzionale italiano (CIA, Gelli, Moro, Andreotti, Sindona, Ambrosiano, servizi, magistratura), con i nodi dell'eversione nera come cerniera verso il lobo internazionale e il nodo Trump come cerniera verso la dorsale euroasiatica.</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: strumento di ORDINE, non di accertamento; registra nodi/fonti/domini/centralita', non promuove gradi ne' trasforma centralita' in colpa. Il grado sinaptico e' misura di connessione, distinto dal grado probatorio Savona (le schede V63 recano quasi tutte A dalla sede d'origine). Regola di Ferro comune alle due opere. Il registro unico sussume le due anagrafi (voce 47 e base V63) senza cancellarle (restano fonti). Nessuna interrogazione in rete. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>REGISTRO UNICO DEI NODI GENERATO E CERTIFICATO (753 nodi, 10 domini, 40 hub, tassonomia V63 riconciliata). Domini: tutti (D1-D10).</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica/ITALIA_NERA_REGISTRO_UNICO_NODI_V63.docx + repertorio/ITALIA_NERA_REGISTRO_UNICO_NODI_V63.xlsx</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3176,6 +3176,51 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>ATTO DI RICEZIONE: la Terza Serie di triangolazione sul caso Moro e i Tomi 2, 3, 4 del V67 Titanico V63 (edizione integrale federata) - completano l'edizione titanica in quattro tomi</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera (ingesti con nome pulito)</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Ricevuti e collocati 4 file nuovi (tutti gli altri del lotto erano ri-caricamenti gia' in repo, compreso il mio Registro Unico dei Nodi, la Nota Metodologica, il Tomo 1, la Seconda Serie e la Schede-Dossier). ITALIA_NERA_TRIANGOLAZIONE_TERZA_SERIE_CASO_MORO_V63 (3.192 parole): la terza serie di triangolazione dedicata al caso Moro. I TRE TOMI mancanti dell'EDIZIONE INTEGRALE FEDERATA 'V67 Titanico V63': Tomo 2 (472.029 parole), Tomo 3 (140.820 parole), Tomo 4 (614.240 parole). Con il Tomo 1 (193.384 parole, gia' in repo alla voce 59) l'edizione titanica in quattro tomi e' ora COMPLETA nel corpus, per un totale di circa 1,42 milioni di parole - la versione federata e impaginata del Registro Integrale V63 (voce 59).</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>COMPLETAMENTO DELL'EDIZIONE V67 TITANICO: i quattro tomi sono la forma editoriale definitiva della base V63 (il registro-madre da 1,4 milioni di parole della voce 59, qui articolato in quattro volumi). Con questo ingresso il corpus possiede l'intera base V63 sia in forma di registro-madre unico, sia in forma di edizione federata in quattro tomi, sia in forma di 556 schede-nodo e connettoma (voce 56), sia nel Registro Unico dei Nodi che le federa (voce 60).</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: ATTO DI RICEZIONE, non verifica; conservazione cumulativa. La Terza Serie sul caso Moro si aggiunge alla Prima e alla Seconda (Ricognizioni) gia' in corpus. Nessuna interrogazione in rete. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>RICEZIONE CERTIFICATA (Terza Serie Moro + Tomi 2-4 del V67 Titanico; edizione in 4 tomi completa). Domini: tutti (D1-D10), D7 (Moro).</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera/ (TRIANGOLAZIONE_TERZA_SERIE_CASO_MORO_V63; V67_TOMO_2/3/4_TITANICO_V63)</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3221,6 +3221,51 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>ATTO DI RICEZIONE di un dittico metodologico V61: l'ELENCO P2 verificato (fonte Anselmi/Castiglion Fibocchi, grado A) e l'ANALISI STRUTTURALE che motiva il NON-USO di due liste massoniche anonime (reperto negativo)</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera (elenco P2) + corpus/diagnostica (analisi strutturale)</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>ELENCO_P2_FASCICOLI_VERIFICATO_V61 (corpus/opera, D4): estrazione dalla FONTE REALE - 960 record su 962, ordinati per numero di fascicolo, dall'elenco alfabetico sequestrato a Castiglion Fibocchi il 17.3.1981 e pubblicato in allegato alla Relazione della Commissione parlamentare d'inchiesta presieduta da Tina Anselmi (comunicata alle Camere il 12.7.1984). GRADO A (fonte verificabile). Corregge tre attribuzioni del Registro V61 e risponde empiricamente alla domanda sull'adiacenza numerica dei fascicoli.</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>ANALISI_STRUTTURALE_FILE_CARICATI_V61 (corpus/diagnostica): diagnosi di provenienza, portata e qualita' di due PDF di elenchi massonici (308 e 2.206 pagine) condotta SENZA estrarre alcun nominativo, che documenta e motiva la DECISIONE DI NON UTILIZZARLI COME FONTE - privi di intestazione, data, riferimento a operazione giudiziaria o qualunque marcatura di riconducibilita' a fonte verificabile; e sono due esportazioni del medesimo archivio (non due fonti indipendenti). E' un REPERTO NEGATIVO dichiarato (non verificabilita' + riservatezza): il corpus registra la decisione di non-uso come risultato.</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: DITTICO ESEMPLARE dello statuto Savona - una fonte verificabile (Anselmi/Castiglion Fibocchi) e' USATA e graduata A; due liste anonime sono RESPINTE con motivazione dichiarata. NB: NESSUN nominativo di massa entra nel corpus - le liste massoniche anonime NON sono ingerite, solo l'analisi d'autore che ne motiva l'esclusione. Il P2 verificato alimenta il dominio D4 (massoneria) e corregge il Registro V61. Nessuna interrogazione in rete. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>RICEZIONE CERTIFICATA (dittico P2: elenco verificato grado A + analisi con decisione di non-uso dichiarata). Domini: D4 (massoneria/P2).</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera/ITALIA_NERA_ELENCO_P2_FASCICOLI_VERIFICATO_V61.docx + corpus/diagnostica/ITALIA_NERA_ANALISI_STRUTTURALE_FILE_CARICATI_V61.docx</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3266,6 +3266,51 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>ATTO DI RICEZIONE: il REGISTRO DOMINIALE D07 - Terrorismo e violenza politica (partizione V63) - colma PARZIALMENTE la lacuna del dominio D7 dichiarata alla voce 60</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera (registro dominiale)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Ricevuto e collocato (deduplicato: caricato due volte, identico) il REGISTRO DOMINIALE DEL DOMINIO 7 - TERRORISMO E VIOLENZA POLITICA (6.827 parole), 'area cerebrale D7 della struttura neuronale dell'opera', partizione del Registro Integrale V63. Documenta l'area D7 con i suoi nodi (eversione nera e rossa: Delle Chiaie, Ordine Nuovo, Brigate Rosse, Avanguardia Nazionale, Vinciguerra...), gli archi cross-section e la cronologia marcata. E' l'omologo D7 dei registri dominiali D03/D04/D08 gia' ricevuti (voce 55).</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>EFFETTO SULLA LACUNA D7: alla voce 60 (Registro Unico dei Nodi) il dominio D7 era presente solo 'di seconda mano' (dalla sintesi voce 47 e dal connettoma), perche' le schede-nodo singole del D7 non erano state caricate. Questo registro dominiale porta ora il D7 nel corpus in FORMA DI REGISTRO DI DOMINIO (non ancora come schede singole): la lacuna e' COLMATA PARZIALMENTE. RESTA DA ACQUISIRE: le schede-nodo individuali del D7 (l'archivio ZIP non si carica - da ritentare o da committare direttamente nel repo).</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: ATTO DI RICEZIONE, non verifica; conservazione cumulativa. Il registro dominiale D7 e' fonte autoritativa V63 per l'area terrorismo, coerente con i domini gia' ricevuti. Con questo il corpus possiede i registri dominiali per D3, D4, D7, D8 (mancano ancora D1, D2, D5, D6, D9, D10 come registri dominiali autonomi, benche' le loro schede siano gia' in corpus). Nessuna interrogazione in rete. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>RICEZIONE CERTIFICATA (registro dominiale D7; lacuna D7 colmata a livello di dominio, schede singole ancora attese). Domini: D7 (eversione/terrorismo).</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera/ITALIA_NERA_REGISTRO_DOMINIALE_D07_TERRORISMO_2AGO2026.docx</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3311,6 +3311,51 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE del cluster P2-VATICANO-FINANZA (Gelli/P2 - Sindona - Calvi/Ambrosiano - IOR/Marcinkus) - il grande nodo italiano finora annunciato e non sviluppato - DOCX + Excel</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica (DOCX) + repertorio (Excel a 6 fogli)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>QUADRILATERO a 4 vertici, dalle schede V63 grado A: Licio Gelli (D4, Venerabile P2, lista Castiglion Fibocchi 17.3.1981, 962 affiliati, pregresso fascista/CIA/Argentina); Michele Sindona (D6, banchiere P2, Banca Privata Italiana + Franklin National Bank/David Kennedy, ergastolo per Ambrosoli, avvelenato in carcere 22.3.1986); Roberto Calvi (D6, Banco Ambrosiano, P2, impiccato a Blackfriars 18.6.1982, sentenza 2007 = omicidio mandato Calo'); IOR/Marcinkus (D5, banca vaticana, presidenza 1971-1989, FBI legami Chicago Outfit, lettere di patronato a off-shore Calvi 1981, immunita' lateranense). SPINA = ARCO #10 GIA' CERTIFICATO A: Sindona-Calvi -&gt; IOR -&gt; banchi vaticani -&gt; estero (Filiazione). SCIA DI SANGUE: Ambrosoli 1979 (mandato Sindona), Calvi 1982 (mandato Calo'), Sindona 1986 (avvelenato).</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>CONFERMA DAL CONNETTOMA (sinapsi piu' intense): Gelli-Sindona 135, IOR-Sindona 134, CIA-IOR 129, IOR-Ambrosiano 121, Andreotti-Gelli 116, Gelli-IOR 101. TRIANGOLAZIONE COL CORPUS: verso D1 mafia (Sindona riciclatore, Calvi/Calo', Marcinkus/Chicago) = ponte finanza-criminalita'; verso Condor/galassia nera (Gelli fascista, P2 in Argentina/Massera-Suarez Mason, voce 40); verso l'atlantico (CIA, Franklin/Kennedy); verso D10 magistratura (Ambrosoli caso simbolo dell'omicidio del servitore che documenta, come Falcone/Borsellino); verso le stragi (Gelli mandante di Bologna, voce 48).</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: triangolazione condotta sul SOLO CORPUS (schede V63 grado A + connettoma), senza interrogazione in rete. CERTO (A): identita'/legami, Arco #10, omicidio Ambrosoli+ergastolo Sindona, omicidio Calvi (sentenza 2007), avvelenamento Sindona, crack Ambrosiano, lettere IOR-Calvi, Gelli mandante Bologna. RESTA B/C: mandante ultimo oltre l'esecutore, responsabilita' penale IOR/Marcinkus (immunita' lateranense, mai processati in Italia), nesso Andreotti-cluster (Livello C, appaiamento automatico), regia complessiva. Convergenza di milieu certificata; catena di comando unica non provata. Cifra: e' il VOLTO FINANZIARIO dello Stato profondo (l'arma e' il denaro, il metodo il riciclaggio, la scia di sangue e la protezione istituzionale le stesse degli altri fronti). Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE CERTIFICATA (cluster P2-Vaticano-finanza; quadrilatero, arco-spina, scia di sangue, conferma connettoma). Domini: D4, D5, D6, D1, D2, D10.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica/ITALIA_NERA_TRIANGOLAZIONE_P2_VATICANO_FINANZA.docx + repertorio/ITALIA_NERA_TRIANGOLAZIONE_P2_VATICANO_FINANZA.xlsx</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3356,6 +3356,51 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>ATTO DI RICEZIONE di 4 FONTI PRIMARIE in fonti/ (atto parlamentare 'Memoria Condivisa', saggio accademico sul caso Cirillo, articolo di stampa sul 2 agosto, memoriale Gladio da blog) - con gradazione differenziata</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>fonti/ (atti e fonti acquisiti da terzi)</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Ricevute e collocate in fonti/ 4 fonti primarie uniche (deduplicata la Memoria Condivisa, caricata 4 volte): (1) XIII_leg_Doc_XXIII_64_Vol_I_Tomo_IV_p375_Memoria_Condivisa (9.351 parole): ATTO PARLAMENTARE - Commissione stragi XIII legislatura, Doc. XXIII n.64, Vol I Tomo IV pp.375-408, 'Il problema di definire una memoria storica condivisa', elaborato del senatore Athos De Luca. GRADO: A per l'acquisizione (atto pubblicato), B per le valutazioni (elaborato = ricostruzione, per l'undicesima regola della risalita). (2) Storiaememoria.pdf (50 pagine): SAGGIO ACCADEMICO - rivista Cross Vol.2 N.3 (2016), DOI 10.13130/cross-7795, 'La Camorra e il caso Cirillo' a cura di Sarah Mazzenzana, con estratti dal Rapporto parlamentare sulla Camorra. GRADO B (accademico, peer-reviewed). Aggancio: il caso Cirillo (sequestro BR 1981, mediazione Cutolo/Camorra-DC-servizi) - nodo che lega BR, Camorra (D1), DC (D2) e servizi (D3).</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>(3) Due_agosto_a_un_passo_dai_mandanti_la_Repubblica.mht: ARTICOLO DI STAMPA (bologna.repubblica.it, 2.8.2013) sui mandanti della strage di Bologna. GRADO B/C (fonte giornalistica; la Repubblica NON e' fonte vietata - solo il manifesto lo e'). (4) Documento_Gladio_Memoriale_di_un_Gladiatore_blog.mht: 'Memoriale di un Gladiatore, missioni segrete estere', da BLOG (fisicamente.blog, 2023). GRADO C CON RISERVA DI ATTENDIBILITA': fonte auto-pubblicata, non verificabile, riconducibile a un blog - reperto di livello C, da trattare con la stessa cautela delle liste anonime della voce 62.</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: ATTO DI RICEZIONE con GRADAZIONE DIFFERENZIATA (non tutte le fonti sono uguali - dall'atto parlamentare A al blog C). fonti/ NON era vuota: gia' conteneva biografie Genovese, nazisti in Sudamerica/USA, network finanziario Sudafrica, un censimento fonti P2 (Governali) - queste 4 vi si aggiungono. L'articolo di stampa e il memoriale-blog restano fonti da usare con cautela (allegazione, non prova); il saggio Cross e l'atto De Luca sono fonti di prim'ordine per il caso Cirillo e la Camorra. Nessuna interrogazione in rete. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>RICEZIONE FONTI CERTIFICATA (4 fonti primarie graduate: parlamentare A/B, accademica B, stampa B/C, blog C). Domini: D7 (stragi/Gladio), D1 (Camorra), D4 (P2).</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>fonti/ (Memoria_Condivisa De Luca; Storiaememoria/caso Cirillo; Due_agosto la Repubblica; Memoriale_Gladiatore blog)</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3401,6 +3401,51 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE del CASO CIRILLO con 100 blocchi mirati - il nodo che lega BR (D7), camorra/Cutolo (D1), DC campana (D2) e servizi SISDE/SISMI (D3), con ponte P2 (D4) verso la voce 64 - DOCX + Excel a 100 blocchi</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica (DOCX) + repertorio (Excel a 12 fogli, 100 blocchi)</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>SVILUPPO dell'innesto entrato alla voce 65 (fonte accademica Cross 2016 sul caso Cirillo). Il sequestro di Ciro Cirillo (assessore DC, corrente Gava) da parte delle BR il 27.4.1981 a Torre del Greco (uccisi Carbone e Cancello) e la liberazione il 24.7.1981 avvengono - dixit la Commissione parlamentare Antimafia - 'dopo trattative condotte da funzionari dello Stato e uomini politici con camorristi e brigatisti'. Cutolo/NCO 'elevato a rango di intermediario tra lo Stato e le BR' (rel. Gualtieri 10.10.1984 = 'gravi deviazioni' del SISMI). 100 blocchi in 10 sezioni: (1) il fatto; (2) terremoto/NCO/Cutolo; (3) mediazione e contropartite giudiziarie (Cutolo rifiuta il denaro); (4) servizi SISDE (Parisi, Criscuolo/Acanfora) poi SISMI (Santovito, Musumeci); (5) DC campana (Granata, Patriarca, riunione 'non statutaria' Roma, unita' di crisi Russo); (6) appalti ricostruzione; (7) esiti giudiziari (Trib. Napoli 25.10.1989; ord. Alemi 28.7.1988) e omicidio Casillo; (8) doppio Stato; (9) ponte P2; (10) statuto e verdetto.</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>PONTE P2 CERTIFICATO (aggancio a voce 64): i due vertici SISMI che condussero la trattativa - gen. Santovito e gen. Musumeci - figurano ENTRAMBI nell'elenco P2 verificato gia' in corpus (con Grassini, direttore SISDE): grado A, documentale. Musumeci poi condannato per il depistaggio di Bologna (corpus voce 48). Il caso Cirillo = volto poliziesco-criminale dello Stato profondo, come il cluster P2-Vaticano (voce 64) ne e' il volto finanziario: stessa loggia ai vertici, stesso metodo di delega alla criminalita', stessa scia di sangue. Contraltare del caso Moro: nel 1978 fermezza assoluta, nel 1981 trattativa. Gradi: A 74, B 22, C 4.</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: triangolazione su fonte acquisita (Cross/Rapporto Antimafia 1993, rel. Gualtieri, sentenze) + corpus (elenco P2 verificato, nodi D03, connettoma), senza interrogazione in rete. CERTO (A): sequestro, morti, liberazione dopo trattativa, contatti SISDE/SISMI con Cutolo, rifiuto del denaro, contropartite giudiziarie, 'gravi deviazioni' SISMI, iscrizione P2 di Santovito/Musumeci/Grassini, sentenze. RESTA B/C: mandato politico ultimo, natura di 'operazione P2' della trattativa (regia unica NON provata), ruolo di Pazienza (assente dall'elenco P2 verificato = non certificabile, grado C), movente ultimo dell'omicidio Casillo, categoria 'doppio Stato'. Convergenza di milieu certificata; catena di comando unica non provata. Vincolo fonti rispettato (no interrogazione in rete, no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE CERTIFICATA (caso Cirillo; 100 blocchi; nodo a 4 domini D1-D2-D3-D7 con ponte P2/D4 alla voce 64). Gradazione mista A/B/C.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica/ITALIA_NERA_TRIANGOLAZIONE_CASO_CIRILLO.docx + repertorio/ITALIA_NERA_TRIANGOLAZIONE_CASO_CIRILLO.xlsx</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3446,6 +3446,56 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>VERIFICA, CERTIFICAZIONE e AMPLIAMENTO dei vertici piduisti dell'apparato di sicurezza al momento del sequestro Moro ('occupazione dei centri di controllo') - 250 blocchi mirati + biografia/storia per ogni affiliato - DOCX + Excel a 20 fogli</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica (DOCX) + repertorio (Excel a 20 fogli, 250 blocchi + 40 biografie)</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Su input d'autore (lista di 33 affiliati P2 con ruoli e numeri di tessera, tesi dell'occupazione dei centri di controllo per un 'change regime'). VERIFICATI nominativo per nominativo incrociando il corpus (Elenco P2 verificato, nodi grado A) con ricerca esterna gradata (5 agenti; vincolo no Grokipedia/no il manifesto; WebFetch bloccato -&gt; solo WebSearch). ESITO: nucleo della tesi CORROBORATO - i tre direttori dei servizi riformati (Santovito SISMI, Grassini SISDE, Pelosi CESIS) erano tutti P2; con loro GdF (Giudice, Lo Prete), CC (Siracusano, Cornacchia), Marina (Torrisi), Farnesina (Malfatti, Semprini), magistratura (Spagnuolo), informazione (Di Bella, Selva, Costanzo, Pecorelli), finanza (Sindona, Calvi, Ortolani). Biografia+storia scritte per 33 nominati + Gelli + 6 di ampliamento.</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>AMPLIAMENTO: chiarito che i due sistemi di numerazione (FASCICOLO, corpus, &lt;=962; TESSERA, autore, fino a 1887) sono DISTINTI (prova Berlusconi: tessera 1816/fascicolo 0625; Quarta Prescrizione del corpus). Le adiacenze di TESSERA NON sono certificabili (nessun elenco pubblico ordinato per tessera; risultato negativo registrato). L'ampliamento e' fatto nel sistema dei FASCICOLI (corpus, grado B): il 'blocco' 462-552 fa emergere 6 affiliati NON nella lista d'autore - Maletti (499), Romolo Dalla Chiesa (500, fratello di C.A. Dalla Chiesa), La Bruna (502), Allavena (505), Angelo Rizzoli (532), Tassan Din (534).</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>CORREZIONI CERTIFICATE (valore della verifica): Antonio VARISCO e Achille GALLUCCI NON sono affiliati (Varisco investigo' la loggia e fu ucciso dalle BR il 13.7.1979; Gallucci fu il magistrato criticato dall'Anselmi per aver minimizzato la P2) - attribuzione infondata, ESPUNTI. NON confermati: Guglielmi, Giovannone, Esposito (P2 non documentata). Identita' da correggere: 'Sergio Di Donato/Penthouse' confonde con lo scrittore Pietro Di Donato; Geraci rischio omonimia (Ammiraglio SIOS Marina). Tessere CONFERMATE: Lo Prete 1600, D'Amato 1643, Semprini 1637, Costanzo 1819, Di Bella 1887. CORRETTE: Santovito 1630 (non 163)/Salacone 163 (non 1630) [scambio]; Ortolani 1622 (non 1609); Selva 1814 (non 1803, e appartenenza contestata).</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Statuto: verifica su corpus + ricerca gradata, senza WebFetch (solo WebSearch). CERTO (A/B): appartenenza P2 di 27 dei 33 nominati; i tre vertici dei servizi; il clustering di fascicolo (blocco settoriale); condanne connesse (Musumeci/Bologna, Giudice-Lo Prete/petroli, Maletti-La Bruna/Piazza Fontana, Sindona/Ambrosoli, Calvi/Ambrosiano). NEGATIVI registrati: Varisco e Gallucci non affiliati; adiacenze di tessera non documentate; 3 non confermati. RESTA C: 'change regime', hub Magliana (Musumeci), Stoccolma (Ferracuti), comitato Moro (Semprini), Bologna 2020 (D'Amato). Appartenenza != responsabilita' penale; presenza in lista != appartenenza provata (Cornacchia prosciolto); allegazione != sentenza. Convergenza di milieu CERTIFICATA; catena di comando unica NON provata. Ponte con voci 48 (Bologna), 64 (P2-Vaticano), 66 (Cirillo). Vincolo fonti rispettato (no Grokipedia, no il manifesto). Pendenza: certificare le tessere sull'elenco Anselmi originale (egress aperto).</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>VERIFICA/CERTIFICAZIONE CERTIFICATA (250 blocchi; 40 biografie; tesi corroborata; 2 espunzioni; 6 ampliamenti; numeri in parte confermati/corretti). Gradi blocchi: A 41, B 118, C 48, neg 5. Domini: D3, D4, D9, D10, D8, D6, D2.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica/ITALIA_NERA_P2_APPARATO_MORO_OCCUPAZIONE.docx + repertorio/ITALIA_NERA_P2_APPARATO_MORO_250_BLOCCHI.xlsx</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3496,6 +3496,51 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>RETE ESTESA con 1000 NODI E PONTI MIRATI (1974 - tardo 1982): le persone del corpus LEGATE ma NON AFFILIATE alla P2 - estrazione sistematica dal solo corpus (ritorno al corpus integrale) - DOCX + Excel a 9 fogli</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica (DOCX) + repertorio (Excel a 9 fogli, 1000 blocchi)</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Su consegna d'autore (estendere la rete neurale ad altri 1000 nodi/ponti mirati 1974-tardo 1982, SOLO persone del corpus legate ma non affiliate P2). METODO (solo corpus, nessuna interrogazione in rete): estrazione sistematica dalle 556 schede-nodo (340 nodi-persona) + decodifica di 7.203 sinapsi del Registro Sinaptico Generale (numerali per esteso -&gt; cifre). ANELLO PRIMO: 135 persone non affiliate con sinapsi diretta a un affiliato/loggia. ANELLO SECONDO: 10 persone legate alle istituzioni occupate (base: voce 67), pertinenza mediata C. PONTI: 440 diretti persona-affiliato (B) + 15 istituzionali (C) + 400 interni fra qualificati (soglia intensita' 8, C). TOTALE 1000 blocchi esatti (145 nodi + 855 ponti). Gradi: A 42, B 481, C 477.</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>VERTICI DELL'ANELLO PRIMO (intensita' sinaptica verso gli affiliati): Andreotti-Gelli 116 (conferma quantitativa dell'aggancio DC-loggia, gia' voce 64); Moro-Gelli 88 (la vittima piu' avviluppata dalla rete che la stritolo'); Dalla Chiesa-Sindona 59; Borghese-Gelli 59; Riina-Sindona 47; Ambrosoli-Marcinkus 46; Maletti-Miceli 43; Delle Chiaie-Gelli 43. PONTI INTERNI massimi: Borghese-Delle Chiaie 122; Falcone-Andreotti 119; Bagarella-Riina 94; Riina-Ciancimino 87. La rete tiene insieme carnefici, vittime (Moro, Ambrosoli, Dalla Chiesa, Falcone, Borsellino, La Torre, P. Mattarella, Casalegno, Tobagi, Occorsio), investigatori e cospiratori: topologia documentale, non giudizio.</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: sinapsi = co-occorrenza documentale d'autore, NON prova di rapporto personale ne' complicita' (LEGATO != COMPLICE, avvertenza in testa all'Excel). NEGATIVI REGISTRATI (45 esclusioni in 3 categorie dichiarate): 21 morti prima del 1974 (Luciano, S. Giuliano, Calabresi, De Lorenzo, Allende...); 14 figure di epoche successive senza alcun anno 1974-82 in scheda (Sheinbaum, Milei, Boric, bin Salman...); 10 entita' non-persona espunte (la consegna chiede SOLO persone). PENDENZE: 45 nodi anello primo senza scheda individuale (lacuna D7 dichiarata a voce 60: Borghese, Delle Chiaie, Freda, Ventura... inclusi a grado C come endpoint del connettoma); figure con scheda su epoche successive (Parisi, Sica) gradate C per sola regola automatica benche' note nel periodo da altre voci. Convergenza di milieu certificata; catena di comando unica non provata; nessun blocco imputa reati. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>RETE ESTESA CERTIFICATA (1000 blocchi esatti: 145 nodi non affiliati in 2 anelli + 855 ponti in 3 classi; 45 negativi registrati). Cifra: la loggia come CENTRO DI GRAVITA' del sistema di potere 1974-82, non suo perimetro. Domini: tutti (D1-D10).</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica/ITALIA_NERA_RETE_ESTESA_NON_AFFILIATI.docx + repertorio/ITALIA_NERA_RETE_ESTESA_NON_AFFILIATI_1000.xlsx</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3541,6 +3541,51 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE MIRATA sul PONTE FALCONE-ANDREOTTI (sinapsi 119, la piu' intensa del connettoma per ENTRAMBI i nodi) con 100 blocchi - solo corpus - DOCX + Excel a 12 fogli</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica (DOCX) + repertorio (Excel, 100 blocchi in 10 sezioni)</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Sviluppo del ponte massimo emerso dalla rete estesa (voce 68). DATO PRIMO: il 119 e' la sinapsi PIU' INTENSA di entrambi i capi - per Falcone sopra Riina (92), per Andreotti sopra perfino Gelli (116): primato reciproco unico nel connettoma per una coppia magistrato-politico. INTERMEDIARI CONDIVISI (doppia intensita' F/A): Riina 92/50, Sindona 51/69, Ciancimino 41/63, Lima 41/57, Brusca 71/34, Calo' 28/38, Cossiga 34/51, Moro 40/79. VERSANTE SICILIANO certificato dalle schede A: catena Andreotti-&gt;Lima (referente siciliano)-&gt;Ciancimino (AFFILIATO corleonese, Sacco di Palermo, condannato); Bontate = unico boss dichiarato nella riga sinapsi della scheda Andreotti. CATENA DEL 1992 certificata: Cassazione conferma Maxiprocesso (genn.) -&gt; Lima ucciso 12.3 PER RITORSIONE (scheda) -&gt; Capaci 23.5 (500kg, mandante Riina, esecutore Brusca) -&gt; via D'Amelio 19.7 (morte accelerata per la Trattativa, mediatore Ciancimino).</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>PROCESSO ANDREOTTI (dalla scheda A): assolto in via definitiva (Cass. 2003-2004) con formula articolata - rapporti con Cosa Nostra RICONOSCIUTI fino al 1980, associazione successiva ESCLUSA; Pecorelli: assolto definitivo. ENTRAMBE le meta' registrate come risultati. La cesura giudiziaria del 1980 COMBACIA con la topologia del corpus: il canale Bontate muore nel 1981 (seconda guerra di mafia, scheda Riina), il rapporto muta in ritorsione (Lima 1992). SPIEGAZIONE DEL PONTE (3 ipotesi vagliate): documentale (il documentatore e il documentato: il campo di Falcone = il campo della corrente) + epocale (1989-92: settimo governo, Affari Penali, Cassazione); il RAPPORTO PERSONALE NON e' documentato da alcuna scheda - negativo registrato. Parallelo interno: Ambrosoli-Marcinkus/Sindona (voce 64). Serie 'chi documenta muore': Occorsio, Pecorelli, Ambrosoli, Varisco, Terranova, La Torre, Dalla Chiesa, Chinnici, Falcone, Borsellino.</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: solo corpus (schede V63 grado A + connettoma voce 68 + voci 64/66/67), nessuna interrogazione in rete. LEGATO != COMPLICE in testa. CERTO (A, 50 blocchi): identita', Maxiprocesso, catena 1992 con moventi/mandanti, catena di corrente, formula giudiziaria 2003-04. MISURE (B, 43): il 119, il doppio primato, gli intermediari, Borsellino-Andreotti 38 (un terzo del ponte). INTERPRETAZIONI dichiarate (C, 3). NEGATIVI/PENDENZE (4): nessun rapporto personale documentato; mancano schede Bontate/Salvo/Buscetta/Calo'; sentenze integrali non in fonti/; Trattativa documentata ma non sviluppata (prossimo innesto naturale). Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE CERTIFICATA (ponte documentale ed epocale fra il documentatore e il documentato; 100 blocchi: A 50, B 43, C 3, neg 4). Cifra: la sinapsi massima del politico piu' potente e' il magistrato che ne documento' il campo - e la documentazione si paga. Domini: D10, D2, D1, D4, D6.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica/ITALIA_NERA_TRIANGOLAZIONE_PONTE_FALCONE_ANDREOTTI.docx + repertorio/ITALIA_NERA_TRIANGOLAZIONE_PONTE_FALCONE_ANDREOTTI.xlsx</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3586,6 +3586,51 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE MIRATA sulla TRATTATIVA STATO-MAFIA (1992-1993) con 100 blocchi - l'evento che il corpus documenta (4 schede A) e il processo che NON possiede (perimetro dichiarato) - DOCX + Excel a 12 fogli</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica (DOCX) + repertorio (Excel, 100 blocchi in 10 sezioni)</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Sviluppo dell'innesto indicato dalla voce 69. QUATTRO ATTESTAZIONI grado A: scheda CIANCIMINO ('Mediatore della Trattativa Stato-Mafia 1992-1993 attraverso il figlio Massimo' = esistenza, periodo, mediatore, tramite); scheda BORSELLINO ('documentata da Brusca: la sua morte fu accelerata per i contatti con i Servizi' = fonte ed effetto); scheda MANCINO (Interno 1992-94, 'coinvolto nelle INCHIESTE' - non nel negoziato: distinzione custodita); scheda RIINA (sinapsi 'Trattativa' dichiarata; stragi 1992-93; cattura 15.1.1993). Contesto: catena del 1992 (voce 69), 57 giorni fra Capaci e via D'Amelio = cambio al Viminale + apertura del canale. MEDIATORE: Ciancimino unico nodo bifronte del grafo (affiliato corleonese E sindaco), conferma quantitativa dal connettoma (Lima 99, Riina 87, Andreotti 63, Provenzano 56): la via piu' corta Stato-Cupola passa per lui.</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>REPERTO DELLE MISURE: asimmetria di un ordine di grandezza fra fronte criminale (Bagarella-Provenzano 94, Bagarella-Riina 94, Brusca 78) e fronte istituzionale (Mancino max 8, Scalfaro max 19) -&gt; la Trattativa e' un EVENTO clandestino, non una topologia (a differenza del ponte 119, voce 69); il silenzio sinaptico statale = indizio metodologico coerente col carattere coperto, non prova. TRILOGIA DELLE TRATTATIVE completata: Moro 1978 (negata e non fatta, l'ostaggio muore), Cirillo 1981 (fatta e negata, voce 66), 1992-93 (sotto ricatto stragista, muore Borsellino) - stesso metodo: canale coperto, mediatore criminale elevato a interlocutore, Servizi presenti, smentita. La fermezza selettiva e' costante di sistema.</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: SOLO corpus, nessuna interrogazione in rete. PERIMETRO DICHIARATO (17 negativi registrati): il corpus NON possiede il canale statale (Mori/De Donno/Subranni senza scheda), il papello, il 41-bis/Conso, Massimo Ciancimino come scheda propria, il depistaggio di via D'Amelio (Scarantino/agenda rossa), le stragi continentali 1993 come schede-evento, Dell'Utri/Berlusconi, e SOPRATTUTTO le sentenze del processo Trattativa (2018/2021/2023) -&gt; NESSUN esito processuale affermato, ne' condanne ne' assoluzioni. LEGATO != COMPLICE (vale per Mancino e per ogni nome). Borsellino 'ostacolo al canale' = lettura C dichiarata oltre la lettera della scheda. Prossime acquisizioni indicate: sentenze processo in fonti/, schede ROS/DAP/Graviano, dossier via D'Amelio. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE CERTIFICATA al livello che il corpus consente (evento documentato: 4 schede A; mediatore e effetto certificati; fronte statale quasi non censito; esiti processuali fuori perimetro). 100 blocchi: A 39, B 40, C 4, negativi 17. Domini: D1, D2, D3, D10.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica/ITALIA_NERA_TRIANGOLAZIONE_TRATTATIVA_STATO_MAFIA.docx + repertorio/ITALIA_NERA_TRIANGOLAZIONE_TRATTATIVA_STATO_MAFIA.xlsx</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3631,6 +3631,51 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>VERIFICA del PROCESSO TRATTATIVA STATO-MAFIA (2012-2023) con 100 blocchi - ricerca esterna gradata su 3 gradi di giudizio: colma la pendenza principale della voce 70 - DOCX + Excel a 12 fogli</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica (DOCX) + repertorio (Excel, 100 blocchi in 10 sezioni)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Su consegna d'autore ('procedi a processo Trattativa'). METODO: 3 agenti paralleli (primo grado/appello/Cassazione+quadro), fonti gradate: A = comunicato Cassazione (sistemapenale/giurisprudenzapenale) e testi ripubblicati; B = stampa di qualita' concorde; C segnalato. RICOSTRUZIONE: rinvio a giudizio 7.3.2013 (GUP Morosini), art. 338 c.p.; dibattimento 27.5.2013, 228 udienze (pres. Montalto). PRIMO GRADO 20.4.2018: Bagarella 28, Mori/Subranni/Dell'Utri/Cina' 12, De Donno 8, M. Ciancimino 8 (calunnia), Mancino ASSOLTO, Brusca prescritto; motivazioni 5.252 pp: 'veicolazione' della minaccia + ipotesi accelerazione via D'Amelio. APPELLO 23.9.2021 (pres. Pellino): ROS assolti 'il fatto non costituisce reato' ('improvvida iniziativa', 'finalita' solidaristiche': far cessare le stragi); Dell'Utri 'per non aver commesso il fatto'; Bagarella 27 (segmento riqualificato tentativo, prescritto); motivazioni 2.971 pp. CASSAZIONE VI sez. 27.4.2023 n. 45506: annullamento SENZA RINVIO con formula AMPLIATA per i ROS ('per non aver commesso il fatto'), Dell'Utri definitivo, ricorso PG respinto nel merito; Bagarella/Cina' riqualificati in TENTATIVO -&gt; PRESCRITTO (le pene cadono); motivazioni 95 pp (10.11.2023): il dialogo 'puntava a fermare le stragi', 'si limitarono a ricevere la minaccia senza sollecitarla'.</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>ESITO CAPITALE: NESSUNO e' condannato in via definitiva per la Trattativa (assolti tutti gli uomini dello Stato e Dell'Utri; prescritto il tentativo dei boss; Riina/Provenzano morte del reo; Mannino definitivo 2020; Mancino non impugnato). MA IL FATTO RESTA: l'interlocuzione ROS-Ciancimino 1992-93 e' affermata da TUTTE le corti - la controversia fu solo la qualificazione penale. RACCORDO COL CORPUS: scheda Ciancimino CONFERMATA (mediatore = fatto); scheda Mancino CONFERMATA E CHIUSA (assoluzione definitiva); scheda Borsellino DA ANNOTARE ('accelerata' = tesi di primo grado 2018, non accertamento definitivo - retrocede a ipotesi di merito); trilogia della voce 70 NON toccata (il canale resta storicamente affermato). DEPISTAGGIO VIA D'AMELIO acquisito: Borsellino quater definitivo (Cass. 5.10.2021: ergastoli Madonia/Tutino; Scarantino 'indotto'; 'uno dei piu' gravi depistaggi della storia giudiziaria'); processo poliziotti: prescrizione per tutti e tre in appello (4.6.2024) a condotta riconosciuta; motivazioni 2026 'interessi esterni' = fonte unica C.</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: ASSOLTO E' UN RISULTATO (formule esatte registrate); PRESCRITTO NON SIGNIFICA ASSOLTO (Bagarella, Cina', Brusca, M. Ciancimino, poliziotti: distinzione custodita); TESI DI MERITO != ACCERTAMENTO (veicolazione/accelerazione = primo grado riformato); dichiarazioni di parte registrate come tali (Di Matteo 'colpo di spugna'). LIMITE: testi integrali non letti (proxy) -&gt; A solo su comunicati/testi ufficiali ripubblicati; PENDENZE (7): PDF sentenze da acquisire in fonti/ (4 testi indicati), papello, 41-bis, agenda rossa, esito Cassazione depistaggio, schede-nodo dei nuovi nomi (Mori, Subranni, De Donno, Dell'Utri, Mannino...). Vincolo fonti rispettato (no Grokipedia, no il manifesto; Wikipedia solo corroborazione C segnalata).</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>VERIFICA PROCESSUALE CERTIFICATA nei limiti delle fonti (100 blocchi: A 43, B 46, C 4, neg 7). Cifra: la Trattativa e' un FATTO senza REATO per gli uomini dello Stato e un REATO TENTATO PRESCRITTO per i boss; il depistaggio di via D'Amelio e' fatto giudizialmente accertato. Domini: D1, D2, D3, D10.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica/ITALIA_NERA_PROCESSO_TRATTATIVA.docx + repertorio/ITALIA_NERA_PROCESSO_TRATTATIVA_100_BLOCCHI.xlsx</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3676,6 +3676,51 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>CHIUSURA DELLE PENDENZE DELLA TRATTATIVA (voce 71) con 80 blocchi + 9 SCHEDE INTEGRATIVE: papello, 41-bis/Conso, agenda rossa, Cassazione depistaggio, nodi processuali - DOCX + Excel a 11 fogli</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica (DOCX) + repertorio (Excel: 80 blocchi in 8 sezioni + foglio Schede integrative)</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Su consegna d'autore ('procedi con le pendenze'). ESITI: (1) PDF sentenze = NEGATIVO CERTIFICATO (curl 403 al CONNECT, egress policy; acquisizione rimessa all'autore/sessione a rete aperta, URL censiti). (2) PAPELLO censito col suo statuto esatto: FOTOCOPIA consegnata da M. Ciancimino il 15.10.2009 con post-it attribuito al padre; perizia 2016 senza manomissioni MA senza datazione/attribuzione; 1° grado NON vi fonda l'accertamento (demolisce l'attendibilita' del consegnante); appello: non escluso che l'originale non sia mai esistito nelle mani del figlio -&gt; AUTENTICITA' MAI ACCERTATA GIUDIZIALMENTE (risultato per assenza); le 12 richieste censite come 'versione 2009'. (3) 41-BIS doppia verita': D.L. 306/1992; ~300 decreti Martelli post-D'Amelio; MANCATO RINNOVO di 334 decreti (Conso, nov. 1993) rivendicato 'in completa solitudine... per fermare la minaccia di altre stragi' (Antimafia 2010); il 'segnale' e' ricostruzione storica confermata in appello MA nessun reato di alcuno (Cassazione).</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>(4) AGENDA ROSSA - la novita' piu' grande dal 1992: perquisizioni ROS (giu. 2025, proc. De Luca) in immobili dell'ex procuratore GIOVANNI TINEBRA (+2017, primo titolare delle indagini; ipotesi loggia segreta di Nicosia) sulla base di un APPUNTO del 20.7.1992 A FIRMA LA BARBERA mai trasmesso alla procura: scatola con borsa e 'un'agenda' consegnata a Tinebra (quale agenda: in accertamento). Arcangioli resta prosciolto definitivo (Cass. 2009); agenda mai ritrovata (34° anniversario). (5) DEPISTAGGIO: motivazioni d'appello ORA CONFERMATE da piu' testate (GdS, La Sicilia, L'Indipendente...): 'La Barbera protesse interessi e centri di potere esterni a Cosa Nostra', servizi che 'assecondarono' -&gt; il dato sale da C a A/B; L'APPUNTO E LA SENTENZA CONVERGONO SULLO STESSO UOMO. Cassazione sul depistaggio PENDENTE (ago. 2026); PISTA NERA: ricorso inammissibile (apr. 2026) -&gt; le indagini sui concorrenti esterni DEVONO proseguire; Firenze: Dell'Utri ARCHIVIATO (6a volta, 2026), filone Mori/De Donno APERTO. (6-7) NOVE SCHEDE INTEGRATIVE (grado B, candidati alla formalizzazione V63): Mori (3 assoluzioni definitive), Subranni (+22.3.2024), De Donno (il collaboratore di Falcone su mafia-appalti), Dell'Utri (condanna definitiva concorso esterno fino al 1992 + assoluzione definitiva Trattativa: SEMPRE insieme), Mannino (mai condannato), M. Ciancimino (fonte screditata, 2 condanne definitive proprie), Provenzano, Brusca (libero 2021, vigilata finita 2025), Bagarella (13 ergastoli, 41-bis).</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: assolto e' un risultato; prescritto non significa assolto; un documento si tiene al grado del suo supporto, non della sua fama (papello); citazioni di seconda mano B con via ad A indicata (resoconto Conso; motivazioni depistaggio). PENDENZE RESIDUE dichiarate: PDF in fonti/, Cassazione depistaggio, pista nera, filone Firenze, tenore letterale Conso, l'agenda in se'. Vincolo fonti rispettato (no Grokipedia, no il manifesto; Wikipedia e testate di parte solo segnalate).</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>PENDENZE LAVORATE E CHIUSE OVE POSSIBILE (80 blocchi: A 31, B 43, C 1, neg 5; + 9 schede integrative B). La vicenda Trattativa e' ora completa nei suoi tre strati: evento (voce 70), processo (voce 71), margini e protagonisti (voce 72). Domini: D1, D2, D3, D10.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica/ITALIA_NERA_PENDENZE_TRATTATIVA.docx + repertorio/ITALIA_NERA_PENDENZE_TRATTATIVA.xlsx</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3721,6 +3721,51 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE dell'ASSE LA BARBERA-TINEBRA con 100 blocchi + 2 SCHEDE INTEGRATIVE - innesto interamente nuovo (il corpus non possedeva nulla sui due nomi) - DOCX + Excel a 13 fogli</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica (DOCX) + repertorio (Excel: 100 blocchi in 10 sezioni + 2 schede)</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Su consegna d'autore. AVVERTENZA COSTITUTIVA: La Barbera (+12.12.2002) e Tinebra (+6.5.2017) DECEDUTI, MAI IMPUTATI NE' CONDANNATI - ogni formula e' accertamento incidentale in processi ad altri o valutazione post mortem; NESSUNA imputazione postuma. FATTI A: nota AISI = La Barbera collaboratore RETRIBUITO del SISDE febb.1986-mar.1988, nome in codice RUTILIUS ('Catullo' non confermato dall'atto), arruolato dall'ufficio di Luigi DE SENA (lo stesso che nel 1992 ne propizio' la nomina al gruppo Falcone-Borsellino; due assegni da 22 mln a De Sena agli atti); Tinebra procuratore capo CL dal luglio 1992, delego' le indagini al gruppo La Barbera e il 20.7.1992 chiese la collaborazione IRRITUALE del SISDE (Contrada) - censura del quater; TINEBRA CAPO DEL DAP 2001-2006 (il custode del 41-bis; Protocollo Farfalla DAP-SISDE); CATENA DI CUSTODIA rotta: borsa per giorni SU UN DIVANETTO nell'ufficio di La Barbera, MAI un verbale di sequestro (dep. Cardella), APPUNTO 20.7.1992 ('...viene consegnato al dottore Tinebra uno scatolo... una borsa in pelle e una agenda...') mai trasmesso in 33 anni, SENZA ricevuta, consegna NON verificata, rossa/grigia non accertabile; quater: La Barbera 'ruolo fondamentale nella costruzione delle false collaborazioni', Scarantino 'indotto'; MOTIVAZIONI APPELLO DEPISTAGGIO (dep. 2.3.2026, ~289 pp): La Barbera 'DOMINUS', azione DELIBERATA per 'tutelare sistemi di interessi e centri di potere esterni e piu' complessi' rispetto a Cosa Nostra; poliziotti 'consapevoli delle bugie'; servizi 'quantomeno assecondarono'.</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>LE QUATTRO CONVERGENZE DOCUMENTATE DELL'ASSE: (1) l'appunto 20.7.1992; (2) la delega delle indagini; (3) il doppio filo SISDE (Tinebra lo chiama, La Barbera ne era stato pagato); (4) la gestione condivisa di Scarantino (gruppo di polizia + pm dell'ufficio: lettera Boccassini-Saieva 12.10.1994 sull'inattendibilita' ignorata; ritrattazioni 1995/1998 riassorbite; pm Petralia/Palma indagati a Messina e ARCHIVIATI - il 'nodo pm' resta rilievo, non accertamento). IPOTESI C DICHIARATE: loggia coperta 'TERZO ORIENTE' di Nicosia 'nata dalle ceneri della P2' cui Tinebra sarebbe appartenuto (ipotesi della procura CL nel decreto di perquisizione 26.6.2025, elementi: Pennino, Siino, intercettazione Spinello, dich. Di Bernardo - MAI vagliata da un giudice; perquisizioni: agenda NON trovata); sottrazione/copia dell'agenda da parte di La Barbera (ipotesi procura); 'Tinebra e Mori erano amici' (Ardita, C). STATO 2026: Cassazione depistaggio pendente; depistaggio bis in corso (4 poliziotti); PISTA NERA prosegue per ordine del gip (Cass. inammissibile 23-24.4.2026); procura orientata su MAFIA-APPALTI (il dossier Mori-De Donno, voce 72). Correzioni al corpus: quater definitivo ott.2021/2022; Arcangioli prosciolto dal GUP (2009).</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: convergenza documentale CERTIFICATA, disegno unitario NON giudicato; il documento fondante (l'appunto) e' anche l'anello fragile (nessuna ricevuta) - negativo registrato al centro; ipotesi dichiarate come ipotesi; fonti C (antimafiaduemila, PSF, StampaLibera, il Giornale) usate solo su fatti riscontrabili o come dichiarazioni. Tre indagini aperte possono spostare ogni grado: VOCE GIALLA PER COSTITUZIONE. Vincolo fonti rispettato (no Grokipedia, no il manifesto). Con questa voce la vicenda via D'Amelio e' nel corpus in 4 strati: strage (schede), Trattativa (70-71), processo/margini (71-72), asse del depistaggio (73).</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>ASSE CERTIFICATO COME FATTO DOCUMENTALE (100 blocchi: A 52, B 37, C 10, neg 1; + 2 schede integrative B). Cifra: i due uomini che governarono le prime indagini sono gli stessi su cui convergono, 33 anni dopo, l'appunto e le motivazioni sugli 'interessi esterni'. Domini: D3, D10, D1, D4(ipotesi).</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica/ITALIA_NERA_ASSE_LA_BARBERA_TINEBRA.docx + repertorio/ITALIA_NERA_ASSE_LA_BARBERA_TINEBRA.xlsx</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3766,6 +3766,51 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>ATTO DI RICEZIONE di 8 DOCUMENTI D'AUTORE + 2 IMPRONTE SHA-256, con la PRIMA VERIFICA CRITTOGRAFICA dell'opera - e registrazione del QUINTO_REGISTRO_TAVOLA_UNICA come ATTESO (hash senza file)</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera (8 documenti) + corpus/diagnostica (2 impronte sha256)</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Ricevuti e collocati con nome pulito, deduplicati per hash (2 doppioni scartati: CAMERA e ESOTERICA caricate due volte): (1) MNBB18_AMPLIATO_E_FEDERAZIONE_BRIGHTON_BEACH (2.749 parole: la scheda MN-BB-18 - Trump e il sosia di Gorbaciov, dic. 1988 - ampliata a 50 blocchi in 8 filoni, con federazione nella catena Brighton Beach); (2) la scheda di ricerca in .md che ne e' la base (Trump-Gorbachev Encounter, con tavola Savona e 3 STATI ZERO dichiarati: 'Larissa'-&gt;Raisa, Fred Trump/Don Jr. inesistenti, incontro privato Mosca 1987 infondato); (3) CAMERA_ISTRUTTORIA_RACCORDO_CINQUANTA_BLOCCHI (13.908 parole: aggiudicazione del materiale conferito - BIFORCAZIONE DELLE FILIERE EVERSIVE, confutazione del monolite dell'Internazionale Nera, caso Moro, Badalamenti/Impastato, disciplina sui viventi); (4) REGISTRO_DI_TRIANGOLAZIONE_21AGO2026 (8.338 parole: 16 ricognizioni federate in 5 pannelli - sudafricano-namibiano, opusdeista, tedesco-vaticano/Oder-Neisse, turco/Agca, aginteriano - + calibrazione libica); (5) QUARTA_SERIE_50_BLOCCHI_CERTIFICAZIONE_V70 (3.578 parole: certificazione della linea del Dossier V61-V70, 20 unita', recepimenti e pendenze); (6) SEZIONE_ESOTERICA_CINQUANTA_BLOCCHI (14.305 parole: tradizionalismo Guenon/Evola, Freda/Rauti/ON, Istituto Pollio, satanismo, Santa Sede, caso Moro - con divieto di inferenza simbolica e falsificatori designati); (7) SEZIONE_DIASPORA_NAZISTA_CINQUANTA_BLOCCHI (13.610 parole: i 5 teatri dell'acquisizione del capitale umano del Reich - Paperclip, Osoaviakhim, penisola iberica, Sudamerica, Medio Oriente - con confutazione della sigla unica ODESSA come costruzione postuma); (8) ITALIA_NAZIONI_UNITE_EMBARGO (4.289 parole: 18a ricognizione - l'Italia all'ONU su embargo/apartheid/Namibia, l'INVERSIONE DEL 1976-77, il 'decimo grado di Stato Zero' come barriera macchinica).</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>VERIFICA CRITTOGRAFICA (PRIMA DELL'OPERA): l'impronta dichiarata ITALIA_NERA_IL_SACRO_E_L_EVERSIONE.sha256.txt COMBACIA con la copia gia' in corpus (sha256 5e47c008...641 VERIFICATA): il documento della voce precedente e' ora certificato crittograficamente contro la dichiarazione d'autore; il ri-caricamento del DOCX (md5 identico) e' stato deduplicato. PENDENZE: (a) il PDF del Sacro (impronta dichiarata 4451d034...922) NON e' in corpus - atteso; (b) QUINTO_REGISTRO_TAVOLA_UNICA.docx: e' arrivata SOLO l'impronta (f101b94e...9e9), NON il file - registrato come DOCUMENTO ATTESO: al suo arrivo la verifica sara' immediata contro l'hash gia' depositato. E' il primo caso di 'impronta che precede il documento': meccanismo di integrita' prezioso, da mantenere.</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: ATTO DI RICEZIONE con deduplica per hash e verifica crittografica; nessuna interrogazione in rete; nomi puliti senza prefissi UUID; le due impronte collocate in diagnostica come attestazioni. I documenti (3)-(8) sono sezioni/registri del Registro Unico Federato e ricognizioni d'autore: grado A d'origine conservato; (1)-(2) scheda MN con gradazione interna propria (A/B/C e Stati Zero dichiarati dall'autore). Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>RICEZIONE CERTIFICATA (8 documenti + 2 impronte; 1 verifica crittografica riuscita; 2 doppioni deduplicati; 2 attesi: QUINTO_REGISTRO.docx e SACRO.pdf). Domini: D7, D4, D5, D2, D3, D6, D8 + MONDO NERO.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera/ (8 file) + corpus/diagnostica/ (2 impronte sha256)</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3811,6 +3811,51 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE TOTALE DEL LOTTO (voce 74) con 2000 BLOCCHI MIRATI ESATTI - nove documenti, capoverso per capoverso, contro l'intero grafo del corpus - DOCX + Excel a 25 fogli</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica (DOCX) + repertorio (Excel, 2000 blocchi)</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Architettura a strati: 90 blocchi di SINTESI MIRATA (10 per documento, manuali); 1.228 blocchi di TRIANGOLAZIONE AUTOMATICA (ogni capoverso sostanziale cercato contro 486 schede-nodo + 547 capi del connettoma + alias curati); 162 PONTI documento-nodo (con grado sinaptico); 299 SINAPSI DOCUMENTALI NUOVE (coppie di entita' co-occorrenti nello stesso capoverso = archi candidati per il connettoma); 201 UNITA' INTERNE CERTIFICATE (intestazioni di blocco/capitolo/fase); 20 blocchi di metodo e verdetto. TESI MAGGIORI RECEPITE: biforcazione delle filiere eversive + confutazione del monolite dell'Internazionale Nera (Camera Istruttoria - converge con la tesi bicefala, voce 60, e le da' il criterio di demarcazione); ODESSA come costruzione postuma e il pattern unico Paperclip/Osoaviakhim (Diaspora); INVERSIONE dei voti italiani sulla Namibia 1976-77 (ONU - coincidenza col quadro interno registrata come DOMANDA, grado C); il chiasmo portoghese (protegge Aginter, sorveglia l'Opus Dei); i tre Stati Zero della scheda Trump-Gorbaciov (sosia 1988).</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>ESITO DELLA COPERTURA: 819 blocchi con AGGANCIO documentale al corpus (il lotto parla ai nodi esistenti: Evola/Freda/Rauti, Barbie e i teatri, Aginter/Guerin-Serac, dorsale apartheid, Moro/Santa Sede); 904 INNESTI PURI (capoversi senza aggancio = materia nuova: catena Brighton Beach, personale della diaspora, canali onusiani - candidati a nodi futuri); le 299 coppie co-occorrenti sono la mappa pronta dei nuovi archi. Sezione esoterica + monografia del Sacro federate a vicenda col divieto di inferenza simbolica e i falsificatori designati; Quarta serie = gemello d'autore del registro delle verifiche (linea V61-V70 cumulativa attestata per struttura).</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: triangolazione su SOLO corpus + lotto, nessuna interrogazione in rete; grana lessicale degli strati automatici dichiarata e compensata dagli strati manuali; innesti puri dichiarati C (non forzati); negativi registrati (documento atteso QUINTO_REGISTRO; PDF Sacro atteso; pendenze interne della Quarta serie: Oder-Neisse, ricognizione keniota, cinque proposizioni, linea speculare). Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE TOTALE ESEGUITA (2000 blocchi esatti: A 273, B 819, C 904, neg 4; 25 fogli). Il lotto entra FEDERATO, non giustapposto. Domini: D2, D3, D4, D5, D6, D7, D8 + MONDO NERO.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica/ITALIA_NERA_TRIANGOLAZIONE_LOTTO_2000_BLOCCHI.docx + repertorio/ITALIA_NERA_TRIANGOLAZIONE_LOTTO_2000_BLOCCHI.xlsx</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3856,6 +3856,51 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>ATTO DI RICEZIONE del SECONDO LOTTO: 6 documenti nuovi (2 tomi parlamentari + 4 PDF di ricerca) - 7 ri-allegati gia' in corpus deduplicati, 3 doppioni interni scartati</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>fonti/ (tomi parlamentari) + corpus/opera (PDF di ricerca)</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>NUOVI: (1-2) XIII Legislatura, Doc. XXIII n. 64, Vol. I, TOMO V.2 - 'LA DIMENSIONE SOVRANAZIONALE DEL FENOMENO EVERSIVO IN ITALIA' (Commissione stragi; ~121.000 parole) in DUE VARIANTI con hash diverso (contenuto pressoche' identico: la seconda collocata come _VARIANTE; capitoli: collegamenti internazionali, Apparato di Vigilanza Rivoluzionaria, Orizzontale Latina, Centro Estero, Secchia, rapporto SISMI su Cecoslovacchia/Sejna, carteggio Havel...) -&gt; fonti/, grado A per l'acquisizione (atto parlamentare); (3) ITALIA_NERA_DOSSIER_V10_QUADRANTE_MORO_INTERNAZIONALE.pdf (50 pp, 28.653 parole): 'LA VENDETTA DEL CHE: MONIKA ERTL - il triangolo Bolivia-Amburgo-Milano 1948-1983', quinta campagna del Dossier - 12 capitoli (famiglia Ertl, Quintanilla, ELN/Teoponte, esecuzione di Amburgo 1.4.1971, pista Feltrinelli, apparati attorno a Barbie, summit del crimine Apalachin/Palermo/Montalto, teatro boliviano P2/WACL, Aginter, Hyperion); (4) Rete_P2_E_Dittature_Internazionali_Analisi_Estesa.pdf (18 pp: P2/Condor/stronismo/apartheid, metodologia dell'incrocio onomastico, falsi positivi, Massagrande, Graziani, Paraguay come epicentro); (5) Diaspora_Nazista_PostBellica_Ricerca_Approfondita_1.pdf (40 pp, 10 capitoli: i teatri della diaspora con apparato URL - la base di ricerca della Sezione della voce 74); (6) Ricerca_Oligarca_Ilan_Shor_Connessioni_Internazionali.pdf (21 pp: rapporto sull'infrastruttura di guerra ibrida di Ilan Shor 2024-2026 - MONDO NERO contemporaneo, vettori di infiltrazione, mappatura URL).</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>RI-ALLEGATI GIA' IN CORPUS (deduplicati per hash, nessuna copia doppia): Sezione Diaspora, Italia-ONU Embargo, Nazisti_in_USA_Ricerca_Approfondita.pdf, VERIFICA_03 (Spagna/Portogallo), VERIFICA_05 (Diaspora), VERIFICA_06 (Paperclip), VERIFICA_08 (Sud America) - saranno inclusi nella triangolazione del lotto come richiesto ('tutti i documenti allegati'), i primi due per rinvio alla voce 75 (gia' triangolati capoverso per capoverso). Doppioni interni al lotto scartati: 3. NOTA: il PDF 'Rete P2 e dittature' usa il paradigma dell''Internazionale Nera' che la Camera Istruttoria (voce 74) CONFUTA come monolite: la tensione fra i due documenti d'autore va registrata nella triangolazione, non sanata d'ufficio.</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: ATTO DI RICEZIONE con deduplica per hash e nomi puliti; tomo parlamentare = A per l'acquisizione, B per le valutazioni (undicesima regola della risalita); PDF di ricerca = B (con apparati URL da censire); Shor = MONDO NERO contemporaneo, B/C. Nessuna interrogazione in rete. Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>RICEZIONE CERTIFICATA (6 nuovi + 7 ri-allegati dedup + 3 doppioni scartati). Domini: D7, D2, D3, D4, D9 + MONDO NERO. Prossimo atto: triangolazione del lotto con 2000 blocchi (voce 77).</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>fonti/ (Tomo V.2 + variante) + corpus/opera/ (4 PDF)</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3901,6 +3901,51 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE TOTALE DEL SECONDO LOTTO (voce 76) con 2000 BLOCCHI MIRATI ESATTI - tredici documenti, capoverso per capoverso, contro l'intero grafo del corpus - DOCX + Excel a 29 fogli</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica (DOCX) + repertorio (Excel, 2000 blocchi)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Architettura a strati: 130 blocchi di SINTESI MIRATA (10 per documento, manuali); 1.592 blocchi di TRIANGOLAZIONE AUTOMATICA (ogni capoverso sostanziale vs 486 schede-nodo + connettoma + alias curati); 195 PONTI documento-nodo; 63 SINAPSI DOCUMENTALI NUOVE (coppie co-occorrenti = archi candidati); 20 blocchi di metodo e verdetto. CAMPIONAMENTO DICHIARATO sul Tomo V.2 (XIII leg., Doc. XXIII n.64, Vol. I, ~121.000 parole): 1 capoverso ogni 2 (719 su 1.437) - copertura fine a future unita' dedicate, testo integrale in fonti/; variante non ricontata (collazione = pendenza). TESI MAGGIORI: dimensione sovranazionale parlamentare (Apparato di Vigilanza Rivoluzionaria, Centro Estero/Secchia, rapporto SISMI-Cecoslovacchia/Sejna, carteggio Havel); quadrante andino (Monika Ertl, triangolo Bolivia-Amburgo-Milano: il documento piu' agganciato del lotto, 255/372 capoversi con aggancio); Paraguay epicentro della transumanza nera; TENSIONE REGISTRATA 'Internazionale Nera' (PDF P2-dittature) vs confutazione del monolite (Camera, voce 74) - prevale per statuto il criterio della Camera; Mondo Nero contemporaneo (Shor: 4/99 agganci = innesto quasi puro).</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>ESITO DELLA COPERTURA: 502 blocchi con AGGANCIO documentale (Barbie, Feltrinelli, Aginter, i teatri della diaspora, i vertici criminali) e 1.090 INNESTI PURI - proporzione piu' spostata verso l'innesto rispetto al lotto 1 per il personale nuovo del tomo parlamentare (apparati dell'Est) e per la contemporaneita' del rapporto Shor; il caso boliviano risulta attestato da QUATTRO strati concordi (V10 + Barbie + Verifica 08 + Sezione), il fronte USA e l'iberico da tre. Le 63 coppie co-occorrenti sono la mappa dei nuovi archi.</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: triangolazione su SOLO corpus + lotto, nessuna interrogazione in rete; campionamento dichiarato con k esplicito; grana lessicale degli strati automatici dichiarata e compensata dagli strati manuali; innesti puri non forzati (grado C); negativi registrati (variante non ricontata; pendenze interne delle verifiche). Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE TOTALE ESEGUITA (2000 blocchi esatti: A 65, B 838, C 1.091, neg 6; 29 fogli). Il secondo lotto entra FEDERATO, non giustapposto. Domini: D2, D3, D4, D7 + MONDO NERO + dimensione sovranazionale.</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica/ITALIA_NERA_TRIANGOLAZIONE_LOTTO2_2000_BLOCCHI.docx + repertorio/ITALIA_NERA_TRIANGOLAZIONE_LOTTO2_2000_BLOCCHI.xlsx</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
+++ b/corpus/diagnostica/ITALIA_NERA_REGISTRO_VERIFICHE_DOCUMENTALI.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3946,6 +3946,96 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>ATTO DI RICEZIONE del TERZO LOTTO: 16 file conferiti - deduplica per impronta E per contenuto: 1 NUOVO, 2 varianti di formato, 1 doppione di contenuto con hash diverso, 12 doppioni per hash scartati</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera (nuovo + varianti)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>NUOVO: Russia_Unita_Accordi_Internazionali_e_Zheleznyak.pdf (16 pp, ~6.400 parole): 'L'Internazionale Parallela' - la diplomazia partitica di Russia Unita e la guerra cognitiva globale sotto la regia di Sergei Zheleznyak (sanzionato per la Crimea); la rete dei 58 accordi fra partiti col paradigma dell'accordo di Mosca 6.3.2017 con la Lega Nord; Italia 'laboratorio', Austria, Balcani (Dichiarazione di Lovcen), spazio post-sovietico, Sud Globale -&gt; MONDO NERO, secondo pilastro accanto al rapporto Shor (voce 76). VARIANTI DI FORMATO collocate accanto ai primari: Nazisti_in_USA_Ricerca_Approfondita.txt e Nazisti_in_URSS_Ricerca_Approfondita.docx (testo identico ai PDF gia' in corpus, verificato su inizio/fine/capitoli).</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>NAZIINUSA.pdf: impronta NUOVA ma contenuto IDENTICO al finding aid gia' in fonti/ (stesso inizio, stessa fine, stesse 537 parole) -&gt; DOPPIONE DI CONTENUTO scartato: fissata la regola che due impronte diverse possono custodire lo stesso testo (confronto testuale d'obbligo). 12 doppioni per hash scartati (fra cui 2 doppi anche interni al lotto); rilevata pendenza di pulizia: Diaspora_Nazista_..._Approfondita.docx figura in corpus in DUE copie identiche.</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: deduplica dichiarata file per file nel foglio 'Ricezione e deduplica' del repertorio del lotto; nessuna interrogazione in rete; vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>RICEZIONE CERTIFICATA (1 nuovo + 2 varianti + 13 scarti dichiarati). Dominio: MONDO NERO. Prossimo atto: triangolazione del lotto (voce 79).</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>corpus/opera/ (3 file collocati)</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE DEL TERZO LOTTO con 152 BLOCCHI - il rapporto Russia Unita/Zheleznyak capoverso per capoverso, il finding aid campionato, le omonimie scartate - DOCX + Excel a 9 fogli</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica (DOCX) + repertorio (Excel, 152 blocchi)</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Architettura: 16 blocchi di ricezione/deduplica; 10 di sintesi mirata; 98 di TRIANGOLAZIONE AUTOMATICA (capoverso per capoverso vs 486 schede-nodo + connettoma + alias): 2 SOLI AGGANCI GENUINI (Putin; Namibia/SWAPO) e 96 innesti puri - il corpus storico si ferma ai primi anni '90, il rapporto e' materia contemporanea; 3 ponti documento-nodo + 2 FALSI POSITIVI dichiarati; 1 sinapsi documentale nuova (Namibia&lt;-&gt;SWAPO); 10 blocchi di campione del finding aid (Cukurs, Arajs, Artukovic, Axmann, d'Alquen - con difetto di lezione da traduzione automatica dichiarato); 10 di statuto e verdetto. CONVERGENZA REGISTRATA: la SWAPO della rete di Russia Unita e' la stessa Namibia dell'inversione dei voti italiani 1976-77 (voce 75) - continuita' di TEATRO come dato, nessuna inferenza di continuita' di regia.</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>ESITO PIU' ISTRUTTIVO: l'aggancio automatico proponeva 'Partito Democratico' e 'Partito Repubblicano' (nodi del corpus), ma la lettura dei contesti mostra che designano il Partito Democratico di Serbia, il PDP-Laban filippino, il Partito Repubblicano d'Armenia, il PDP tagiko: OMONIMIE = falsi positivi dell'incrocio onomastico, scartati e registrati - PRIMA APPLICAZIONE OPERATIVA della metodologia dei falsi positivi teorizzata dal PDF Rete_P2_E_Dittature (voce 76): il lotto precedente ha fornito la regola con cui si e' vagliato il successivo.</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Statuto: triangolazione su SOLO corpus + lotto; omonimie scartate per lettura dei contesti; l'elenco nominativo indirizza e non pronuncia; negativi registrati (lezione deformata del finding aid; doppia copia interna Diaspora; materia contemporanea che aggancia poco per costruzione). Vincolo fonti rispettato (no Grokipedia, no il manifesto).</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>TRIANGOLAZIONE ESEGUITA (152 blocchi: A 16, B 24, C 96, neg 16; 9 fogli). Il terzo lotto entra FEDERATO. Catena ricezione-triangolazione = protocollo stabile (74-75, 76-77, 78-79). Dominio: MONDO NERO + D.diaspora.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>corpus/diagnostica/ITALIA_NERA_TRIANGOLAZIONE_LOTTO3_RUSSIA_UNITA.docx + repertorio/ITALIA_NERA_TRIANGOLAZIONE_LOTTO3_RUSSIA_UNITA.xlsx</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>9.8.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
